--- a/nbv_turniermodi_excel/T16a_9-Spieler-Kalender-Vorlage.xlsx
+++ b/nbv_turniermodi_excel/T16a_9-Spieler-Kalender-Vorlage.xlsx
@@ -1754,7 +1754,6 @@
     <x:mergeCell ref="T13:T15"/>
     <x:mergeCell ref="A17:T17"/>
   </x:mergeCells>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:pageMargins left="0.2" right="0.2" top="0.3" bottom="0.3" header="0.1" footer="0.1"/>
   <x:pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="1"/>
 </x:worksheet>
@@ -3124,7 +3123,6 @@
     <x:mergeCell ref="T16:T18"/>
     <x:mergeCell ref="A20:T20"/>
   </x:mergeCells>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:pageMargins left="0.2" right="0.2" top="0.3" bottom="0.3" header="0.1" footer="0.1"/>
   <x:pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="1"/>
 </x:worksheet>
@@ -4486,7 +4484,6 @@
     <x:mergeCell ref="S1:T1"/>
     <x:mergeCell ref="S2:T2"/>
   </x:mergeCells>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:pageMargins left="0.2" right="0.2" top="0.3" bottom="0.3" header="0.1" footer="0.1"/>
   <x:pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="1"/>
 </x:worksheet>
@@ -5725,7 +5722,6 @@
   <x:mergeCells>
     <x:mergeCell ref="A12:P12"/>
   </x:mergeCells>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:pageMargins left="0.2" right="0.2" top="0.3" bottom="0.3" header="0.1" footer="0.1"/>
   <x:pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="1"/>
 </x:worksheet>
@@ -7304,7 +7300,6 @@
       <x:c r="T45" s="2"/>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:pageMargins left="0.2" right="0.2" top="0.3" bottom="0.3" header="0.1" footer="0.1"/>
   <x:pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="1"/>
 </x:worksheet>

--- a/nbv_turniermodi_excel/T16a_9-Spieler-Kalender-Vorlage.xlsx
+++ b/nbv_turniermodi_excel/T16a_9-Spieler-Kalender-Vorlage.xlsx
@@ -2,18 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet name="Gruppe A" sheetId="1" ns1:id="R241edcd564094995"/>
-    <x:sheet name="Gruppe B" sheetId="2" ns1:id="R35b359f5d19b40b7"/>
-    <x:sheet name="Finalrunde" sheetId="3" ns1:id="Rd28df2019d394ba2"/>
-    <x:sheet name="Teilnehmer" sheetId="4" ns1:id="R75e73f22ef6c4fa5"/>
-    <x:sheet name="CSV Export" sheetId="5" ns1:id="Rbb1fc035748f4c2d"/>
+    <x:sheet name="Gruppe A" sheetId="1" ns1:id="R3b84c1e1b2b141fb"/>
+    <x:sheet name="Gruppe B" sheetId="2" ns1:id="R94439bf219614067"/>
+    <x:sheet name="Finalrunde" sheetId="3" ns1:id="R1ba88e7bf9404fd9"/>
+    <x:sheet name="Teilnehmer" sheetId="4" ns1:id="R3237eebf8c9d4749"/>
+    <x:sheet name="CSV Export" sheetId="5" ns1:id="R3ca468bbf08e41dc"/>
+    <x:sheet name="Rangliste" sheetId="6" ns1:id="Rc0597fc3f95347a5"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0">'Gruppe A'!$A$1:$T$18</x:definedName>
     <x:definedName name="_xlnm.Print_Area" localSheetId="1">'Gruppe B'!$A$1:$T$21</x:definedName>
-    <x:definedName name="_xlnm.Print_Area" localSheetId="2">'Finalrunde'!$A$1:$T$34</x:definedName>
+    <x:definedName name="_xlnm.Print_Area" localSheetId="2">'Finalrunde'!$A$1:$T$51</x:definedName>
     <x:definedName name="_xlnm.Print_Area" localSheetId="3">'Teilnehmer'!$A$1:$P$12</x:definedName>
     <x:definedName name="_xlnm.Print_Area" localSheetId="4">'CSV Export'!$A$1:$M$23</x:definedName>
+    <x:definedName name="_xlnm.Print_Area" localSheetId="5">'Rangliste'!$A$1:$T$15</x:definedName>
   </x:definedNames>
 </x:workbook>
 </file>
@@ -48,12 +50,22 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2EFD9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFBFBFBF"/>
+      </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
@@ -158,7 +170,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="41">
+  <x:cellXfs count="74">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -278,6 +290,47 @@
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -3135,1357 +3188,2131 @@
   </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="11" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="11" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="30" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="11" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="11" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="11" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="11" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="30" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="11" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="11" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="11" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="11" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="35" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="11" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="11" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="11" hidden="0" customWidth="1"/>
-    <x:col min="18" max="18" width="11" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="11" hidden="0" customWidth="1"/>
-    <x:col min="20" max="20" width="11" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="12" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="12" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="12" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="3" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="3" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="3" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="3" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="12" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="12" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="12" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="12" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="12" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="12" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="12" hidden="0" customWidth="1"/>
     <x:col min="21" max="22" hidden="1" width="10" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="36" customHeight="1">
-      <x:c r="A1" s="7" t="str">
-        <x:v>2=gewonnen  1=unentschieden</x:v>
-      </x:c>
-      <x:c r="B1" s="2"/>
-      <x:c r="C1" s="2"/>
-      <x:c r="D1" s="5" t="str">
+      <x:c r="A1" s="1"/>
+      <x:c r="B1" s="1"/>
+      <x:c r="C1" s="1"/>
+      <x:c r="D1" s="43" t="str">
         <x:v>T16a – Finalrunde</x:v>
       </x:c>
-      <x:c r="E1" s="5"/>
-      <x:c r="F1" s="5"/>
-      <x:c r="G1" s="5"/>
-      <x:c r="H1" s="5"/>
-      <x:c r="I1" s="5"/>
-      <x:c r="J1" s="5"/>
-      <x:c r="K1" s="5"/>
-      <x:c r="L1" s="5"/>
-      <x:c r="M1" s="5"/>
-      <x:c r="N1" s="5"/>
-      <x:c r="O1" s="5"/>
-      <x:c r="P1" s="5"/>
-      <x:c r="Q1" s="2"/>
-      <x:c r="R1" s="2" t="str">
-        <x:v>Ausrichter:</x:v>
-      </x:c>
-      <x:c r="S1" s="2" t="str"/>
-      <x:c r="T1" s="2"/>
+      <x:c r="E1" s="43"/>
+      <x:c r="F1" s="43"/>
+      <x:c r="G1" s="43"/>
+      <x:c r="H1" s="43"/>
+      <x:c r="I1" s="43"/>
+      <x:c r="J1" s="43"/>
+      <x:c r="K1" s="43"/>
+      <x:c r="L1" s="43"/>
+      <x:c r="M1" s="43"/>
+      <x:c r="N1" s="43"/>
+      <x:c r="O1" s="43"/>
+      <x:c r="P1" s="43"/>
+      <x:c r="Q1" s="1"/>
+      <x:c r="R1" s="1"/>
+      <x:c r="S1" s="1"/>
+      <x:c r="T1" s="1"/>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
-      <x:c r="A2" s="7" t="str">
-        <x:v>0=verloren</x:v>
-      </x:c>
-      <x:c r="B2" s="2"/>
-      <x:c r="C2" s="2"/>
-      <x:c r="D2" s="2"/>
-      <x:c r="E2" s="2"/>
-      <x:c r="F2" s="2"/>
-      <x:c r="G2" s="2"/>
-      <x:c r="H2" s="2"/>
-      <x:c r="I2" s="2"/>
-      <x:c r="J2" s="2"/>
-      <x:c r="K2" s="2"/>
-      <x:c r="L2" s="2"/>
-      <x:c r="M2" s="2"/>
-      <x:c r="N2" s="2"/>
-      <x:c r="O2" s="2"/>
-      <x:c r="P2" s="2"/>
-      <x:c r="Q2" s="2"/>
-      <x:c r="R2" s="2" t="str">
+      <x:c r="A2" s="1"/>
+      <x:c r="B2" s="1"/>
+      <x:c r="C2" s="1"/>
+      <x:c r="D2" s="1"/>
+      <x:c r="E2" s="1"/>
+      <x:c r="F2" s="1"/>
+      <x:c r="G2" s="1"/>
+      <x:c r="H2" s="1"/>
+      <x:c r="I2" s="1"/>
+      <x:c r="J2" s="1"/>
+      <x:c r="K2" s="1"/>
+      <x:c r="L2" s="1"/>
+      <x:c r="M2" s="1"/>
+      <x:c r="N2" s="1"/>
+      <x:c r="O2" s="1"/>
+      <x:c r="P2" s="1"/>
+      <x:c r="Q2" s="1"/>
+      <x:c r="R2" s="1" t="str">
         <x:v>Datum:</x:v>
       </x:c>
-      <x:c r="S2" s="6"/>
-      <x:c r="T2" s="2"/>
+      <x:c r="S2" s="44"/>
+      <x:c r="T2" s="1"/>
     </x:row>
     <x:row r="3" ht="24" customHeight="1">
-      <x:c r="A3" s="2"/>
-      <x:c r="B3" s="2"/>
-      <x:c r="C3" s="2"/>
-      <x:c r="D3" s="2"/>
-      <x:c r="E3" s="2"/>
-      <x:c r="F3" s="2"/>
-      <x:c r="G3" s="2"/>
-      <x:c r="H3" s="2"/>
-      <x:c r="I3" s="2"/>
-      <x:c r="J3" s="2"/>
-      <x:c r="K3" s="2"/>
-      <x:c r="L3" s="2"/>
-      <x:c r="M3" s="2"/>
-      <x:c r="N3" s="2"/>
-      <x:c r="O3" s="2"/>
-      <x:c r="P3" s="2"/>
-      <x:c r="Q3" s="2"/>
-      <x:c r="R3" s="2"/>
-      <x:c r="S3" s="2"/>
-      <x:c r="T3" s="2"/>
+      <x:c r="A3" s="45" t="str">
+        <x:v>Halbfinale – Runde 6, Tisch 1: HF1; Tisch 2: HF2</x:v>
+      </x:c>
+      <x:c r="B3" s="1"/>
+      <x:c r="C3" s="1"/>
+      <x:c r="D3" s="1"/>
+      <x:c r="E3" s="1"/>
+      <x:c r="F3" s="1"/>
+      <x:c r="G3" s="1"/>
+      <x:c r="H3" s="1"/>
+      <x:c r="I3" s="1"/>
+      <x:c r="J3" s="1"/>
+      <x:c r="K3" s="1"/>
+      <x:c r="L3" s="1"/>
+      <x:c r="M3" s="1"/>
+      <x:c r="N3" s="1"/>
+      <x:c r="O3" s="1"/>
+      <x:c r="P3" s="1"/>
+      <x:c r="Q3" s="1"/>
+      <x:c r="R3" s="1"/>
+      <x:c r="S3" s="1"/>
+      <x:c r="T3" s="1"/>
     </x:row>
     <x:row r="4" ht="40" customHeight="1">
-      <x:c r="A4" s="9" t="str">
-        <x:v>Runde</x:v>
-      </x:c>
-      <x:c r="B4" s="9" t="str">
-        <x:v>Tisch</x:v>
-      </x:c>
-      <x:c r="C4" s="9" t="str">
-        <x:v>Spiel</x:v>
-      </x:c>
-      <x:c r="D4" s="9" t="str">
-        <x:v>Spieler 1</x:v>
-      </x:c>
-      <x:c r="E4" s="9" t="str">
-        <x:v>Bälle 1</x:v>
-      </x:c>
-      <x:c r="F4" s="9" t="str">
-        <x:v>Aufn. 1</x:v>
-      </x:c>
-      <x:c r="G4" s="9" t="str">
-        <x:v>HS 1</x:v>
-      </x:c>
-      <x:c r="H4" s="9" t="str">
-        <x:v>MP 1</x:v>
-      </x:c>
-      <x:c r="I4" s="9" t="str">
-        <x:v>Spieler 2</x:v>
-      </x:c>
-      <x:c r="J4" s="9" t="str">
-        <x:v>Bälle 2</x:v>
-      </x:c>
-      <x:c r="K4" s="9" t="str">
-        <x:v>Aufn. 2</x:v>
-      </x:c>
-      <x:c r="L4" s="9" t="str">
-        <x:v>HS 2</x:v>
-      </x:c>
-      <x:c r="M4" s="9" t="str">
-        <x:v>MP 2</x:v>
-      </x:c>
-      <x:c r="N4" s="9" t="str">
-        <x:v>Entscheidung</x:v>
-      </x:c>
-      <x:c r="O4" s="2"/>
-      <x:c r="P4" s="2"/>
-      <x:c r="Q4" s="2"/>
-      <x:c r="R4" s="2"/>
-      <x:c r="S4" s="2"/>
-      <x:c r="T4" s="2"/>
+      <x:c r="A4" s="46" t="str">
+        <x:v>Name</x:v>
+      </x:c>
+      <x:c r="B4" s="47" t="str">
+        <x:f>IF(U4="","",INDEX(Teilnehmer!$B$2:$B$10,MATCH(U4,Teilnehmer!$A$2:$A$10,0)))</x:f>
+      </x:c>
+      <x:c r="C4" s="46"/>
+      <x:c r="D4" s="47" t="str">
+        <x:f>IF(U5="","",INDEX(Teilnehmer!$B$2:$B$10,MATCH(U5,Teilnehmer!$A$2:$A$10,0)))</x:f>
+      </x:c>
+      <x:c r="E4" s="46"/>
+      <x:c r="F4" s="47" t="str">
+        <x:f>IF(U6="","",INDEX(Teilnehmer!$B$2:$B$10,MATCH(U6,Teilnehmer!$A$2:$A$10,0)))</x:f>
+      </x:c>
+      <x:c r="G4" s="46"/>
+      <x:c r="H4" s="47" t="str">
+        <x:f>IF(U7="","",INDEX(Teilnehmer!$B$2:$B$10,MATCH(U7,Teilnehmer!$A$2:$A$10,0)))</x:f>
+      </x:c>
+      <x:c r="I4" s="46"/>
+      <x:c r="J4" s="46"/>
+      <x:c r="K4" s="46"/>
+      <x:c r="L4" s="46"/>
+      <x:c r="M4" s="46"/>
+      <x:c r="N4" s="46" t="str">
+        <x:v>Partiepunkte</x:v>
+      </x:c>
+      <x:c r="O4" s="46" t="str">
+        <x:v>Bälle</x:v>
+      </x:c>
+      <x:c r="P4" s="46" t="str">
+        <x:v>Aufnahmen</x:v>
+      </x:c>
+      <x:c r="Q4" s="46" t="str">
+        <x:v>BED</x:v>
+      </x:c>
+      <x:c r="R4" s="46" t="str">
+        <x:v>DS</x:v>
+      </x:c>
+      <x:c r="S4" s="46" t="str">
+        <x:v>HS</x:v>
+      </x:c>
+      <x:c r="T4" s="46" t="str">
+        <x:v>Platz</x:v>
+      </x:c>
+      <x:c r="U4" t="str">
+        <x:f>IF(COUNTIF(Teilnehmer!$P$2:$P$10,"A1")=1,INDEX(Teilnehmer!$A$2:$A$10,MATCH("A1",Teilnehmer!$P$2:$P$10,0)),"")</x:f>
+      </x:c>
     </x:row>
     <x:row r="5" ht="24" customHeight="1">
-      <x:c r="A5" s="2" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B5" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="2" t="str">
-        <x:v>HF1</x:v>
-      </x:c>
-      <x:c r="D5" s="2" t="str">
-        <x:f>IF(U5="","",INDEX(Teilnehmer!$B$2:$B$10,MATCH(U5,Teilnehmer!$A$2:$A$10,0)))</x:f>
-      </x:c>
-      <x:c r="E5" s="3"/>
-      <x:c r="F5" s="3"/>
-      <x:c r="G5" s="3"/>
-      <x:c r="H5" s="3" t="str">
-        <x:f>IF(AND(ISNUMBER(E5),ISNUMBER(J5),U5&lt;&gt;"",V5&lt;&gt;""),IF(IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U5,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(V5,Teilnehmer!$A$2:$A$10,0))&gt;0),E5/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U5,Teilnehmer!$A$2:$A$10,0)),E5)&gt;IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U5,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(V5,Teilnehmer!$A$2:$A$10,0))&gt;0),J5/INDEX(Teilnehmer!$F$2:$F$10,MATCH(V5,Teilnehmer!$A$2:$A$10,0)),J5),2,IF(IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U5,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(V5,Teilnehmer!$A$2:$A$10,0))&gt;0),E5/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U5,Teilnehmer!$A$2:$A$10,0)),E5)=IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U5,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(V5,Teilnehmer!$A$2:$A$10,0))&gt;0),J5/INDEX(Teilnehmer!$F$2:$F$10,MATCH(V5,Teilnehmer!$A$2:$A$10,0)),J5),1,0)),"")</x:f>
-      </x:c>
-      <x:c r="I5" s="2" t="str">
-        <x:f>IF(V5="","",INDEX(Teilnehmer!$B$2:$B$10,MATCH(V5,Teilnehmer!$A$2:$A$10,0)))</x:f>
-      </x:c>
-      <x:c r="J5" s="3"/>
-      <x:c r="K5" s="3"/>
-      <x:c r="L5" s="3"/>
-      <x:c r="M5" s="3" t="str">
-        <x:f>IF(ISNUMBER(H5),2-H5,"")</x:f>
-      </x:c>
-      <x:c r="N5" s="2" t="str">
-        <x:v>MP bei Verlängerung 2/0 eintragen</x:v>
-      </x:c>
-      <x:c r="O5" s="2"/>
-      <x:c r="P5" s="2"/>
-      <x:c r="Q5" s="2"/>
-      <x:c r="R5" s="2"/>
-      <x:c r="S5" s="2"/>
-      <x:c r="T5" s="2"/>
+      <x:c r="A5" s="48" t="str">
+        <x:f>IF(B4="","",B4)</x:f>
+      </x:c>
+      <x:c r="B5" s="55" t="str">
+        <x:v>Bälle</x:v>
+      </x:c>
+      <x:c r="C5" s="56" t="str">
+        <x:v>Aufn.</x:v>
+      </x:c>
+      <x:c r="D5" s="61"/>
+      <x:c r="E5" s="62"/>
+      <x:c r="F5" s="55"/>
+      <x:c r="G5" s="56"/>
+      <x:c r="H5" s="55"/>
+      <x:c r="I5" s="56"/>
+      <x:c r="J5" s="1"/>
+      <x:c r="K5" s="1"/>
+      <x:c r="L5" s="1"/>
+      <x:c r="M5" s="1"/>
+      <x:c r="N5" s="66" t="str">
+        <x:f>IF(COUNT(D6)=0,"",SUM(D6))</x:f>
+      </x:c>
+      <x:c r="O5" s="66" t="str">
+        <x:f>IF(COUNT(D5)=0,"",SUM(D5))</x:f>
+      </x:c>
+      <x:c r="P5" s="66" t="str">
+        <x:f>IF(COUNT(E5)=0,"",SUM(E5))</x:f>
+      </x:c>
+      <x:c r="Q5" s="69" t="str">
+        <x:f>IF(COUNT(D6)=0,"",MAX(IF(D6=2,D7,0)))</x:f>
+      </x:c>
+      <x:c r="R5" s="69" t="str">
+        <x:f>IF(P5&gt;0,TRUNC(O5/P5,3),"")</x:f>
+      </x:c>
+      <x:c r="S5" s="66" t="str">
+        <x:f>IF(COUNT(E7)=0,"",MAX(E7))</x:f>
+      </x:c>
+      <x:c r="T5" s="66" t="str">
+        <x:f>IF(ISNUMBER(N5),IF(N5=2,1,IF(N5=0,2,"")),"")</x:f>
+      </x:c>
       <x:c r="U5" t="str">
-        <x:f>IF(COUNTIF(Teilnehmer!$P$2:$P$10,"A1")=1,INDEX(Teilnehmer!$A$2:$A$10,MATCH("A1",Teilnehmer!$P$2:$P$10,0)),"")</x:f>
-      </x:c>
-      <x:c r="V5" t="str">
         <x:f>IF(COUNTIF(Teilnehmer!$P$2:$P$10,"B2")=1,INDEX(Teilnehmer!$A$2:$A$10,MATCH("B2",Teilnehmer!$P$2:$P$10,0)),"")</x:f>
       </x:c>
+      <x:c r="V5"/>
     </x:row>
     <x:row r="6" ht="24" customHeight="1">
-      <x:c r="A6" s="2" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B6" s="2" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="2" t="str">
-        <x:v>HF2</x:v>
-      </x:c>
-      <x:c r="D6" s="2" t="str">
-        <x:f>IF(U6="","",INDEX(Teilnehmer!$B$2:$B$10,MATCH(U6,Teilnehmer!$A$2:$A$10,0)))</x:f>
-      </x:c>
-      <x:c r="E6" s="3"/>
-      <x:c r="F6" s="3"/>
-      <x:c r="G6" s="3"/>
-      <x:c r="H6" s="3" t="str">
-        <x:f>IF(AND(ISNUMBER(E6),ISNUMBER(J6),U6&lt;&gt;"",V6&lt;&gt;""),IF(IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U6,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(V6,Teilnehmer!$A$2:$A$10,0))&gt;0),E6/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U6,Teilnehmer!$A$2:$A$10,0)),E6)&gt;IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U6,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(V6,Teilnehmer!$A$2:$A$10,0))&gt;0),J6/INDEX(Teilnehmer!$F$2:$F$10,MATCH(V6,Teilnehmer!$A$2:$A$10,0)),J6),2,IF(IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U6,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(V6,Teilnehmer!$A$2:$A$10,0))&gt;0),E6/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U6,Teilnehmer!$A$2:$A$10,0)),E6)=IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U6,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(V6,Teilnehmer!$A$2:$A$10,0))&gt;0),J6/INDEX(Teilnehmer!$F$2:$F$10,MATCH(V6,Teilnehmer!$A$2:$A$10,0)),J6),1,0)),"")</x:f>
-      </x:c>
-      <x:c r="I6" s="2" t="str">
-        <x:f>IF(V6="","",INDEX(Teilnehmer!$B$2:$B$10,MATCH(V6,Teilnehmer!$A$2:$A$10,0)))</x:f>
-      </x:c>
-      <x:c r="J6" s="3"/>
-      <x:c r="K6" s="3"/>
-      <x:c r="L6" s="3"/>
-      <x:c r="M6" s="3" t="str">
-        <x:f>IF(ISNUMBER(H6),2-H6,"")</x:f>
-      </x:c>
-      <x:c r="N6" s="2" t="str">
-        <x:v>MP bei Verlängerung 2/0 eintragen</x:v>
-      </x:c>
-      <x:c r="O6" s="2"/>
-      <x:c r="P6" s="2"/>
-      <x:c r="Q6" s="2"/>
-      <x:c r="R6" s="2"/>
-      <x:c r="S6" s="2"/>
-      <x:c r="T6" s="2"/>
+      <x:c r="A6" s="1"/>
+      <x:c r="B6" s="57" t="str">
+        <x:v>Partiepunkte</x:v>
+      </x:c>
+      <x:c r="C6" s="58"/>
+      <x:c r="D6" s="64" t="str">
+        <x:f>IF(AND(ISNUMBER(D5),ISNUMBER(B8),U4&lt;&gt;"",U5&lt;&gt;""),IF(IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U4,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(U5,Teilnehmer!$A$2:$A$10,0))&gt;0),D5/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U4,Teilnehmer!$A$2:$A$10,0)),D5)&gt;IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U4,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(U5,Teilnehmer!$A$2:$A$10,0))&gt;0),B8/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U5,Teilnehmer!$A$2:$A$10,0)),B8),2,IF(IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U4,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(U5,Teilnehmer!$A$2:$A$10,0))&gt;0),D5/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U4,Teilnehmer!$A$2:$A$10,0)),D5)=IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U4,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(U5,Teilnehmer!$A$2:$A$10,0))&gt;0),B8/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U5,Teilnehmer!$A$2:$A$10,0)),B8),1,0)),"")</x:f>
+      </x:c>
+      <x:c r="E6" s="52"/>
+      <x:c r="F6" s="57"/>
+      <x:c r="G6" s="58"/>
+      <x:c r="H6" s="57"/>
+      <x:c r="I6" s="58"/>
+      <x:c r="J6" s="1"/>
+      <x:c r="K6" s="1"/>
+      <x:c r="L6" s="1"/>
+      <x:c r="M6" s="1"/>
+      <x:c r="N6" s="67"/>
+      <x:c r="O6" s="67"/>
+      <x:c r="P6" s="67"/>
+      <x:c r="Q6" s="70"/>
+      <x:c r="R6" s="70"/>
+      <x:c r="S6" s="67"/>
+      <x:c r="T6" s="67"/>
       <x:c r="U6" t="str">
         <x:f>IF(COUNTIF(Teilnehmer!$P$2:$P$10,"B1")=1,INDEX(Teilnehmer!$A$2:$A$10,MATCH("B1",Teilnehmer!$P$2:$P$10,0)),"")</x:f>
       </x:c>
-      <x:c r="V6" t="str">
+      <x:c r="V6"/>
+    </x:row>
+    <x:row r="7" ht="24" customHeight="1">
+      <x:c r="A7" s="1"/>
+      <x:c r="B7" s="59" t="str">
+        <x:v>DS</x:v>
+      </x:c>
+      <x:c r="C7" s="60" t="str">
+        <x:v>HS</x:v>
+      </x:c>
+      <x:c r="D7" s="65" t="str">
+        <x:f>IF(AND(ISNUMBER(D5),E5&gt;0),TRUNC(D5/E5,3),"")</x:f>
+      </x:c>
+      <x:c r="E7" s="63"/>
+      <x:c r="F7" s="59"/>
+      <x:c r="G7" s="60"/>
+      <x:c r="H7" s="59"/>
+      <x:c r="I7" s="60"/>
+      <x:c r="J7" s="1"/>
+      <x:c r="K7" s="1"/>
+      <x:c r="L7" s="1"/>
+      <x:c r="M7" s="1"/>
+      <x:c r="N7" s="68"/>
+      <x:c r="O7" s="68"/>
+      <x:c r="P7" s="68"/>
+      <x:c r="Q7" s="71"/>
+      <x:c r="R7" s="71"/>
+      <x:c r="S7" s="68"/>
+      <x:c r="T7" s="68"/>
+      <x:c r="U7" t="str">
         <x:f>IF(COUNTIF(Teilnehmer!$P$2:$P$10,"A2")=1,INDEX(Teilnehmer!$A$2:$A$10,MATCH("A2",Teilnehmer!$P$2:$P$10,0)),"")</x:f>
       </x:c>
-    </x:row>
-    <x:row r="7" ht="24" customHeight="1">
-      <x:c r="A7" s="2" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B7" s="2" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C7" s="2" t="str">
-        <x:v>Platz 5–6</x:v>
-      </x:c>
-      <x:c r="D7" s="2" t="str">
-        <x:f>IF(U7="","",INDEX(Teilnehmer!$B$2:$B$10,MATCH(U7,Teilnehmer!$A$2:$A$10,0)))</x:f>
-      </x:c>
-      <x:c r="E7" s="3"/>
-      <x:c r="F7" s="3"/>
-      <x:c r="G7" s="3"/>
-      <x:c r="H7" s="3" t="str">
-        <x:f>IF(AND(ISNUMBER(E7),ISNUMBER(J7),U7&lt;&gt;"",V7&lt;&gt;""),IF(IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U7,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(V7,Teilnehmer!$A$2:$A$10,0))&gt;0),E7/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U7,Teilnehmer!$A$2:$A$10,0)),E7)&gt;IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U7,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(V7,Teilnehmer!$A$2:$A$10,0))&gt;0),J7/INDEX(Teilnehmer!$F$2:$F$10,MATCH(V7,Teilnehmer!$A$2:$A$10,0)),J7),2,IF(IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U7,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(V7,Teilnehmer!$A$2:$A$10,0))&gt;0),E7/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U7,Teilnehmer!$A$2:$A$10,0)),E7)=IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U7,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(V7,Teilnehmer!$A$2:$A$10,0))&gt;0),J7/INDEX(Teilnehmer!$F$2:$F$10,MATCH(V7,Teilnehmer!$A$2:$A$10,0)),J7),1,0)),"")</x:f>
-      </x:c>
-      <x:c r="I7" s="2" t="str">
-        <x:f>IF(V7="","",INDEX(Teilnehmer!$B$2:$B$10,MATCH(V7,Teilnehmer!$A$2:$A$10,0)))</x:f>
-      </x:c>
-      <x:c r="J7" s="3"/>
-      <x:c r="K7" s="3"/>
-      <x:c r="L7" s="3"/>
-      <x:c r="M7" s="3" t="str">
-        <x:f>IF(ISNUMBER(H7),2-H7,"")</x:f>
-      </x:c>
-      <x:c r="N7" s="2" t="str">
-        <x:v>MP bei Verlängerung 2/0 eintragen</x:v>
-      </x:c>
-      <x:c r="O7" s="2"/>
-      <x:c r="P7" s="2"/>
-      <x:c r="Q7" s="2"/>
-      <x:c r="R7" s="2"/>
-      <x:c r="S7" s="2"/>
-      <x:c r="T7" s="2"/>
-      <x:c r="U7" t="str">
+      <x:c r="V7"/>
+    </x:row>
+    <x:row r="8" ht="24" customHeight="1">
+      <x:c r="A8" s="48" t="str">
+        <x:f>IF(D4="","",D4)</x:f>
+      </x:c>
+      <x:c r="B8" s="61"/>
+      <x:c r="C8" s="62" t="str">
+        <x:f>IF(ISNUMBER(E5),E5,"")</x:f>
+      </x:c>
+      <x:c r="D8" s="55" t="str">
+        <x:v>Bälle</x:v>
+      </x:c>
+      <x:c r="E8" s="56" t="str">
+        <x:v>Aufn.</x:v>
+      </x:c>
+      <x:c r="F8" s="55"/>
+      <x:c r="G8" s="56"/>
+      <x:c r="H8" s="55"/>
+      <x:c r="I8" s="56"/>
+      <x:c r="J8" s="1"/>
+      <x:c r="K8" s="1"/>
+      <x:c r="L8" s="1"/>
+      <x:c r="M8" s="1"/>
+      <x:c r="N8" s="66" t="str">
+        <x:f>IF(COUNT(B9)=0,"",SUM(B9))</x:f>
+      </x:c>
+      <x:c r="O8" s="66" t="str">
+        <x:f>IF(COUNT(B8)=0,"",SUM(B8))</x:f>
+      </x:c>
+      <x:c r="P8" s="66" t="str">
+        <x:f>IF(COUNT(C8)=0,"",SUM(C8))</x:f>
+      </x:c>
+      <x:c r="Q8" s="69" t="str">
+        <x:f>IF(COUNT(B9)=0,"",MAX(IF(B9=2,B10,0)))</x:f>
+      </x:c>
+      <x:c r="R8" s="69" t="str">
+        <x:f>IF(P8&gt;0,TRUNC(O8/P8,3),"")</x:f>
+      </x:c>
+      <x:c r="S8" s="66" t="str">
+        <x:f>IF(COUNT(C10)=0,"",MAX(C10))</x:f>
+      </x:c>
+      <x:c r="T8" s="66" t="str">
+        <x:f>IF(ISNUMBER(N8),IF(N8=2,1,IF(N8=0,2,"")),"")</x:f>
+      </x:c>
+      <x:c r="U8"/>
+      <x:c r="V8"/>
+    </x:row>
+    <x:row r="9" ht="24" customHeight="1">
+      <x:c r="A9" s="1"/>
+      <x:c r="B9" s="64" t="str">
+        <x:f>IF(AND(ISNUMBER(B8),ISNUMBER(D5),U5&lt;&gt;"",U4&lt;&gt;""),IF(IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U5,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(U4,Teilnehmer!$A$2:$A$10,0))&gt;0),B8/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U5,Teilnehmer!$A$2:$A$10,0)),B8)&gt;IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U5,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(U4,Teilnehmer!$A$2:$A$10,0))&gt;0),D5/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U4,Teilnehmer!$A$2:$A$10,0)),D5),2,IF(IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U5,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(U4,Teilnehmer!$A$2:$A$10,0))&gt;0),B8/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U5,Teilnehmer!$A$2:$A$10,0)),B8)=IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U5,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(U4,Teilnehmer!$A$2:$A$10,0))&gt;0),D5/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U4,Teilnehmer!$A$2:$A$10,0)),D5),1,0)),"")</x:f>
+      </x:c>
+      <x:c r="C9" s="52"/>
+      <x:c r="D9" s="57" t="str">
+        <x:v>Partiepunkte</x:v>
+      </x:c>
+      <x:c r="E9" s="58"/>
+      <x:c r="F9" s="57"/>
+      <x:c r="G9" s="58"/>
+      <x:c r="H9" s="57"/>
+      <x:c r="I9" s="58"/>
+      <x:c r="J9" s="1"/>
+      <x:c r="K9" s="1"/>
+      <x:c r="L9" s="1"/>
+      <x:c r="M9" s="1"/>
+      <x:c r="N9" s="67"/>
+      <x:c r="O9" s="67"/>
+      <x:c r="P9" s="67"/>
+      <x:c r="Q9" s="70"/>
+      <x:c r="R9" s="70"/>
+      <x:c r="S9" s="67"/>
+      <x:c r="T9" s="67"/>
+      <x:c r="U9"/>
+      <x:c r="V9"/>
+    </x:row>
+    <x:row r="10" ht="24" customHeight="1">
+      <x:c r="A10" s="1"/>
+      <x:c r="B10" s="65" t="str">
+        <x:f>IF(AND(ISNUMBER(B8),C8&gt;0),TRUNC(B8/C8,3),"")</x:f>
+      </x:c>
+      <x:c r="C10" s="63"/>
+      <x:c r="D10" s="59" t="str">
+        <x:v>DS</x:v>
+      </x:c>
+      <x:c r="E10" s="60" t="str">
+        <x:v>HS</x:v>
+      </x:c>
+      <x:c r="F10" s="59"/>
+      <x:c r="G10" s="60"/>
+      <x:c r="H10" s="59"/>
+      <x:c r="I10" s="60"/>
+      <x:c r="J10" s="1"/>
+      <x:c r="K10" s="1"/>
+      <x:c r="L10" s="1"/>
+      <x:c r="M10" s="1"/>
+      <x:c r="N10" s="68"/>
+      <x:c r="O10" s="68"/>
+      <x:c r="P10" s="68"/>
+      <x:c r="Q10" s="71"/>
+      <x:c r="R10" s="71"/>
+      <x:c r="S10" s="68"/>
+      <x:c r="T10" s="68"/>
+      <x:c r="U10"/>
+      <x:c r="V10"/>
+    </x:row>
+    <x:row r="11" ht="24" customHeight="1">
+      <x:c r="A11" s="48" t="str">
+        <x:f>IF(F4="","",F4)</x:f>
+      </x:c>
+      <x:c r="B11" s="55"/>
+      <x:c r="C11" s="56"/>
+      <x:c r="D11" s="55"/>
+      <x:c r="E11" s="56"/>
+      <x:c r="F11" s="55" t="str">
+        <x:v>Bälle</x:v>
+      </x:c>
+      <x:c r="G11" s="56" t="str">
+        <x:v>Aufn.</x:v>
+      </x:c>
+      <x:c r="H11" s="61"/>
+      <x:c r="I11" s="62"/>
+      <x:c r="J11" s="1"/>
+      <x:c r="K11" s="1"/>
+      <x:c r="L11" s="1"/>
+      <x:c r="M11" s="1"/>
+      <x:c r="N11" s="66" t="str">
+        <x:f>IF(COUNT(H12)=0,"",SUM(H12))</x:f>
+      </x:c>
+      <x:c r="O11" s="66" t="str">
+        <x:f>IF(COUNT(H11)=0,"",SUM(H11))</x:f>
+      </x:c>
+      <x:c r="P11" s="66" t="str">
+        <x:f>IF(COUNT(I11)=0,"",SUM(I11))</x:f>
+      </x:c>
+      <x:c r="Q11" s="69" t="str">
+        <x:f>IF(COUNT(H12)=0,"",MAX(IF(H12=2,H13,0)))</x:f>
+      </x:c>
+      <x:c r="R11" s="69" t="str">
+        <x:f>IF(P11&gt;0,TRUNC(O11/P11,3),"")</x:f>
+      </x:c>
+      <x:c r="S11" s="66" t="str">
+        <x:f>IF(COUNT(I13)=0,"",MAX(I13))</x:f>
+      </x:c>
+      <x:c r="T11" s="66" t="str">
+        <x:f>IF(ISNUMBER(N11),IF(N11=2,1,IF(N11=0,2,"")),"")</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="24" customHeight="1">
+      <x:c r="A12" s="1"/>
+      <x:c r="B12" s="57"/>
+      <x:c r="C12" s="58"/>
+      <x:c r="D12" s="57"/>
+      <x:c r="E12" s="58"/>
+      <x:c r="F12" s="57" t="str">
+        <x:v>Partiepunkte</x:v>
+      </x:c>
+      <x:c r="G12" s="58"/>
+      <x:c r="H12" s="64" t="str">
+        <x:f>IF(AND(ISNUMBER(H11),ISNUMBER(F14),U6&lt;&gt;"",U7&lt;&gt;""),IF(IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U6,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(U7,Teilnehmer!$A$2:$A$10,0))&gt;0),H11/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U6,Teilnehmer!$A$2:$A$10,0)),H11)&gt;IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U6,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(U7,Teilnehmer!$A$2:$A$10,0))&gt;0),F14/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U7,Teilnehmer!$A$2:$A$10,0)),F14),2,IF(IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U6,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(U7,Teilnehmer!$A$2:$A$10,0))&gt;0),H11/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U6,Teilnehmer!$A$2:$A$10,0)),H11)=IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U6,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(U7,Teilnehmer!$A$2:$A$10,0))&gt;0),F14/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U7,Teilnehmer!$A$2:$A$10,0)),F14),1,0)),"")</x:f>
+      </x:c>
+      <x:c r="I12" s="52"/>
+      <x:c r="J12" s="1"/>
+      <x:c r="K12" s="1"/>
+      <x:c r="L12" s="1"/>
+      <x:c r="M12" s="1"/>
+      <x:c r="N12" s="67"/>
+      <x:c r="O12" s="67"/>
+      <x:c r="P12" s="67"/>
+      <x:c r="Q12" s="70"/>
+      <x:c r="R12" s="70"/>
+      <x:c r="S12" s="67"/>
+      <x:c r="T12" s="67"/>
+    </x:row>
+    <x:row r="13" ht="24" customHeight="1">
+      <x:c r="A13" s="1"/>
+      <x:c r="B13" s="59"/>
+      <x:c r="C13" s="60"/>
+      <x:c r="D13" s="59"/>
+      <x:c r="E13" s="60"/>
+      <x:c r="F13" s="59" t="str">
+        <x:v>DS</x:v>
+      </x:c>
+      <x:c r="G13" s="60" t="str">
+        <x:v>HS</x:v>
+      </x:c>
+      <x:c r="H13" s="65" t="str">
+        <x:f>IF(AND(ISNUMBER(H11),I11&gt;0),TRUNC(H11/I11,3),"")</x:f>
+      </x:c>
+      <x:c r="I13" s="63"/>
+      <x:c r="J13" s="1"/>
+      <x:c r="K13" s="1"/>
+      <x:c r="L13" s="1"/>
+      <x:c r="M13" s="1"/>
+      <x:c r="N13" s="68"/>
+      <x:c r="O13" s="68"/>
+      <x:c r="P13" s="68"/>
+      <x:c r="Q13" s="71"/>
+      <x:c r="R13" s="71"/>
+      <x:c r="S13" s="68"/>
+      <x:c r="T13" s="68"/>
+    </x:row>
+    <x:row r="14" ht="24" customHeight="1">
+      <x:c r="A14" s="48" t="str">
+        <x:f>IF(H4="","",H4)</x:f>
+      </x:c>
+      <x:c r="B14" s="55"/>
+      <x:c r="C14" s="56"/>
+      <x:c r="D14" s="55"/>
+      <x:c r="E14" s="56"/>
+      <x:c r="F14" s="61"/>
+      <x:c r="G14" s="62" t="str">
+        <x:f>IF(ISNUMBER(I11),I11,"")</x:f>
+      </x:c>
+      <x:c r="H14" s="55" t="str">
+        <x:v>Bälle</x:v>
+      </x:c>
+      <x:c r="I14" s="56" t="str">
+        <x:v>Aufn.</x:v>
+      </x:c>
+      <x:c r="J14" s="1"/>
+      <x:c r="K14" s="1"/>
+      <x:c r="L14" s="1"/>
+      <x:c r="M14" s="1"/>
+      <x:c r="N14" s="66" t="str">
+        <x:f>IF(COUNT(F15)=0,"",SUM(F15))</x:f>
+      </x:c>
+      <x:c r="O14" s="66" t="str">
+        <x:f>IF(COUNT(F14)=0,"",SUM(F14))</x:f>
+      </x:c>
+      <x:c r="P14" s="66" t="str">
+        <x:f>IF(COUNT(G14)=0,"",SUM(G14))</x:f>
+      </x:c>
+      <x:c r="Q14" s="69" t="str">
+        <x:f>IF(COUNT(F15)=0,"",MAX(IF(F15=2,F16,0)))</x:f>
+      </x:c>
+      <x:c r="R14" s="69" t="str">
+        <x:f>IF(P14&gt;0,TRUNC(O14/P14,3),"")</x:f>
+      </x:c>
+      <x:c r="S14" s="66" t="str">
+        <x:f>IF(COUNT(G16)=0,"",MAX(G16))</x:f>
+      </x:c>
+      <x:c r="T14" s="66" t="str">
+        <x:f>IF(ISNUMBER(N14),IF(N14=2,1,IF(N14=0,2,"")),"")</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="24" customHeight="1">
+      <x:c r="A15" s="1"/>
+      <x:c r="B15" s="57"/>
+      <x:c r="C15" s="58"/>
+      <x:c r="D15" s="57"/>
+      <x:c r="E15" s="58"/>
+      <x:c r="F15" s="64" t="str">
+        <x:f>IF(AND(ISNUMBER(F14),ISNUMBER(H11),U7&lt;&gt;"",U6&lt;&gt;""),IF(IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U7,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(U6,Teilnehmer!$A$2:$A$10,0))&gt;0),F14/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U7,Teilnehmer!$A$2:$A$10,0)),F14)&gt;IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U7,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(U6,Teilnehmer!$A$2:$A$10,0))&gt;0),H11/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U6,Teilnehmer!$A$2:$A$10,0)),H11),2,IF(IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U7,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(U6,Teilnehmer!$A$2:$A$10,0))&gt;0),F14/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U7,Teilnehmer!$A$2:$A$10,0)),F14)=IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U7,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(U6,Teilnehmer!$A$2:$A$10,0))&gt;0),H11/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U6,Teilnehmer!$A$2:$A$10,0)),H11),1,0)),"")</x:f>
+      </x:c>
+      <x:c r="G15" s="52"/>
+      <x:c r="H15" s="57" t="str">
+        <x:v>Partiepunkte</x:v>
+      </x:c>
+      <x:c r="I15" s="58"/>
+      <x:c r="J15" s="1"/>
+      <x:c r="K15" s="1"/>
+      <x:c r="L15" s="1"/>
+      <x:c r="M15" s="1"/>
+      <x:c r="N15" s="67"/>
+      <x:c r="O15" s="67"/>
+      <x:c r="P15" s="67"/>
+      <x:c r="Q15" s="70"/>
+      <x:c r="R15" s="70"/>
+      <x:c r="S15" s="67"/>
+      <x:c r="T15" s="67"/>
+    </x:row>
+    <x:row r="16" ht="24" customHeight="1">
+      <x:c r="A16" s="1"/>
+      <x:c r="B16" s="59"/>
+      <x:c r="C16" s="60"/>
+      <x:c r="D16" s="59"/>
+      <x:c r="E16" s="60"/>
+      <x:c r="F16" s="65" t="str">
+        <x:f>IF(AND(ISNUMBER(F14),G14&gt;0),TRUNC(F14/G14,3),"")</x:f>
+      </x:c>
+      <x:c r="G16" s="63"/>
+      <x:c r="H16" s="59" t="str">
+        <x:v>DS</x:v>
+      </x:c>
+      <x:c r="I16" s="60" t="str">
+        <x:v>HS</x:v>
+      </x:c>
+      <x:c r="J16" s="1"/>
+      <x:c r="K16" s="1"/>
+      <x:c r="L16" s="1"/>
+      <x:c r="M16" s="1"/>
+      <x:c r="N16" s="68"/>
+      <x:c r="O16" s="68"/>
+      <x:c r="P16" s="68"/>
+      <x:c r="Q16" s="71"/>
+      <x:c r="R16" s="71"/>
+      <x:c r="S16" s="68"/>
+      <x:c r="T16" s="68"/>
+    </x:row>
+    <x:row r="17" ht="24" customHeight="1">
+      <x:c r="A17" s="1"/>
+      <x:c r="B17" s="1"/>
+      <x:c r="C17" s="1"/>
+      <x:c r="D17" s="1"/>
+      <x:c r="E17" s="1"/>
+      <x:c r="F17" s="1"/>
+      <x:c r="G17" s="1"/>
+      <x:c r="H17" s="1"/>
+      <x:c r="I17" s="1"/>
+      <x:c r="J17" s="1"/>
+      <x:c r="K17" s="1"/>
+      <x:c r="L17" s="1"/>
+      <x:c r="M17" s="1"/>
+      <x:c r="N17" s="1"/>
+      <x:c r="O17" s="1"/>
+      <x:c r="P17" s="1"/>
+      <x:c r="Q17" s="1"/>
+      <x:c r="R17" s="1"/>
+      <x:c r="S17" s="1"/>
+      <x:c r="T17" s="1"/>
+    </x:row>
+    <x:row r="18" ht="24" customHeight="1">
+      <x:c r="A18" s="1"/>
+      <x:c r="B18" s="1"/>
+      <x:c r="C18" s="1"/>
+      <x:c r="D18" s="1"/>
+      <x:c r="E18" s="1"/>
+      <x:c r="F18" s="1"/>
+      <x:c r="G18" s="1"/>
+      <x:c r="H18" s="1"/>
+      <x:c r="I18" s="1"/>
+      <x:c r="J18" s="1"/>
+      <x:c r="K18" s="1"/>
+      <x:c r="L18" s="1"/>
+      <x:c r="M18" s="1"/>
+      <x:c r="N18" s="1"/>
+      <x:c r="O18" s="1"/>
+      <x:c r="P18" s="1"/>
+      <x:c r="Q18" s="1"/>
+      <x:c r="R18" s="1"/>
+      <x:c r="S18" s="1"/>
+      <x:c r="T18" s="1"/>
+    </x:row>
+    <x:row r="19" ht="24" customHeight="1">
+      <x:c r="A19" s="45" t="str">
+        <x:v>Finale und Platz 3–4 – Runde 7, Tisch 1: Finale; Tisch 2: Platz 3–4</x:v>
+      </x:c>
+      <x:c r="B19" s="1"/>
+      <x:c r="C19" s="1"/>
+      <x:c r="D19" s="1"/>
+      <x:c r="E19" s="1"/>
+      <x:c r="F19" s="1"/>
+      <x:c r="G19" s="1"/>
+      <x:c r="H19" s="1"/>
+      <x:c r="I19" s="1"/>
+      <x:c r="J19" s="1"/>
+      <x:c r="K19" s="1"/>
+      <x:c r="L19" s="1"/>
+      <x:c r="M19" s="1"/>
+      <x:c r="N19" s="1"/>
+      <x:c r="O19" s="1"/>
+      <x:c r="P19" s="1"/>
+      <x:c r="Q19" s="1"/>
+      <x:c r="R19" s="1"/>
+      <x:c r="S19" s="1"/>
+      <x:c r="T19" s="1"/>
+    </x:row>
+    <x:row r="20" ht="40" customHeight="1">
+      <x:c r="A20" s="46" t="str">
+        <x:v>Name</x:v>
+      </x:c>
+      <x:c r="B20" s="47" t="str">
+        <x:f>IF(U20="","",INDEX(Teilnehmer!$B$2:$B$10,MATCH(U20,Teilnehmer!$A$2:$A$10,0)))</x:f>
+      </x:c>
+      <x:c r="C20" s="46"/>
+      <x:c r="D20" s="47" t="str">
+        <x:f>IF(U21="","",INDEX(Teilnehmer!$B$2:$B$10,MATCH(U21,Teilnehmer!$A$2:$A$10,0)))</x:f>
+      </x:c>
+      <x:c r="E20" s="46"/>
+      <x:c r="F20" s="47" t="str">
+        <x:f>IF(U22="","",INDEX(Teilnehmer!$B$2:$B$10,MATCH(U22,Teilnehmer!$A$2:$A$10,0)))</x:f>
+      </x:c>
+      <x:c r="G20" s="46"/>
+      <x:c r="H20" s="47" t="str">
+        <x:f>IF(U23="","",INDEX(Teilnehmer!$B$2:$B$10,MATCH(U23,Teilnehmer!$A$2:$A$10,0)))</x:f>
+      </x:c>
+      <x:c r="I20" s="46"/>
+      <x:c r="J20" s="46"/>
+      <x:c r="K20" s="46"/>
+      <x:c r="L20" s="46"/>
+      <x:c r="M20" s="46"/>
+      <x:c r="N20" s="46" t="str">
+        <x:v>Partiepunkte</x:v>
+      </x:c>
+      <x:c r="O20" s="46" t="str">
+        <x:v>Bälle</x:v>
+      </x:c>
+      <x:c r="P20" s="46" t="str">
+        <x:v>Aufnahmen</x:v>
+      </x:c>
+      <x:c r="Q20" s="46" t="str">
+        <x:v>BED</x:v>
+      </x:c>
+      <x:c r="R20" s="46" t="str">
+        <x:v>DS</x:v>
+      </x:c>
+      <x:c r="S20" s="46" t="str">
+        <x:v>HS</x:v>
+      </x:c>
+      <x:c r="T20" s="46" t="str">
+        <x:v>Platz</x:v>
+      </x:c>
+      <x:c r="U20" t="str">
+        <x:f>IF(AND(ISNUMBER(D6),ISNUMBER(B9),D6&lt;&gt;B9),IF(D6&gt;B9,U4,U5),"")</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="24" customHeight="1">
+      <x:c r="A21" s="48" t="str">
+        <x:f>IF(B20="","",B20)</x:f>
+      </x:c>
+      <x:c r="B21" s="55" t="str">
+        <x:v>Bälle</x:v>
+      </x:c>
+      <x:c r="C21" s="56" t="str">
+        <x:v>Aufn.</x:v>
+      </x:c>
+      <x:c r="D21" s="61"/>
+      <x:c r="E21" s="62"/>
+      <x:c r="F21" s="55"/>
+      <x:c r="G21" s="56"/>
+      <x:c r="H21" s="55"/>
+      <x:c r="I21" s="56"/>
+      <x:c r="J21" s="1"/>
+      <x:c r="K21" s="1"/>
+      <x:c r="L21" s="1"/>
+      <x:c r="M21" s="1"/>
+      <x:c r="N21" s="66" t="str">
+        <x:f>IF(COUNT(D22)=0,"",SUM(D22))</x:f>
+      </x:c>
+      <x:c r="O21" s="66" t="str">
+        <x:f>IF(COUNT(D21)=0,"",SUM(D21))</x:f>
+      </x:c>
+      <x:c r="P21" s="66" t="str">
+        <x:f>IF(COUNT(E21)=0,"",SUM(E21))</x:f>
+      </x:c>
+      <x:c r="Q21" s="69" t="str">
+        <x:f>IF(COUNT(D22)=0,"",MAX(IF(D22=2,D23,0)))</x:f>
+      </x:c>
+      <x:c r="R21" s="69" t="str">
+        <x:f>IF(P21&gt;0,TRUNC(O21/P21,3),"")</x:f>
+      </x:c>
+      <x:c r="S21" s="66" t="str">
+        <x:f>IF(COUNT(E23)=0,"",MAX(E23))</x:f>
+      </x:c>
+      <x:c r="T21" s="66" t="str">
+        <x:f>IF(ISNUMBER(N21),IF(N21=2,1,IF(N21=0,2,"")),"")</x:f>
+      </x:c>
+      <x:c r="U21" t="str">
+        <x:f>IF(AND(ISNUMBER(H12),ISNUMBER(F15),H12&lt;&gt;F15),IF(H12&gt;F15,U6,U7),"")</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="24" customHeight="1">
+      <x:c r="A22" s="1"/>
+      <x:c r="B22" s="57" t="str">
+        <x:v>Partiepunkte</x:v>
+      </x:c>
+      <x:c r="C22" s="58"/>
+      <x:c r="D22" s="64" t="str">
+        <x:f>IF(AND(ISNUMBER(D21),ISNUMBER(B24),U20&lt;&gt;"",U21&lt;&gt;""),IF(IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U20,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(U21,Teilnehmer!$A$2:$A$10,0))&gt;0),D21/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U20,Teilnehmer!$A$2:$A$10,0)),D21)&gt;IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U20,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(U21,Teilnehmer!$A$2:$A$10,0))&gt;0),B24/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U21,Teilnehmer!$A$2:$A$10,0)),B24),2,IF(IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U20,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(U21,Teilnehmer!$A$2:$A$10,0))&gt;0),D21/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U20,Teilnehmer!$A$2:$A$10,0)),D21)=IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U20,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(U21,Teilnehmer!$A$2:$A$10,0))&gt;0),B24/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U21,Teilnehmer!$A$2:$A$10,0)),B24),1,0)),"")</x:f>
+      </x:c>
+      <x:c r="E22" s="52"/>
+      <x:c r="F22" s="57"/>
+      <x:c r="G22" s="58"/>
+      <x:c r="H22" s="57"/>
+      <x:c r="I22" s="58"/>
+      <x:c r="J22" s="1"/>
+      <x:c r="K22" s="1"/>
+      <x:c r="L22" s="1"/>
+      <x:c r="M22" s="1"/>
+      <x:c r="N22" s="67"/>
+      <x:c r="O22" s="67"/>
+      <x:c r="P22" s="67"/>
+      <x:c r="Q22" s="70"/>
+      <x:c r="R22" s="70"/>
+      <x:c r="S22" s="67"/>
+      <x:c r="T22" s="67"/>
+      <x:c r="U22" t="str">
+        <x:f>IF(AND(ISNUMBER(D6),ISNUMBER(B9),D6&lt;&gt;B9),IF(D6&lt;B9,U4,U5),"")</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="24" customHeight="1">
+      <x:c r="A23" s="1"/>
+      <x:c r="B23" s="59" t="str">
+        <x:v>DS</x:v>
+      </x:c>
+      <x:c r="C23" s="60" t="str">
+        <x:v>HS</x:v>
+      </x:c>
+      <x:c r="D23" s="65" t="str">
+        <x:f>IF(AND(ISNUMBER(D21),E21&gt;0),TRUNC(D21/E21,3),"")</x:f>
+      </x:c>
+      <x:c r="E23" s="63"/>
+      <x:c r="F23" s="59"/>
+      <x:c r="G23" s="60"/>
+      <x:c r="H23" s="59"/>
+      <x:c r="I23" s="60"/>
+      <x:c r="J23" s="1"/>
+      <x:c r="K23" s="1"/>
+      <x:c r="L23" s="1"/>
+      <x:c r="M23" s="1"/>
+      <x:c r="N23" s="68"/>
+      <x:c r="O23" s="68"/>
+      <x:c r="P23" s="68"/>
+      <x:c r="Q23" s="71"/>
+      <x:c r="R23" s="71"/>
+      <x:c r="S23" s="68"/>
+      <x:c r="T23" s="68"/>
+      <x:c r="U23" t="str">
+        <x:f>IF(AND(ISNUMBER(H12),ISNUMBER(F15),H12&lt;&gt;F15),IF(H12&lt;F15,U6,U7),"")</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="24" customHeight="1">
+      <x:c r="A24" s="48" t="str">
+        <x:f>IF(D20="","",D20)</x:f>
+      </x:c>
+      <x:c r="B24" s="61"/>
+      <x:c r="C24" s="62" t="str">
+        <x:f>IF(ISNUMBER(E21),E21,"")</x:f>
+      </x:c>
+      <x:c r="D24" s="55" t="str">
+        <x:v>Bälle</x:v>
+      </x:c>
+      <x:c r="E24" s="56" t="str">
+        <x:v>Aufn.</x:v>
+      </x:c>
+      <x:c r="F24" s="55"/>
+      <x:c r="G24" s="56"/>
+      <x:c r="H24" s="55"/>
+      <x:c r="I24" s="56"/>
+      <x:c r="J24" s="1"/>
+      <x:c r="K24" s="1"/>
+      <x:c r="L24" s="1"/>
+      <x:c r="M24" s="1"/>
+      <x:c r="N24" s="66" t="str">
+        <x:f>IF(COUNT(B25)=0,"",SUM(B25))</x:f>
+      </x:c>
+      <x:c r="O24" s="66" t="str">
+        <x:f>IF(COUNT(B24)=0,"",SUM(B24))</x:f>
+      </x:c>
+      <x:c r="P24" s="66" t="str">
+        <x:f>IF(COUNT(C24)=0,"",SUM(C24))</x:f>
+      </x:c>
+      <x:c r="Q24" s="69" t="str">
+        <x:f>IF(COUNT(B25)=0,"",MAX(IF(B25=2,B26,0)))</x:f>
+      </x:c>
+      <x:c r="R24" s="69" t="str">
+        <x:f>IF(P24&gt;0,TRUNC(O24/P24,3),"")</x:f>
+      </x:c>
+      <x:c r="S24" s="66" t="str">
+        <x:f>IF(COUNT(C26)=0,"",MAX(C26))</x:f>
+      </x:c>
+      <x:c r="T24" s="66" t="str">
+        <x:f>IF(ISNUMBER(N24),IF(N24=2,1,IF(N24=0,2,"")),"")</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="24" customHeight="1">
+      <x:c r="A25" s="1"/>
+      <x:c r="B25" s="64" t="str">
+        <x:f>IF(AND(ISNUMBER(B24),ISNUMBER(D21),U21&lt;&gt;"",U20&lt;&gt;""),IF(IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U21,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(U20,Teilnehmer!$A$2:$A$10,0))&gt;0),B24/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U21,Teilnehmer!$A$2:$A$10,0)),B24)&gt;IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U21,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(U20,Teilnehmer!$A$2:$A$10,0))&gt;0),D21/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U20,Teilnehmer!$A$2:$A$10,0)),D21),2,IF(IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U21,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(U20,Teilnehmer!$A$2:$A$10,0))&gt;0),B24/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U21,Teilnehmer!$A$2:$A$10,0)),B24)=IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U21,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(U20,Teilnehmer!$A$2:$A$10,0))&gt;0),D21/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U20,Teilnehmer!$A$2:$A$10,0)),D21),1,0)),"")</x:f>
+      </x:c>
+      <x:c r="C25" s="52"/>
+      <x:c r="D25" s="57" t="str">
+        <x:v>Partiepunkte</x:v>
+      </x:c>
+      <x:c r="E25" s="58"/>
+      <x:c r="F25" s="57"/>
+      <x:c r="G25" s="58"/>
+      <x:c r="H25" s="57"/>
+      <x:c r="I25" s="58"/>
+      <x:c r="J25" s="1"/>
+      <x:c r="K25" s="1"/>
+      <x:c r="L25" s="1"/>
+      <x:c r="M25" s="1"/>
+      <x:c r="N25" s="67"/>
+      <x:c r="O25" s="67"/>
+      <x:c r="P25" s="67"/>
+      <x:c r="Q25" s="70"/>
+      <x:c r="R25" s="70"/>
+      <x:c r="S25" s="67"/>
+      <x:c r="T25" s="67"/>
+    </x:row>
+    <x:row r="26" ht="24" customHeight="1">
+      <x:c r="A26" s="1"/>
+      <x:c r="B26" s="65" t="str">
+        <x:f>IF(AND(ISNUMBER(B24),C24&gt;0),TRUNC(B24/C24,3),"")</x:f>
+      </x:c>
+      <x:c r="C26" s="63"/>
+      <x:c r="D26" s="59" t="str">
+        <x:v>DS</x:v>
+      </x:c>
+      <x:c r="E26" s="60" t="str">
+        <x:v>HS</x:v>
+      </x:c>
+      <x:c r="F26" s="59"/>
+      <x:c r="G26" s="60"/>
+      <x:c r="H26" s="59"/>
+      <x:c r="I26" s="60"/>
+      <x:c r="J26" s="1"/>
+      <x:c r="K26" s="1"/>
+      <x:c r="L26" s="1"/>
+      <x:c r="M26" s="1"/>
+      <x:c r="N26" s="68"/>
+      <x:c r="O26" s="68"/>
+      <x:c r="P26" s="68"/>
+      <x:c r="Q26" s="71"/>
+      <x:c r="R26" s="71"/>
+      <x:c r="S26" s="68"/>
+      <x:c r="T26" s="68"/>
+    </x:row>
+    <x:row r="27" ht="24" customHeight="1">
+      <x:c r="A27" s="48" t="str">
+        <x:f>IF(F20="","",F20)</x:f>
+      </x:c>
+      <x:c r="B27" s="55"/>
+      <x:c r="C27" s="56"/>
+      <x:c r="D27" s="55"/>
+      <x:c r="E27" s="56"/>
+      <x:c r="F27" s="55" t="str">
+        <x:v>Bälle</x:v>
+      </x:c>
+      <x:c r="G27" s="56" t="str">
+        <x:v>Aufn.</x:v>
+      </x:c>
+      <x:c r="H27" s="61"/>
+      <x:c r="I27" s="62"/>
+      <x:c r="J27" s="1"/>
+      <x:c r="K27" s="1"/>
+      <x:c r="L27" s="1"/>
+      <x:c r="M27" s="1"/>
+      <x:c r="N27" s="66" t="str">
+        <x:f>IF(COUNT(H28)=0,"",SUM(H28))</x:f>
+      </x:c>
+      <x:c r="O27" s="66" t="str">
+        <x:f>IF(COUNT(H27)=0,"",SUM(H27))</x:f>
+      </x:c>
+      <x:c r="P27" s="66" t="str">
+        <x:f>IF(COUNT(I27)=0,"",SUM(I27))</x:f>
+      </x:c>
+      <x:c r="Q27" s="69" t="str">
+        <x:f>IF(COUNT(H28)=0,"",MAX(IF(H28=2,H29,0)))</x:f>
+      </x:c>
+      <x:c r="R27" s="69" t="str">
+        <x:f>IF(P27&gt;0,TRUNC(O27/P27,3),"")</x:f>
+      </x:c>
+      <x:c r="S27" s="66" t="str">
+        <x:f>IF(COUNT(I29)=0,"",MAX(I29))</x:f>
+      </x:c>
+      <x:c r="T27" s="66" t="str">
+        <x:f>IF(ISNUMBER(N27),IF(N27=2,1,IF(N27=0,2,"")),"")</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="24" customHeight="1">
+      <x:c r="A28" s="1"/>
+      <x:c r="B28" s="57"/>
+      <x:c r="C28" s="58"/>
+      <x:c r="D28" s="57"/>
+      <x:c r="E28" s="58"/>
+      <x:c r="F28" s="57" t="str">
+        <x:v>Partiepunkte</x:v>
+      </x:c>
+      <x:c r="G28" s="58"/>
+      <x:c r="H28" s="64" t="str">
+        <x:f>IF(AND(ISNUMBER(H27),ISNUMBER(F30),U22&lt;&gt;"",U23&lt;&gt;""),IF(IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U22,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(U23,Teilnehmer!$A$2:$A$10,0))&gt;0),H27/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U22,Teilnehmer!$A$2:$A$10,0)),H27)&gt;IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U22,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(U23,Teilnehmer!$A$2:$A$10,0))&gt;0),F30/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U23,Teilnehmer!$A$2:$A$10,0)),F30),2,IF(IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U22,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(U23,Teilnehmer!$A$2:$A$10,0))&gt;0),H27/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U22,Teilnehmer!$A$2:$A$10,0)),H27)=IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U22,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(U23,Teilnehmer!$A$2:$A$10,0))&gt;0),F30/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U23,Teilnehmer!$A$2:$A$10,0)),F30),1,0)),"")</x:f>
+      </x:c>
+      <x:c r="I28" s="52"/>
+      <x:c r="J28" s="1"/>
+      <x:c r="K28" s="1"/>
+      <x:c r="L28" s="1"/>
+      <x:c r="M28" s="1"/>
+      <x:c r="N28" s="67"/>
+      <x:c r="O28" s="67"/>
+      <x:c r="P28" s="67"/>
+      <x:c r="Q28" s="70"/>
+      <x:c r="R28" s="70"/>
+      <x:c r="S28" s="67"/>
+      <x:c r="T28" s="67"/>
+    </x:row>
+    <x:row r="29" ht="24" customHeight="1">
+      <x:c r="A29" s="1"/>
+      <x:c r="B29" s="59"/>
+      <x:c r="C29" s="60"/>
+      <x:c r="D29" s="59"/>
+      <x:c r="E29" s="60"/>
+      <x:c r="F29" s="59" t="str">
+        <x:v>DS</x:v>
+      </x:c>
+      <x:c r="G29" s="60" t="str">
+        <x:v>HS</x:v>
+      </x:c>
+      <x:c r="H29" s="65" t="str">
+        <x:f>IF(AND(ISNUMBER(H27),I27&gt;0),TRUNC(H27/I27,3),"")</x:f>
+      </x:c>
+      <x:c r="I29" s="63"/>
+      <x:c r="J29" s="1"/>
+      <x:c r="K29" s="1"/>
+      <x:c r="L29" s="1"/>
+      <x:c r="M29" s="1"/>
+      <x:c r="N29" s="68"/>
+      <x:c r="O29" s="68"/>
+      <x:c r="P29" s="68"/>
+      <x:c r="Q29" s="71"/>
+      <x:c r="R29" s="71"/>
+      <x:c r="S29" s="68"/>
+      <x:c r="T29" s="68"/>
+    </x:row>
+    <x:row r="30" ht="24" customHeight="1">
+      <x:c r="A30" s="48" t="str">
+        <x:f>IF(H20="","",H20)</x:f>
+      </x:c>
+      <x:c r="B30" s="55"/>
+      <x:c r="C30" s="56"/>
+      <x:c r="D30" s="55"/>
+      <x:c r="E30" s="56"/>
+      <x:c r="F30" s="61"/>
+      <x:c r="G30" s="62" t="str">
+        <x:f>IF(ISNUMBER(I27),I27,"")</x:f>
+      </x:c>
+      <x:c r="H30" s="55" t="str">
+        <x:v>Bälle</x:v>
+      </x:c>
+      <x:c r="I30" s="56" t="str">
+        <x:v>Aufn.</x:v>
+      </x:c>
+      <x:c r="J30" s="1"/>
+      <x:c r="K30" s="1"/>
+      <x:c r="L30" s="1"/>
+      <x:c r="M30" s="1"/>
+      <x:c r="N30" s="66" t="str">
+        <x:f>IF(COUNT(F31)=0,"",SUM(F31))</x:f>
+      </x:c>
+      <x:c r="O30" s="66" t="str">
+        <x:f>IF(COUNT(F30)=0,"",SUM(F30))</x:f>
+      </x:c>
+      <x:c r="P30" s="66" t="str">
+        <x:f>IF(COUNT(G30)=0,"",SUM(G30))</x:f>
+      </x:c>
+      <x:c r="Q30" s="69" t="str">
+        <x:f>IF(COUNT(F31)=0,"",MAX(IF(F31=2,F32,0)))</x:f>
+      </x:c>
+      <x:c r="R30" s="69" t="str">
+        <x:f>IF(P30&gt;0,TRUNC(O30/P30,3),"")</x:f>
+      </x:c>
+      <x:c r="S30" s="66" t="str">
+        <x:f>IF(COUNT(G32)=0,"",MAX(G32))</x:f>
+      </x:c>
+      <x:c r="T30" s="66" t="str">
+        <x:f>IF(ISNUMBER(N30),IF(N30=2,1,IF(N30=0,2,"")),"")</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="24" customHeight="1">
+      <x:c r="A31" s="1"/>
+      <x:c r="B31" s="57"/>
+      <x:c r="C31" s="58"/>
+      <x:c r="D31" s="57"/>
+      <x:c r="E31" s="58"/>
+      <x:c r="F31" s="64" t="str">
+        <x:f>IF(AND(ISNUMBER(F30),ISNUMBER(H27),U23&lt;&gt;"",U22&lt;&gt;""),IF(IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U23,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(U22,Teilnehmer!$A$2:$A$10,0))&gt;0),F30/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U23,Teilnehmer!$A$2:$A$10,0)),F30)&gt;IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U23,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(U22,Teilnehmer!$A$2:$A$10,0))&gt;0),H27/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U22,Teilnehmer!$A$2:$A$10,0)),H27),2,IF(IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U23,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(U22,Teilnehmer!$A$2:$A$10,0))&gt;0),F30/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U23,Teilnehmer!$A$2:$A$10,0)),F30)=IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U23,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(U22,Teilnehmer!$A$2:$A$10,0))&gt;0),H27/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U22,Teilnehmer!$A$2:$A$10,0)),H27),1,0)),"")</x:f>
+      </x:c>
+      <x:c r="G31" s="52"/>
+      <x:c r="H31" s="57" t="str">
+        <x:v>Partiepunkte</x:v>
+      </x:c>
+      <x:c r="I31" s="58"/>
+      <x:c r="J31" s="1"/>
+      <x:c r="K31" s="1"/>
+      <x:c r="L31" s="1"/>
+      <x:c r="M31" s="1"/>
+      <x:c r="N31" s="67"/>
+      <x:c r="O31" s="67"/>
+      <x:c r="P31" s="67"/>
+      <x:c r="Q31" s="70"/>
+      <x:c r="R31" s="70"/>
+      <x:c r="S31" s="67"/>
+      <x:c r="T31" s="67"/>
+    </x:row>
+    <x:row r="32" ht="24" customHeight="1">
+      <x:c r="A32" s="1"/>
+      <x:c r="B32" s="59"/>
+      <x:c r="C32" s="60"/>
+      <x:c r="D32" s="59"/>
+      <x:c r="E32" s="60"/>
+      <x:c r="F32" s="65" t="str">
+        <x:f>IF(AND(ISNUMBER(F30),G30&gt;0),TRUNC(F30/G30,3),"")</x:f>
+      </x:c>
+      <x:c r="G32" s="63"/>
+      <x:c r="H32" s="59" t="str">
+        <x:v>DS</x:v>
+      </x:c>
+      <x:c r="I32" s="60" t="str">
+        <x:v>HS</x:v>
+      </x:c>
+      <x:c r="J32" s="1"/>
+      <x:c r="K32" s="1"/>
+      <x:c r="L32" s="1"/>
+      <x:c r="M32" s="1"/>
+      <x:c r="N32" s="68"/>
+      <x:c r="O32" s="68"/>
+      <x:c r="P32" s="68"/>
+      <x:c r="Q32" s="71"/>
+      <x:c r="R32" s="71"/>
+      <x:c r="S32" s="68"/>
+      <x:c r="T32" s="68"/>
+    </x:row>
+    <x:row r="33" ht="24" customHeight="1">
+      <x:c r="A33" s="1"/>
+      <x:c r="B33" s="1"/>
+      <x:c r="C33" s="1"/>
+      <x:c r="D33" s="1"/>
+      <x:c r="E33" s="1"/>
+      <x:c r="F33" s="1"/>
+      <x:c r="G33" s="1"/>
+      <x:c r="H33" s="1"/>
+      <x:c r="I33" s="1"/>
+      <x:c r="J33" s="1"/>
+      <x:c r="K33" s="1"/>
+      <x:c r="L33" s="1"/>
+      <x:c r="M33" s="1"/>
+      <x:c r="N33" s="1"/>
+      <x:c r="O33" s="1"/>
+      <x:c r="P33" s="1"/>
+      <x:c r="Q33" s="1"/>
+      <x:c r="R33" s="1"/>
+      <x:c r="S33" s="1"/>
+      <x:c r="T33" s="1"/>
+    </x:row>
+    <x:row r="34" ht="24" customHeight="1">
+      <x:c r="A34" s="1"/>
+      <x:c r="B34" s="1"/>
+      <x:c r="C34" s="1"/>
+      <x:c r="D34" s="1"/>
+      <x:c r="E34" s="1"/>
+      <x:c r="F34" s="1"/>
+      <x:c r="G34" s="1"/>
+      <x:c r="H34" s="1"/>
+      <x:c r="I34" s="1"/>
+      <x:c r="J34" s="1"/>
+      <x:c r="K34" s="1"/>
+      <x:c r="L34" s="1"/>
+      <x:c r="M34" s="1"/>
+      <x:c r="N34" s="1"/>
+      <x:c r="O34" s="1"/>
+      <x:c r="P34" s="1"/>
+      <x:c r="Q34" s="1"/>
+      <x:c r="R34" s="1"/>
+      <x:c r="S34" s="1"/>
+      <x:c r="T34" s="1"/>
+    </x:row>
+    <x:row r="35" ht="24" customHeight="1">
+      <x:c r="A35" s="45" t="str">
+        <x:v>Platzierungen – Runde 6, Tisch 3: Platz 5–6; Tisch 4: Platz 7–8</x:v>
+      </x:c>
+      <x:c r="B35" s="1"/>
+      <x:c r="C35" s="1"/>
+      <x:c r="D35" s="1"/>
+      <x:c r="E35" s="1"/>
+      <x:c r="F35" s="1"/>
+      <x:c r="G35" s="1"/>
+      <x:c r="H35" s="1"/>
+      <x:c r="I35" s="1"/>
+      <x:c r="J35" s="1"/>
+      <x:c r="K35" s="1"/>
+      <x:c r="L35" s="1"/>
+      <x:c r="M35" s="1"/>
+      <x:c r="N35" s="1"/>
+      <x:c r="O35" s="1"/>
+      <x:c r="P35" s="1"/>
+      <x:c r="Q35" s="1"/>
+      <x:c r="R35" s="1"/>
+      <x:c r="S35" s="1"/>
+      <x:c r="T35" s="1"/>
+    </x:row>
+    <x:row r="36" ht="40" customHeight="1">
+      <x:c r="A36" s="46" t="str">
+        <x:v>Name</x:v>
+      </x:c>
+      <x:c r="B36" s="47" t="str">
+        <x:f>IF(U36="","",INDEX(Teilnehmer!$B$2:$B$10,MATCH(U36,Teilnehmer!$A$2:$A$10,0)))</x:f>
+      </x:c>
+      <x:c r="C36" s="46"/>
+      <x:c r="D36" s="47" t="str">
+        <x:f>IF(U37="","",INDEX(Teilnehmer!$B$2:$B$10,MATCH(U37,Teilnehmer!$A$2:$A$10,0)))</x:f>
+      </x:c>
+      <x:c r="E36" s="46"/>
+      <x:c r="F36" s="47" t="str">
+        <x:f>IF(U38="","",INDEX(Teilnehmer!$B$2:$B$10,MATCH(U38,Teilnehmer!$A$2:$A$10,0)))</x:f>
+      </x:c>
+      <x:c r="G36" s="46"/>
+      <x:c r="H36" s="47" t="str">
+        <x:f>IF(U39="","",INDEX(Teilnehmer!$B$2:$B$10,MATCH(U39,Teilnehmer!$A$2:$A$10,0)))</x:f>
+      </x:c>
+      <x:c r="I36" s="46"/>
+      <x:c r="J36" s="46"/>
+      <x:c r="K36" s="46"/>
+      <x:c r="L36" s="46"/>
+      <x:c r="M36" s="46"/>
+      <x:c r="N36" s="46" t="str">
+        <x:v>Partiepunkte</x:v>
+      </x:c>
+      <x:c r="O36" s="46" t="str">
+        <x:v>Bälle</x:v>
+      </x:c>
+      <x:c r="P36" s="46" t="str">
+        <x:v>Aufnahmen</x:v>
+      </x:c>
+      <x:c r="Q36" s="46" t="str">
+        <x:v>BED</x:v>
+      </x:c>
+      <x:c r="R36" s="46" t="str">
+        <x:v>DS</x:v>
+      </x:c>
+      <x:c r="S36" s="46" t="str">
+        <x:v>HS</x:v>
+      </x:c>
+      <x:c r="T36" s="46" t="str">
+        <x:v>Platz</x:v>
+      </x:c>
+      <x:c r="U36" t="str">
         <x:f>IF(COUNTIF(Teilnehmer!$P$2:$P$10,"A3")=1,INDEX(Teilnehmer!$A$2:$A$10,MATCH("A3",Teilnehmer!$P$2:$P$10,0)),"")</x:f>
       </x:c>
-      <x:c r="V7" t="str">
+    </x:row>
+    <x:row r="37" ht="24" customHeight="1">
+      <x:c r="A37" s="48" t="str">
+        <x:f>IF(B36="","",B36)</x:f>
+      </x:c>
+      <x:c r="B37" s="55" t="str">
+        <x:v>Bälle</x:v>
+      </x:c>
+      <x:c r="C37" s="56" t="str">
+        <x:v>Aufn.</x:v>
+      </x:c>
+      <x:c r="D37" s="61"/>
+      <x:c r="E37" s="62"/>
+      <x:c r="F37" s="55"/>
+      <x:c r="G37" s="56"/>
+      <x:c r="H37" s="55"/>
+      <x:c r="I37" s="56"/>
+      <x:c r="J37" s="1"/>
+      <x:c r="K37" s="1"/>
+      <x:c r="L37" s="1"/>
+      <x:c r="M37" s="1"/>
+      <x:c r="N37" s="66" t="str">
+        <x:f>IF(COUNT(D38)=0,"",SUM(D38))</x:f>
+      </x:c>
+      <x:c r="O37" s="66" t="str">
+        <x:f>IF(COUNT(D37)=0,"",SUM(D37))</x:f>
+      </x:c>
+      <x:c r="P37" s="66" t="str">
+        <x:f>IF(COUNT(E37)=0,"",SUM(E37))</x:f>
+      </x:c>
+      <x:c r="Q37" s="69" t="str">
+        <x:f>IF(COUNT(D38)=0,"",MAX(IF(D38=2,D39,0)))</x:f>
+      </x:c>
+      <x:c r="R37" s="69" t="str">
+        <x:f>IF(P37&gt;0,TRUNC(O37/P37,3),"")</x:f>
+      </x:c>
+      <x:c r="S37" s="66" t="str">
+        <x:f>IF(COUNT(E39)=0,"",MAX(E39))</x:f>
+      </x:c>
+      <x:c r="T37" s="66" t="str">
+        <x:f>IF(ISNUMBER(N37),IF(N37=2,1,IF(N37=0,2,"")),"")</x:f>
+      </x:c>
+      <x:c r="U37" t="str">
         <x:f>IF(COUNTIF(Teilnehmer!$P$2:$P$10,"B3")=1,INDEX(Teilnehmer!$A$2:$A$10,MATCH("B3",Teilnehmer!$P$2:$P$10,0)),"")</x:f>
       </x:c>
     </x:row>
-    <x:row r="8" ht="24" customHeight="1">
-      <x:c r="A8" s="2" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B8" s="2" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C8" s="2" t="str">
-        <x:v>Platz 7–8</x:v>
-      </x:c>
-      <x:c r="D8" s="2" t="str">
-        <x:f>IF(U8="","",INDEX(Teilnehmer!$B$2:$B$10,MATCH(U8,Teilnehmer!$A$2:$A$10,0)))</x:f>
-      </x:c>
-      <x:c r="E8" s="3"/>
-      <x:c r="F8" s="3"/>
-      <x:c r="G8" s="3"/>
-      <x:c r="H8" s="3" t="str">
-        <x:f>IF(AND(ISNUMBER(E8),ISNUMBER(J8),U8&lt;&gt;"",V8&lt;&gt;""),IF(IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U8,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(V8,Teilnehmer!$A$2:$A$10,0))&gt;0),E8/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U8,Teilnehmer!$A$2:$A$10,0)),E8)&gt;IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U8,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(V8,Teilnehmer!$A$2:$A$10,0))&gt;0),J8/INDEX(Teilnehmer!$F$2:$F$10,MATCH(V8,Teilnehmer!$A$2:$A$10,0)),J8),2,IF(IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U8,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(V8,Teilnehmer!$A$2:$A$10,0))&gt;0),E8/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U8,Teilnehmer!$A$2:$A$10,0)),E8)=IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U8,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(V8,Teilnehmer!$A$2:$A$10,0))&gt;0),J8/INDEX(Teilnehmer!$F$2:$F$10,MATCH(V8,Teilnehmer!$A$2:$A$10,0)),J8),1,0)),"")</x:f>
-      </x:c>
-      <x:c r="I8" s="2" t="str">
-        <x:f>IF(V8="","",INDEX(Teilnehmer!$B$2:$B$10,MATCH(V8,Teilnehmer!$A$2:$A$10,0)))</x:f>
-      </x:c>
-      <x:c r="J8" s="3"/>
-      <x:c r="K8" s="3"/>
-      <x:c r="L8" s="3"/>
-      <x:c r="M8" s="3" t="str">
-        <x:f>IF(ISNUMBER(H8),2-H8,"")</x:f>
-      </x:c>
-      <x:c r="N8" s="2" t="str">
-        <x:v>MP bei Verlängerung 2/0 eintragen</x:v>
-      </x:c>
-      <x:c r="O8" s="2"/>
-      <x:c r="P8" s="2"/>
-      <x:c r="Q8" s="2"/>
-      <x:c r="R8" s="2"/>
-      <x:c r="S8" s="2"/>
-      <x:c r="T8" s="2"/>
-      <x:c r="U8" t="str">
+    <x:row r="38" ht="24" customHeight="1">
+      <x:c r="A38" s="1"/>
+      <x:c r="B38" s="57" t="str">
+        <x:v>Partiepunkte</x:v>
+      </x:c>
+      <x:c r="C38" s="58"/>
+      <x:c r="D38" s="64" t="str">
+        <x:f>IF(AND(ISNUMBER(D37),ISNUMBER(B40),U36&lt;&gt;"",U37&lt;&gt;""),IF(IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U36,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(U37,Teilnehmer!$A$2:$A$10,0))&gt;0),D37/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U36,Teilnehmer!$A$2:$A$10,0)),D37)&gt;IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U36,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(U37,Teilnehmer!$A$2:$A$10,0))&gt;0),B40/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U37,Teilnehmer!$A$2:$A$10,0)),B40),2,IF(IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U36,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(U37,Teilnehmer!$A$2:$A$10,0))&gt;0),D37/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U36,Teilnehmer!$A$2:$A$10,0)),D37)=IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U36,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(U37,Teilnehmer!$A$2:$A$10,0))&gt;0),B40/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U37,Teilnehmer!$A$2:$A$10,0)),B40),1,0)),"")</x:f>
+      </x:c>
+      <x:c r="E38" s="52"/>
+      <x:c r="F38" s="57"/>
+      <x:c r="G38" s="58"/>
+      <x:c r="H38" s="57"/>
+      <x:c r="I38" s="58"/>
+      <x:c r="J38" s="1"/>
+      <x:c r="K38" s="1"/>
+      <x:c r="L38" s="1"/>
+      <x:c r="M38" s="1"/>
+      <x:c r="N38" s="67"/>
+      <x:c r="O38" s="67"/>
+      <x:c r="P38" s="67"/>
+      <x:c r="Q38" s="70"/>
+      <x:c r="R38" s="70"/>
+      <x:c r="S38" s="67"/>
+      <x:c r="T38" s="67"/>
+      <x:c r="U38" t="str">
         <x:f>IF(COUNTIF(Teilnehmer!$P$2:$P$10,"A4")=1,INDEX(Teilnehmer!$A$2:$A$10,MATCH("A4",Teilnehmer!$P$2:$P$10,0)),"")</x:f>
       </x:c>
-      <x:c r="V8" t="str">
+    </x:row>
+    <x:row r="39" ht="24" customHeight="1">
+      <x:c r="A39" s="1"/>
+      <x:c r="B39" s="59" t="str">
+        <x:v>DS</x:v>
+      </x:c>
+      <x:c r="C39" s="60" t="str">
+        <x:v>HS</x:v>
+      </x:c>
+      <x:c r="D39" s="65" t="str">
+        <x:f>IF(AND(ISNUMBER(D37),E37&gt;0),TRUNC(D37/E37,3),"")</x:f>
+      </x:c>
+      <x:c r="E39" s="63"/>
+      <x:c r="F39" s="59"/>
+      <x:c r="G39" s="60"/>
+      <x:c r="H39" s="59"/>
+      <x:c r="I39" s="60"/>
+      <x:c r="J39" s="1"/>
+      <x:c r="K39" s="1"/>
+      <x:c r="L39" s="1"/>
+      <x:c r="M39" s="1"/>
+      <x:c r="N39" s="68"/>
+      <x:c r="O39" s="68"/>
+      <x:c r="P39" s="68"/>
+      <x:c r="Q39" s="71"/>
+      <x:c r="R39" s="71"/>
+      <x:c r="S39" s="68"/>
+      <x:c r="T39" s="68"/>
+      <x:c r="U39" t="str">
         <x:f>IF(COUNTIF(Teilnehmer!$P$2:$P$10,"B4")=1,INDEX(Teilnehmer!$A$2:$A$10,MATCH("B4",Teilnehmer!$P$2:$P$10,0)),"")</x:f>
       </x:c>
     </x:row>
-    <x:row r="9" ht="24" customHeight="1">
-      <x:c r="A9" s="2" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B9" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="2" t="str">
-        <x:v>Finale</x:v>
-      </x:c>
-      <x:c r="D9" s="2" t="str">
-        <x:f>IF(U9="","",INDEX(Teilnehmer!$B$2:$B$10,MATCH(U9,Teilnehmer!$A$2:$A$10,0)))</x:f>
-      </x:c>
-      <x:c r="E9" s="3"/>
-      <x:c r="F9" s="3"/>
-      <x:c r="G9" s="3"/>
-      <x:c r="H9" s="3" t="str">
-        <x:f>IF(AND(ISNUMBER(E9),ISNUMBER(J9),U9&lt;&gt;"",V9&lt;&gt;""),IF(IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U9,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(V9,Teilnehmer!$A$2:$A$10,0))&gt;0),E9/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U9,Teilnehmer!$A$2:$A$10,0)),E9)&gt;IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U9,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(V9,Teilnehmer!$A$2:$A$10,0))&gt;0),J9/INDEX(Teilnehmer!$F$2:$F$10,MATCH(V9,Teilnehmer!$A$2:$A$10,0)),J9),2,IF(IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U9,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(V9,Teilnehmer!$A$2:$A$10,0))&gt;0),E9/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U9,Teilnehmer!$A$2:$A$10,0)),E9)=IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U9,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(V9,Teilnehmer!$A$2:$A$10,0))&gt;0),J9/INDEX(Teilnehmer!$F$2:$F$10,MATCH(V9,Teilnehmer!$A$2:$A$10,0)),J9),1,0)),"")</x:f>
-      </x:c>
-      <x:c r="I9" s="2" t="str">
-        <x:f>IF(V9="","",INDEX(Teilnehmer!$B$2:$B$10,MATCH(V9,Teilnehmer!$A$2:$A$10,0)))</x:f>
-      </x:c>
-      <x:c r="J9" s="3"/>
-      <x:c r="K9" s="3"/>
-      <x:c r="L9" s="3"/>
-      <x:c r="M9" s="3" t="str">
-        <x:f>IF(ISNUMBER(H9),2-H9,"")</x:f>
-      </x:c>
-      <x:c r="N9" s="2" t="str">
-        <x:v>MP bei Verlängerung 2/0 eintragen</x:v>
-      </x:c>
-      <x:c r="O9" s="2"/>
-      <x:c r="P9" s="2"/>
-      <x:c r="Q9" s="2"/>
-      <x:c r="R9" s="2"/>
-      <x:c r="S9" s="2"/>
-      <x:c r="T9" s="2"/>
-      <x:c r="U9" t="str">
-        <x:f>IF(AND(ISNUMBER(H5),ISNUMBER(M5),H5&lt;&gt;M5),IF(H5&gt;M5,U5,V5),"")</x:f>
-      </x:c>
-      <x:c r="V9" t="str">
-        <x:f>IF(AND(ISNUMBER(H6),ISNUMBER(M6),H6&lt;&gt;M6),IF(H6&gt;M6,U6,V6),"")</x:f>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="24" customHeight="1">
-      <x:c r="A10" s="2" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B10" s="2" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C10" s="2" t="str">
-        <x:v>Platz 3–4</x:v>
-      </x:c>
-      <x:c r="D10" s="2" t="str">
-        <x:f>IF(U10="","",INDEX(Teilnehmer!$B$2:$B$10,MATCH(U10,Teilnehmer!$A$2:$A$10,0)))</x:f>
-      </x:c>
-      <x:c r="E10" s="3"/>
-      <x:c r="F10" s="3"/>
-      <x:c r="G10" s="3"/>
-      <x:c r="H10" s="3" t="str">
-        <x:f>IF(AND(ISNUMBER(E10),ISNUMBER(J10),U10&lt;&gt;"",V10&lt;&gt;""),IF(IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U10,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(V10,Teilnehmer!$A$2:$A$10,0))&gt;0),E10/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U10,Teilnehmer!$A$2:$A$10,0)),E10)&gt;IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U10,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(V10,Teilnehmer!$A$2:$A$10,0))&gt;0),J10/INDEX(Teilnehmer!$F$2:$F$10,MATCH(V10,Teilnehmer!$A$2:$A$10,0)),J10),2,IF(IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U10,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(V10,Teilnehmer!$A$2:$A$10,0))&gt;0),E10/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U10,Teilnehmer!$A$2:$A$10,0)),E10)=IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U10,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(V10,Teilnehmer!$A$2:$A$10,0))&gt;0),J10/INDEX(Teilnehmer!$F$2:$F$10,MATCH(V10,Teilnehmer!$A$2:$A$10,0)),J10),1,0)),"")</x:f>
-      </x:c>
-      <x:c r="I10" s="2" t="str">
-        <x:f>IF(V10="","",INDEX(Teilnehmer!$B$2:$B$10,MATCH(V10,Teilnehmer!$A$2:$A$10,0)))</x:f>
-      </x:c>
-      <x:c r="J10" s="3"/>
-      <x:c r="K10" s="3"/>
-      <x:c r="L10" s="3"/>
-      <x:c r="M10" s="3" t="str">
-        <x:f>IF(ISNUMBER(H10),2-H10,"")</x:f>
-      </x:c>
-      <x:c r="N10" s="2" t="str">
-        <x:v>MP bei Verlängerung 2/0 eintragen</x:v>
-      </x:c>
-      <x:c r="O10" s="2"/>
-      <x:c r="P10" s="2"/>
-      <x:c r="Q10" s="2"/>
-      <x:c r="R10" s="2"/>
-      <x:c r="S10" s="2"/>
-      <x:c r="T10" s="2"/>
-      <x:c r="U10" t="str">
-        <x:f>IF(AND(ISNUMBER(H5),ISNUMBER(M5),H5&lt;&gt;M5),IF(H5&lt;M5,U5,V5),"")</x:f>
-      </x:c>
-      <x:c r="V10" t="str">
-        <x:f>IF(AND(ISNUMBER(H6),ISNUMBER(M6),H6&lt;&gt;M6),IF(H6&lt;M6,U6,V6),"")</x:f>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="24" customHeight="1">
-      <x:c r="A11" s="2"/>
-      <x:c r="B11" s="2"/>
-      <x:c r="C11" s="2"/>
-      <x:c r="D11" s="2"/>
-      <x:c r="E11" s="2"/>
-      <x:c r="F11" s="2"/>
-      <x:c r="G11" s="2"/>
-      <x:c r="H11" s="2"/>
-      <x:c r="I11" s="2"/>
-      <x:c r="J11" s="2"/>
-      <x:c r="K11" s="2"/>
-      <x:c r="L11" s="2"/>
-      <x:c r="M11" s="2"/>
-      <x:c r="N11" s="2"/>
-      <x:c r="O11" s="2"/>
-      <x:c r="P11" s="2"/>
-      <x:c r="Q11" s="2"/>
-      <x:c r="R11" s="2"/>
-      <x:c r="S11" s="2"/>
-      <x:c r="T11" s="2"/>
-    </x:row>
-    <x:row r="12" ht="24" customHeight="1">
-      <x:c r="A12" s="2"/>
-      <x:c r="B12" s="2"/>
-      <x:c r="C12" s="2"/>
-      <x:c r="D12" s="2"/>
-      <x:c r="E12" s="2"/>
-      <x:c r="F12" s="2"/>
-      <x:c r="G12" s="2"/>
-      <x:c r="H12" s="2"/>
-      <x:c r="I12" s="2"/>
-      <x:c r="J12" s="2"/>
-      <x:c r="K12" s="2"/>
-      <x:c r="L12" s="2"/>
-      <x:c r="M12" s="2"/>
-      <x:c r="N12" s="2"/>
-      <x:c r="O12" s="2"/>
-      <x:c r="P12" s="2"/>
-      <x:c r="Q12" s="2"/>
-      <x:c r="R12" s="2"/>
-      <x:c r="S12" s="2"/>
-      <x:c r="T12" s="2"/>
-    </x:row>
-    <x:row r="13" ht="24" customHeight="1">
-      <x:c r="A13" s="3" t="str">
-        <x:v>Platz</x:v>
-      </x:c>
-      <x:c r="B13" s="3" t="str">
-        <x:v>Spieler</x:v>
-      </x:c>
-      <x:c r="C13" s="3" t="str">
-        <x:v>Setzplatz</x:v>
-      </x:c>
-      <x:c r="D13" s="3" t="str">
-        <x:v>Ermittelt aus</x:v>
-      </x:c>
-      <x:c r="E13" s="2"/>
-      <x:c r="F13" s="2"/>
-      <x:c r="G13" s="2"/>
-      <x:c r="H13" s="2"/>
-      <x:c r="I13" s="2"/>
-      <x:c r="J13" s="2"/>
-      <x:c r="K13" s="2"/>
-      <x:c r="L13" s="2"/>
-      <x:c r="M13" s="2"/>
-      <x:c r="N13" s="2"/>
-      <x:c r="O13" s="2"/>
-      <x:c r="P13" s="2"/>
-      <x:c r="Q13" s="2"/>
-      <x:c r="R13" s="2"/>
-      <x:c r="S13" s="2"/>
-      <x:c r="T13" s="2"/>
-    </x:row>
-    <x:row r="14" ht="24" customHeight="1">
-      <x:c r="A14" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B14" s="2" t="str">
-        <x:f>IF(C14="","",INDEX(Teilnehmer!$B$2:$B$10,MATCH(C14,Teilnehmer!$A$2:$A$10,0)))</x:f>
-      </x:c>
-      <x:c r="C14" s="2" t="str">
-        <x:f>IF(AND(ISNUMBER(H9),ISNUMBER(M9),H9&lt;&gt;M9),IF(H9&gt;M9,U9,V9),"")</x:f>
-      </x:c>
-      <x:c r="D14" s="2" t="str">
-        <x:v>Platzierungsspiel</x:v>
-      </x:c>
-      <x:c r="E14" s="2"/>
-      <x:c r="F14" s="2"/>
-      <x:c r="G14" s="2"/>
-      <x:c r="H14" s="2"/>
-      <x:c r="I14" s="2"/>
-      <x:c r="J14" s="2"/>
-      <x:c r="K14" s="2"/>
-      <x:c r="L14" s="2"/>
-      <x:c r="M14" s="2"/>
-      <x:c r="N14" s="2"/>
-      <x:c r="O14" s="2"/>
-      <x:c r="P14" s="2"/>
-      <x:c r="Q14" s="2"/>
-      <x:c r="R14" s="2"/>
-      <x:c r="S14" s="2"/>
-      <x:c r="T14" s="2"/>
-    </x:row>
-    <x:row r="15" ht="24" customHeight="1">
-      <x:c r="A15" s="2" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B15" s="2" t="str">
-        <x:f>IF(C15="","",INDEX(Teilnehmer!$B$2:$B$10,MATCH(C15,Teilnehmer!$A$2:$A$10,0)))</x:f>
-      </x:c>
-      <x:c r="C15" s="2" t="str">
-        <x:f>IF(AND(ISNUMBER(H9),ISNUMBER(M9),H9&lt;&gt;M9),IF(H9&lt;M9,U9,V9),"")</x:f>
-      </x:c>
-      <x:c r="D15" s="2" t="str">
-        <x:v>Platzierungsspiel</x:v>
-      </x:c>
-      <x:c r="E15" s="2"/>
-      <x:c r="F15" s="2"/>
-      <x:c r="G15" s="2"/>
-      <x:c r="H15" s="2"/>
-      <x:c r="I15" s="2"/>
-      <x:c r="J15" s="2"/>
-      <x:c r="K15" s="2"/>
-      <x:c r="L15" s="2"/>
-      <x:c r="M15" s="2"/>
-      <x:c r="N15" s="2"/>
-      <x:c r="O15" s="2"/>
-      <x:c r="P15" s="2"/>
-      <x:c r="Q15" s="2"/>
-      <x:c r="R15" s="2"/>
-      <x:c r="S15" s="2"/>
-      <x:c r="T15" s="2"/>
-    </x:row>
-    <x:row r="16" ht="24" customHeight="1">
-      <x:c r="A16" s="2" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B16" s="2" t="str">
-        <x:f>IF(C16="","",INDEX(Teilnehmer!$B$2:$B$10,MATCH(C16,Teilnehmer!$A$2:$A$10,0)))</x:f>
-      </x:c>
-      <x:c r="C16" s="2" t="str">
-        <x:f>IF(AND(ISNUMBER(H10),ISNUMBER(M10),H10&lt;&gt;M10),IF(H10&gt;M10,U10,V10),"")</x:f>
-      </x:c>
-      <x:c r="D16" s="2" t="str">
-        <x:v>Platzierungsspiel</x:v>
-      </x:c>
-      <x:c r="E16" s="2"/>
-      <x:c r="F16" s="2"/>
-      <x:c r="G16" s="2"/>
-      <x:c r="H16" s="2"/>
-      <x:c r="I16" s="2"/>
-      <x:c r="J16" s="2"/>
-      <x:c r="K16" s="2"/>
-      <x:c r="L16" s="2"/>
-      <x:c r="M16" s="2"/>
-      <x:c r="N16" s="2"/>
-      <x:c r="O16" s="2"/>
-      <x:c r="P16" s="2"/>
-      <x:c r="Q16" s="2"/>
-      <x:c r="R16" s="2"/>
-      <x:c r="S16" s="2"/>
-      <x:c r="T16" s="2"/>
-    </x:row>
-    <x:row r="17" ht="24" customHeight="1">
-      <x:c r="A17" s="2" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B17" s="2" t="str">
-        <x:f>IF(C17="","",INDEX(Teilnehmer!$B$2:$B$10,MATCH(C17,Teilnehmer!$A$2:$A$10,0)))</x:f>
-      </x:c>
-      <x:c r="C17" s="2" t="str">
-        <x:f>IF(AND(ISNUMBER(H10),ISNUMBER(M10),H10&lt;&gt;M10),IF(H10&lt;M10,U10,V10),"")</x:f>
-      </x:c>
-      <x:c r="D17" s="2" t="str">
-        <x:v>Platzierungsspiel</x:v>
-      </x:c>
-      <x:c r="E17" s="2"/>
-      <x:c r="F17" s="2"/>
-      <x:c r="G17" s="2"/>
-      <x:c r="H17" s="2"/>
-      <x:c r="I17" s="2"/>
-      <x:c r="J17" s="2"/>
-      <x:c r="K17" s="2"/>
-      <x:c r="L17" s="2"/>
-      <x:c r="M17" s="2"/>
-      <x:c r="N17" s="2"/>
-      <x:c r="O17" s="2"/>
-      <x:c r="P17" s="2"/>
-      <x:c r="Q17" s="2"/>
-      <x:c r="R17" s="2"/>
-      <x:c r="S17" s="2"/>
-      <x:c r="T17" s="2"/>
-    </x:row>
-    <x:row r="18" ht="24" customHeight="1">
-      <x:c r="A18" s="2" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B18" s="2" t="str">
-        <x:f>IF(C18="","",INDEX(Teilnehmer!$B$2:$B$10,MATCH(C18,Teilnehmer!$A$2:$A$10,0)))</x:f>
-      </x:c>
-      <x:c r="C18" s="2" t="str">
-        <x:f>IF(AND(ISNUMBER(H7),ISNUMBER(M7),H7&lt;&gt;M7),IF(H7&gt;M7,U7,V7),"")</x:f>
-      </x:c>
-      <x:c r="D18" s="2" t="str">
-        <x:v>Platzierungsspiel</x:v>
-      </x:c>
-      <x:c r="E18" s="2"/>
-      <x:c r="F18" s="2"/>
-      <x:c r="G18" s="2"/>
-      <x:c r="H18" s="2"/>
-      <x:c r="I18" s="2"/>
-      <x:c r="J18" s="2"/>
-      <x:c r="K18" s="2"/>
-      <x:c r="L18" s="2"/>
-      <x:c r="M18" s="2"/>
-      <x:c r="N18" s="2"/>
-      <x:c r="O18" s="2"/>
-      <x:c r="P18" s="2"/>
-      <x:c r="Q18" s="2"/>
-      <x:c r="R18" s="2"/>
-      <x:c r="S18" s="2"/>
-      <x:c r="T18" s="2"/>
-    </x:row>
-    <x:row r="19" ht="24" customHeight="1">
-      <x:c r="A19" s="2" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B19" s="2" t="str">
-        <x:f>IF(C19="","",INDEX(Teilnehmer!$B$2:$B$10,MATCH(C19,Teilnehmer!$A$2:$A$10,0)))</x:f>
-      </x:c>
-      <x:c r="C19" s="2" t="str">
-        <x:f>IF(AND(ISNUMBER(H7),ISNUMBER(M7),H7&lt;&gt;M7),IF(H7&lt;M7,U7,V7),"")</x:f>
-      </x:c>
-      <x:c r="D19" s="2" t="str">
-        <x:v>Platzierungsspiel</x:v>
-      </x:c>
-      <x:c r="E19" s="2"/>
-      <x:c r="F19" s="2"/>
-      <x:c r="G19" s="2"/>
-      <x:c r="H19" s="2"/>
-      <x:c r="I19" s="2"/>
-      <x:c r="J19" s="2"/>
-      <x:c r="K19" s="2"/>
-      <x:c r="L19" s="2"/>
-      <x:c r="M19" s="2"/>
-      <x:c r="N19" s="2"/>
-      <x:c r="O19" s="2"/>
-      <x:c r="P19" s="2"/>
-      <x:c r="Q19" s="2"/>
-      <x:c r="R19" s="2"/>
-      <x:c r="S19" s="2"/>
-      <x:c r="T19" s="2"/>
-    </x:row>
-    <x:row r="20" ht="24" customHeight="1">
-      <x:c r="A20" s="2" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B20" s="2" t="str">
-        <x:f>IF(C20="","",INDEX(Teilnehmer!$B$2:$B$10,MATCH(C20,Teilnehmer!$A$2:$A$10,0)))</x:f>
-      </x:c>
-      <x:c r="C20" s="2" t="str">
-        <x:f>IF(AND(ISNUMBER(H8),ISNUMBER(M8),H8&lt;&gt;M8),IF(H8&gt;M8,U8,V8),"")</x:f>
-      </x:c>
-      <x:c r="D20" s="2" t="str">
-        <x:v>Platzierungsspiel</x:v>
-      </x:c>
-      <x:c r="E20" s="2"/>
-      <x:c r="F20" s="2"/>
-      <x:c r="G20" s="2"/>
-      <x:c r="H20" s="2"/>
-      <x:c r="I20" s="2"/>
-      <x:c r="J20" s="2"/>
-      <x:c r="K20" s="2"/>
-      <x:c r="L20" s="2"/>
-      <x:c r="M20" s="2"/>
-      <x:c r="N20" s="2"/>
-      <x:c r="O20" s="2"/>
-      <x:c r="P20" s="2"/>
-      <x:c r="Q20" s="2"/>
-      <x:c r="R20" s="2"/>
-      <x:c r="S20" s="2"/>
-      <x:c r="T20" s="2"/>
-    </x:row>
-    <x:row r="21" ht="24" customHeight="1">
-      <x:c r="A21" s="2" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B21" s="2" t="str">
-        <x:f>IF(C21="","",INDEX(Teilnehmer!$B$2:$B$10,MATCH(C21,Teilnehmer!$A$2:$A$10,0)))</x:f>
-      </x:c>
-      <x:c r="C21" s="2" t="str">
-        <x:f>IF(AND(ISNUMBER(H8),ISNUMBER(M8),H8&lt;&gt;M8),IF(H8&lt;M8,U8,V8),"")</x:f>
-      </x:c>
-      <x:c r="D21" s="2" t="str">
-        <x:v>Platzierungsspiel</x:v>
-      </x:c>
-      <x:c r="E21" s="2"/>
-      <x:c r="F21" s="2"/>
-      <x:c r="G21" s="2"/>
-      <x:c r="H21" s="2"/>
-      <x:c r="I21" s="2"/>
-      <x:c r="J21" s="2"/>
-      <x:c r="K21" s="2"/>
-      <x:c r="L21" s="2"/>
-      <x:c r="M21" s="2"/>
-      <x:c r="N21" s="2"/>
-      <x:c r="O21" s="2"/>
-      <x:c r="P21" s="2"/>
-      <x:c r="Q21" s="2"/>
-      <x:c r="R21" s="2"/>
-      <x:c r="S21" s="2"/>
-      <x:c r="T21" s="2"/>
-    </x:row>
-    <x:row r="22" ht="24" customHeight="1">
-      <x:c r="A22" s="2" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B22" s="2" t="str">
-        <x:f>IF(C22="","",INDEX(Teilnehmer!$B$2:$B$10,MATCH(C22,Teilnehmer!$A$2:$A$10,0)))</x:f>
-      </x:c>
-      <x:c r="C22" s="2" t="str">
-        <x:f>IF(COUNTIF(Teilnehmer!$P$2:$P$10,"B5")=1,INDEX(Teilnehmer!$A$2:$A$10,MATCH("B5",Teilnehmer!$P$2:$P$10,0)),"")</x:f>
-      </x:c>
-      <x:c r="D22" s="2" t="str">
-        <x:v>Fünfter Gruppe B</x:v>
-      </x:c>
-      <x:c r="E22" s="2"/>
-      <x:c r="F22" s="2"/>
-      <x:c r="G22" s="2"/>
-      <x:c r="H22" s="2"/>
-      <x:c r="I22" s="2"/>
-      <x:c r="J22" s="2"/>
-      <x:c r="K22" s="2"/>
-      <x:c r="L22" s="2"/>
-      <x:c r="M22" s="2"/>
-      <x:c r="N22" s="2"/>
-      <x:c r="O22" s="2"/>
-      <x:c r="P22" s="2"/>
-      <x:c r="Q22" s="2"/>
-      <x:c r="R22" s="2"/>
-      <x:c r="S22" s="2"/>
-      <x:c r="T22" s="2"/>
-    </x:row>
-    <x:row r="23" ht="24" customHeight="1">
-      <x:c r="A23" s="2"/>
-      <x:c r="B23" s="2"/>
-      <x:c r="C23" s="2"/>
-      <x:c r="D23" s="2"/>
-      <x:c r="E23" s="2"/>
-      <x:c r="F23" s="2"/>
-      <x:c r="G23" s="2"/>
-      <x:c r="H23" s="2"/>
-      <x:c r="I23" s="2"/>
-      <x:c r="J23" s="2"/>
-      <x:c r="K23" s="2"/>
-      <x:c r="L23" s="2"/>
-      <x:c r="M23" s="2"/>
-      <x:c r="N23" s="2"/>
-      <x:c r="O23" s="2"/>
-      <x:c r="P23" s="2"/>
-      <x:c r="Q23" s="2"/>
-      <x:c r="R23" s="2"/>
-      <x:c r="S23" s="2"/>
-      <x:c r="T23" s="2"/>
-    </x:row>
-    <x:row r="24" ht="24" customHeight="1">
-      <x:c r="A24" s="2"/>
-      <x:c r="B24" s="2"/>
-      <x:c r="C24" s="2"/>
-      <x:c r="D24" s="2"/>
-      <x:c r="E24" s="2"/>
-      <x:c r="F24" s="2"/>
-      <x:c r="G24" s="2"/>
-      <x:c r="H24" s="2"/>
-      <x:c r="I24" s="2"/>
-      <x:c r="J24" s="2"/>
-      <x:c r="K24" s="2"/>
-      <x:c r="L24" s="2"/>
-      <x:c r="M24" s="2"/>
-      <x:c r="N24" s="2"/>
-      <x:c r="O24" s="2"/>
-      <x:c r="P24" s="2"/>
-      <x:c r="Q24" s="2"/>
-      <x:c r="R24" s="2"/>
-      <x:c r="S24" s="2"/>
-      <x:c r="T24" s="2"/>
-    </x:row>
-    <x:row r="25" ht="24" customHeight="1">
-      <x:c r="A25" s="3" t="str">
-        <x:v>Runde</x:v>
-      </x:c>
-      <x:c r="B25" s="3" t="str">
-        <x:v>Tisch 1</x:v>
-      </x:c>
-      <x:c r="C25" s="3" t="str">
-        <x:v>Tisch 2</x:v>
-      </x:c>
-      <x:c r="D25" s="3" t="str">
-        <x:v>Tisch 3</x:v>
-      </x:c>
-      <x:c r="E25" s="3" t="str">
-        <x:v>Tisch 4</x:v>
-      </x:c>
-      <x:c r="F25" s="2"/>
-      <x:c r="G25" s="2"/>
-      <x:c r="H25" s="2"/>
-      <x:c r="I25" s="2"/>
-      <x:c r="J25" s="2"/>
-      <x:c r="K25" s="2"/>
-      <x:c r="L25" s="2"/>
-      <x:c r="M25" s="2"/>
-      <x:c r="N25" s="2"/>
-      <x:c r="O25" s="2"/>
-      <x:c r="P25" s="2"/>
-      <x:c r="Q25" s="2"/>
-      <x:c r="R25" s="2"/>
-      <x:c r="S25" s="2"/>
-      <x:c r="T25" s="2"/>
-    </x:row>
-    <x:row r="26" ht="42" customHeight="1">
-      <x:c r="A26" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B26" s="40" t="str">
-        <x:v>A1 – A4</x:v>
-      </x:c>
-      <x:c r="C26" s="40" t="str">
-        <x:v>A2 – A3</x:v>
-      </x:c>
-      <x:c r="D26" s="40" t="str">
-        <x:v>B2 – B4</x:v>
-      </x:c>
-      <x:c r="E26" s="40" t="str">
-        <x:v>B1 – B5</x:v>
-      </x:c>
-      <x:c r="F26" s="2"/>
-      <x:c r="G26" s="2"/>
-      <x:c r="H26" s="2"/>
-      <x:c r="I26" s="2"/>
-      <x:c r="J26" s="2"/>
-      <x:c r="K26" s="2"/>
-      <x:c r="L26" s="2"/>
-      <x:c r="M26" s="2"/>
-      <x:c r="N26" s="2"/>
-      <x:c r="O26" s="2"/>
-      <x:c r="P26" s="2"/>
-      <x:c r="Q26" s="2"/>
-      <x:c r="R26" s="2"/>
-      <x:c r="S26" s="2"/>
-      <x:c r="T26" s="2"/>
-    </x:row>
-    <x:row r="27" ht="42" customHeight="1">
-      <x:c r="A27" s="2" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B27" s="40" t="str">
-        <x:v>A1 – A3</x:v>
-      </x:c>
-      <x:c r="C27" s="40" t="str">
-        <x:v>A2 – A4</x:v>
-      </x:c>
-      <x:c r="D27" s="40" t="str">
-        <x:v>B1 – B4</x:v>
-      </x:c>
-      <x:c r="E27" s="40" t="str">
-        <x:v>B2 – B3</x:v>
-      </x:c>
-      <x:c r="F27" s="2"/>
-      <x:c r="G27" s="2"/>
-      <x:c r="H27" s="2"/>
-      <x:c r="I27" s="2"/>
-      <x:c r="J27" s="2"/>
-      <x:c r="K27" s="2"/>
-      <x:c r="L27" s="2"/>
-      <x:c r="M27" s="2"/>
-      <x:c r="N27" s="2"/>
-      <x:c r="O27" s="2"/>
-      <x:c r="P27" s="2"/>
-      <x:c r="Q27" s="2"/>
-      <x:c r="R27" s="2"/>
-      <x:c r="S27" s="2"/>
-      <x:c r="T27" s="2"/>
-    </x:row>
-    <x:row r="28" ht="42" customHeight="1">
-      <x:c r="A28" s="2" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B28" s="40" t="str">
-        <x:v>A1 – A2</x:v>
-      </x:c>
-      <x:c r="C28" s="40" t="str">
-        <x:v>A3 – A4</x:v>
-      </x:c>
-      <x:c r="D28" s="40" t="str">
-        <x:v>B2 – B5</x:v>
-      </x:c>
-      <x:c r="E28" s="40" t="str">
-        <x:v>B3 – B4</x:v>
-      </x:c>
-      <x:c r="F28" s="2"/>
-      <x:c r="G28" s="2"/>
-      <x:c r="H28" s="2"/>
-      <x:c r="I28" s="2"/>
-      <x:c r="J28" s="2"/>
-      <x:c r="K28" s="2"/>
-      <x:c r="L28" s="2"/>
-      <x:c r="M28" s="2"/>
-      <x:c r="N28" s="2"/>
-      <x:c r="O28" s="2"/>
-      <x:c r="P28" s="2"/>
-      <x:c r="Q28" s="2"/>
-      <x:c r="R28" s="2"/>
-      <x:c r="S28" s="2"/>
-      <x:c r="T28" s="2"/>
-    </x:row>
-    <x:row r="29" ht="42" customHeight="1">
-      <x:c r="A29" s="2" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B29" s="40" t="str">
-        <x:v>Frei</x:v>
-      </x:c>
-      <x:c r="C29" s="40" t="str">
-        <x:v>Frei</x:v>
-      </x:c>
-      <x:c r="D29" s="40" t="str">
-        <x:v>B1 – B3</x:v>
-      </x:c>
-      <x:c r="E29" s="40" t="str">
-        <x:v>B4 – B5</x:v>
-      </x:c>
-      <x:c r="F29" s="2"/>
-      <x:c r="G29" s="2"/>
-      <x:c r="H29" s="2"/>
-      <x:c r="I29" s="2"/>
-      <x:c r="J29" s="2"/>
-      <x:c r="K29" s="2"/>
-      <x:c r="L29" s="2"/>
-      <x:c r="M29" s="2"/>
-      <x:c r="N29" s="2"/>
-      <x:c r="O29" s="2"/>
-      <x:c r="P29" s="2"/>
-      <x:c r="Q29" s="2"/>
-      <x:c r="R29" s="2"/>
-      <x:c r="S29" s="2"/>
-      <x:c r="T29" s="2"/>
-    </x:row>
-    <x:row r="30" ht="42" customHeight="1">
-      <x:c r="A30" s="2" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B30" s="40" t="str">
-        <x:v>Frei</x:v>
-      </x:c>
-      <x:c r="C30" s="40" t="str">
-        <x:v>Frei</x:v>
-      </x:c>
-      <x:c r="D30" s="40" t="str">
-        <x:v>B3 – B5</x:v>
-      </x:c>
-      <x:c r="E30" s="40" t="str">
-        <x:v>B1 – B2</x:v>
-      </x:c>
-      <x:c r="F30" s="2"/>
-      <x:c r="G30" s="2"/>
-      <x:c r="H30" s="2"/>
-      <x:c r="I30" s="2"/>
-      <x:c r="J30" s="2"/>
-      <x:c r="K30" s="2"/>
-      <x:c r="L30" s="2"/>
-      <x:c r="M30" s="2"/>
-      <x:c r="N30" s="2"/>
-      <x:c r="O30" s="2"/>
-      <x:c r="P30" s="2"/>
-      <x:c r="Q30" s="2"/>
-      <x:c r="R30" s="2"/>
-      <x:c r="S30" s="2"/>
-      <x:c r="T30" s="2"/>
-    </x:row>
-    <x:row r="31" ht="42" customHeight="1">
-      <x:c r="A31" s="2" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B31" s="40" t="str">
-        <x:v>HF1</x:v>
-      </x:c>
-      <x:c r="C31" s="40" t="str">
-        <x:v>HF2</x:v>
-      </x:c>
-      <x:c r="D31" s="40" t="str">
-        <x:v>Platz 5–6</x:v>
-      </x:c>
-      <x:c r="E31" s="40" t="str">
-        <x:v>Platz 7–8</x:v>
-      </x:c>
-      <x:c r="F31" s="2"/>
-      <x:c r="G31" s="2"/>
-      <x:c r="H31" s="2"/>
-      <x:c r="I31" s="2"/>
-      <x:c r="J31" s="2"/>
-      <x:c r="K31" s="2"/>
-      <x:c r="L31" s="2"/>
-      <x:c r="M31" s="2"/>
-      <x:c r="N31" s="2"/>
-      <x:c r="O31" s="2"/>
-      <x:c r="P31" s="2"/>
-      <x:c r="Q31" s="2"/>
-      <x:c r="R31" s="2"/>
-      <x:c r="S31" s="2"/>
-      <x:c r="T31" s="2"/>
-    </x:row>
-    <x:row r="32" ht="42" customHeight="1">
-      <x:c r="A32" s="2" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B32" s="40" t="str">
-        <x:v>Finale</x:v>
-      </x:c>
-      <x:c r="C32" s="40" t="str">
-        <x:v>Platz 3–4</x:v>
-      </x:c>
-      <x:c r="D32" s="40" t="str">
-        <x:v>Frei</x:v>
-      </x:c>
-      <x:c r="E32" s="40" t="str">
-        <x:v>Frei</x:v>
-      </x:c>
-      <x:c r="F32" s="2"/>
-      <x:c r="G32" s="2"/>
-      <x:c r="H32" s="2"/>
-      <x:c r="I32" s="2"/>
-      <x:c r="J32" s="2"/>
-      <x:c r="K32" s="2"/>
-      <x:c r="L32" s="2"/>
-      <x:c r="M32" s="2"/>
-      <x:c r="N32" s="2"/>
-      <x:c r="O32" s="2"/>
-      <x:c r="P32" s="2"/>
-      <x:c r="Q32" s="2"/>
-      <x:c r="R32" s="2"/>
-      <x:c r="S32" s="2"/>
-      <x:c r="T32" s="2"/>
-    </x:row>
-    <x:row r="33" ht="24" customHeight="1">
-      <x:c r="A33" s="2"/>
-      <x:c r="B33" s="2"/>
-      <x:c r="C33" s="2"/>
-      <x:c r="D33" s="2"/>
-      <x:c r="E33" s="2"/>
-      <x:c r="F33" s="2"/>
-      <x:c r="G33" s="2"/>
-      <x:c r="H33" s="2"/>
-      <x:c r="I33" s="2"/>
-      <x:c r="J33" s="2"/>
-      <x:c r="K33" s="2"/>
-      <x:c r="L33" s="2"/>
-      <x:c r="M33" s="2"/>
-      <x:c r="N33" s="2"/>
-      <x:c r="O33" s="2"/>
-      <x:c r="P33" s="2"/>
-      <x:c r="Q33" s="2"/>
-      <x:c r="R33" s="2"/>
-      <x:c r="S33" s="2"/>
-      <x:c r="T33" s="2"/>
-    </x:row>
-    <x:row r="34" ht="24" customHeight="1">
-      <x:c r="A34" s="2"/>
-      <x:c r="B34" s="2"/>
-      <x:c r="C34" s="2"/>
-      <x:c r="D34" s="2"/>
-      <x:c r="E34" s="2"/>
-      <x:c r="F34" s="2"/>
-      <x:c r="G34" s="2"/>
-      <x:c r="H34" s="2"/>
-      <x:c r="I34" s="2"/>
-      <x:c r="J34" s="2"/>
-      <x:c r="K34" s="2"/>
-      <x:c r="L34" s="2"/>
-      <x:c r="M34" s="2"/>
-      <x:c r="N34" s="2"/>
-      <x:c r="O34" s="2"/>
-      <x:c r="P34" s="2"/>
-      <x:c r="Q34" s="2"/>
-      <x:c r="R34" s="2"/>
-      <x:c r="S34" s="2"/>
-      <x:c r="T34" s="2"/>
-    </x:row>
-    <x:row r="35" ht="24" customHeight="1">
-      <x:c r="A35" s="2"/>
-      <x:c r="B35" s="2"/>
-      <x:c r="C35" s="2"/>
-      <x:c r="D35" s="2"/>
-      <x:c r="E35" s="2"/>
-      <x:c r="F35" s="2"/>
-      <x:c r="G35" s="2"/>
-      <x:c r="H35" s="2"/>
-      <x:c r="I35" s="2"/>
-      <x:c r="J35" s="2"/>
-      <x:c r="K35" s="2"/>
-      <x:c r="L35" s="2"/>
-      <x:c r="M35" s="2"/>
-      <x:c r="N35" s="2"/>
-      <x:c r="O35" s="2"/>
-      <x:c r="P35" s="2"/>
-      <x:c r="Q35" s="2"/>
-      <x:c r="R35" s="2"/>
-      <x:c r="S35" s="2"/>
-      <x:c r="T35" s="2"/>
-    </x:row>
-    <x:row r="36" ht="24" customHeight="1">
-      <x:c r="A36" s="2"/>
-      <x:c r="B36" s="2"/>
-      <x:c r="C36" s="2"/>
-      <x:c r="D36" s="2"/>
-      <x:c r="E36" s="2"/>
-      <x:c r="F36" s="2"/>
-      <x:c r="G36" s="2"/>
-      <x:c r="H36" s="2"/>
-      <x:c r="I36" s="2"/>
-      <x:c r="J36" s="2"/>
-      <x:c r="K36" s="2"/>
-      <x:c r="L36" s="2"/>
-      <x:c r="M36" s="2"/>
-      <x:c r="N36" s="2"/>
-      <x:c r="O36" s="2"/>
-      <x:c r="P36" s="2"/>
-      <x:c r="Q36" s="2"/>
-      <x:c r="R36" s="2"/>
-      <x:c r="S36" s="2"/>
-      <x:c r="T36" s="2"/>
-    </x:row>
-    <x:row r="37" ht="24" customHeight="1">
-      <x:c r="A37" s="2"/>
-      <x:c r="B37" s="2"/>
-      <x:c r="C37" s="2"/>
-      <x:c r="D37" s="2"/>
-      <x:c r="E37" s="2"/>
-      <x:c r="F37" s="2"/>
-      <x:c r="G37" s="2"/>
-      <x:c r="H37" s="2"/>
-      <x:c r="I37" s="2"/>
-      <x:c r="J37" s="2"/>
-      <x:c r="K37" s="2"/>
-      <x:c r="L37" s="2"/>
-      <x:c r="M37" s="2"/>
-      <x:c r="N37" s="2"/>
-      <x:c r="O37" s="2"/>
-      <x:c r="P37" s="2"/>
-      <x:c r="Q37" s="2"/>
-      <x:c r="R37" s="2"/>
-      <x:c r="S37" s="2"/>
-      <x:c r="T37" s="2"/>
-    </x:row>
-    <x:row r="38" ht="24" customHeight="1">
-      <x:c r="A38" s="2"/>
-      <x:c r="B38" s="2"/>
-      <x:c r="C38" s="2"/>
-      <x:c r="D38" s="2"/>
-      <x:c r="E38" s="2"/>
-      <x:c r="F38" s="2"/>
-      <x:c r="G38" s="2"/>
-      <x:c r="H38" s="2"/>
-      <x:c r="I38" s="2"/>
-      <x:c r="J38" s="2"/>
-      <x:c r="K38" s="2"/>
-      <x:c r="L38" s="2"/>
-      <x:c r="M38" s="2"/>
-      <x:c r="N38" s="2"/>
-      <x:c r="O38" s="2"/>
-      <x:c r="P38" s="2"/>
-      <x:c r="Q38" s="2"/>
-      <x:c r="R38" s="2"/>
-      <x:c r="S38" s="2"/>
-      <x:c r="T38" s="2"/>
-    </x:row>
-    <x:row r="39" ht="24" customHeight="1">
-      <x:c r="A39" s="2"/>
-      <x:c r="B39" s="2"/>
-      <x:c r="C39" s="2"/>
-      <x:c r="D39" s="2"/>
-      <x:c r="E39" s="2"/>
-      <x:c r="F39" s="2"/>
-      <x:c r="G39" s="2"/>
-      <x:c r="H39" s="2"/>
-      <x:c r="I39" s="2"/>
-      <x:c r="J39" s="2"/>
-      <x:c r="K39" s="2"/>
-      <x:c r="L39" s="2"/>
-      <x:c r="M39" s="2"/>
-      <x:c r="N39" s="2"/>
-      <x:c r="O39" s="2"/>
-      <x:c r="P39" s="2"/>
-      <x:c r="Q39" s="2"/>
-      <x:c r="R39" s="2"/>
-      <x:c r="S39" s="2"/>
-      <x:c r="T39" s="2"/>
-    </x:row>
     <x:row r="40" ht="24" customHeight="1">
-      <x:c r="A40" s="2"/>
-      <x:c r="B40" s="2"/>
-      <x:c r="C40" s="2"/>
-      <x:c r="D40" s="2"/>
-      <x:c r="E40" s="2"/>
-      <x:c r="F40" s="2"/>
-      <x:c r="G40" s="2"/>
-      <x:c r="H40" s="2"/>
-      <x:c r="I40" s="2"/>
-      <x:c r="J40" s="2"/>
-      <x:c r="K40" s="2"/>
-      <x:c r="L40" s="2"/>
-      <x:c r="M40" s="2"/>
-      <x:c r="N40" s="2"/>
-      <x:c r="O40" s="2"/>
-      <x:c r="P40" s="2"/>
-      <x:c r="Q40" s="2"/>
-      <x:c r="R40" s="2"/>
-      <x:c r="S40" s="2"/>
-      <x:c r="T40" s="2"/>
+      <x:c r="A40" s="48" t="str">
+        <x:f>IF(D36="","",D36)</x:f>
+      </x:c>
+      <x:c r="B40" s="61"/>
+      <x:c r="C40" s="62" t="str">
+        <x:f>IF(ISNUMBER(E37),E37,"")</x:f>
+      </x:c>
+      <x:c r="D40" s="55" t="str">
+        <x:v>Bälle</x:v>
+      </x:c>
+      <x:c r="E40" s="56" t="str">
+        <x:v>Aufn.</x:v>
+      </x:c>
+      <x:c r="F40" s="55"/>
+      <x:c r="G40" s="56"/>
+      <x:c r="H40" s="55"/>
+      <x:c r="I40" s="56"/>
+      <x:c r="J40" s="1"/>
+      <x:c r="K40" s="1"/>
+      <x:c r="L40" s="1"/>
+      <x:c r="M40" s="1"/>
+      <x:c r="N40" s="66" t="str">
+        <x:f>IF(COUNT(B41)=0,"",SUM(B41))</x:f>
+      </x:c>
+      <x:c r="O40" s="66" t="str">
+        <x:f>IF(COUNT(B40)=0,"",SUM(B40))</x:f>
+      </x:c>
+      <x:c r="P40" s="66" t="str">
+        <x:f>IF(COUNT(C40)=0,"",SUM(C40))</x:f>
+      </x:c>
+      <x:c r="Q40" s="69" t="str">
+        <x:f>IF(COUNT(B41)=0,"",MAX(IF(B41=2,B42,0)))</x:f>
+      </x:c>
+      <x:c r="R40" s="69" t="str">
+        <x:f>IF(P40&gt;0,TRUNC(O40/P40,3),"")</x:f>
+      </x:c>
+      <x:c r="S40" s="66" t="str">
+        <x:f>IF(COUNT(C42)=0,"",MAX(C42))</x:f>
+      </x:c>
+      <x:c r="T40" s="66" t="str">
+        <x:f>IF(ISNUMBER(N40),IF(N40=2,1,IF(N40=0,2,"")),"")</x:f>
+      </x:c>
     </x:row>
     <x:row r="41" ht="24" customHeight="1">
-      <x:c r="A41" s="2"/>
-      <x:c r="B41" s="2"/>
-      <x:c r="C41" s="2"/>
-      <x:c r="D41" s="2"/>
-      <x:c r="E41" s="2"/>
-      <x:c r="F41" s="2"/>
-      <x:c r="G41" s="2"/>
-      <x:c r="H41" s="2"/>
-      <x:c r="I41" s="2"/>
-      <x:c r="J41" s="2"/>
-      <x:c r="K41" s="2"/>
-      <x:c r="L41" s="2"/>
-      <x:c r="M41" s="2"/>
-      <x:c r="N41" s="2"/>
-      <x:c r="O41" s="2"/>
-      <x:c r="P41" s="2"/>
-      <x:c r="Q41" s="2"/>
-      <x:c r="R41" s="2"/>
-      <x:c r="S41" s="2"/>
-      <x:c r="T41" s="2"/>
+      <x:c r="A41" s="1"/>
+      <x:c r="B41" s="64" t="str">
+        <x:f>IF(AND(ISNUMBER(B40),ISNUMBER(D37),U37&lt;&gt;"",U36&lt;&gt;""),IF(IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U37,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(U36,Teilnehmer!$A$2:$A$10,0))&gt;0),B40/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U37,Teilnehmer!$A$2:$A$10,0)),B40)&gt;IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U37,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(U36,Teilnehmer!$A$2:$A$10,0))&gt;0),D37/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U36,Teilnehmer!$A$2:$A$10,0)),D37),2,IF(IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U37,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(U36,Teilnehmer!$A$2:$A$10,0))&gt;0),B40/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U37,Teilnehmer!$A$2:$A$10,0)),B40)=IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U37,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(U36,Teilnehmer!$A$2:$A$10,0))&gt;0),D37/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U36,Teilnehmer!$A$2:$A$10,0)),D37),1,0)),"")</x:f>
+      </x:c>
+      <x:c r="C41" s="52"/>
+      <x:c r="D41" s="57" t="str">
+        <x:v>Partiepunkte</x:v>
+      </x:c>
+      <x:c r="E41" s="58"/>
+      <x:c r="F41" s="57"/>
+      <x:c r="G41" s="58"/>
+      <x:c r="H41" s="57"/>
+      <x:c r="I41" s="58"/>
+      <x:c r="J41" s="1"/>
+      <x:c r="K41" s="1"/>
+      <x:c r="L41" s="1"/>
+      <x:c r="M41" s="1"/>
+      <x:c r="N41" s="67"/>
+      <x:c r="O41" s="67"/>
+      <x:c r="P41" s="67"/>
+      <x:c r="Q41" s="70"/>
+      <x:c r="R41" s="70"/>
+      <x:c r="S41" s="67"/>
+      <x:c r="T41" s="67"/>
     </x:row>
     <x:row r="42" ht="24" customHeight="1">
-      <x:c r="A42" s="2"/>
-      <x:c r="B42" s="2"/>
-      <x:c r="C42" s="2"/>
-      <x:c r="D42" s="2"/>
-      <x:c r="E42" s="2"/>
-      <x:c r="F42" s="2"/>
-      <x:c r="G42" s="2"/>
-      <x:c r="H42" s="2"/>
-      <x:c r="I42" s="2"/>
-      <x:c r="J42" s="2"/>
-      <x:c r="K42" s="2"/>
-      <x:c r="L42" s="2"/>
-      <x:c r="M42" s="2"/>
-      <x:c r="N42" s="2"/>
-      <x:c r="O42" s="2"/>
-      <x:c r="P42" s="2"/>
-      <x:c r="Q42" s="2"/>
-      <x:c r="R42" s="2"/>
-      <x:c r="S42" s="2"/>
-      <x:c r="T42" s="2"/>
+      <x:c r="A42" s="1"/>
+      <x:c r="B42" s="65" t="str">
+        <x:f>IF(AND(ISNUMBER(B40),C40&gt;0),TRUNC(B40/C40,3),"")</x:f>
+      </x:c>
+      <x:c r="C42" s="63"/>
+      <x:c r="D42" s="59" t="str">
+        <x:v>DS</x:v>
+      </x:c>
+      <x:c r="E42" s="60" t="str">
+        <x:v>HS</x:v>
+      </x:c>
+      <x:c r="F42" s="59"/>
+      <x:c r="G42" s="60"/>
+      <x:c r="H42" s="59"/>
+      <x:c r="I42" s="60"/>
+      <x:c r="J42" s="1"/>
+      <x:c r="K42" s="1"/>
+      <x:c r="L42" s="1"/>
+      <x:c r="M42" s="1"/>
+      <x:c r="N42" s="68"/>
+      <x:c r="O42" s="68"/>
+      <x:c r="P42" s="68"/>
+      <x:c r="Q42" s="71"/>
+      <x:c r="R42" s="71"/>
+      <x:c r="S42" s="68"/>
+      <x:c r="T42" s="68"/>
     </x:row>
     <x:row r="43" ht="24" customHeight="1">
-      <x:c r="A43" s="2"/>
-      <x:c r="B43" s="2"/>
-      <x:c r="C43" s="2"/>
-      <x:c r="D43" s="2"/>
-      <x:c r="E43" s="2"/>
-      <x:c r="F43" s="2"/>
-      <x:c r="G43" s="2"/>
-      <x:c r="H43" s="2"/>
-      <x:c r="I43" s="2"/>
-      <x:c r="J43" s="2"/>
-      <x:c r="K43" s="2"/>
-      <x:c r="L43" s="2"/>
-      <x:c r="M43" s="2"/>
-      <x:c r="N43" s="2"/>
-      <x:c r="O43" s="2"/>
-      <x:c r="P43" s="2"/>
-      <x:c r="Q43" s="2"/>
-      <x:c r="R43" s="2"/>
-      <x:c r="S43" s="2"/>
-      <x:c r="T43" s="2"/>
+      <x:c r="A43" s="48" t="str">
+        <x:f>IF(F36="","",F36)</x:f>
+      </x:c>
+      <x:c r="B43" s="55"/>
+      <x:c r="C43" s="56"/>
+      <x:c r="D43" s="55"/>
+      <x:c r="E43" s="56"/>
+      <x:c r="F43" s="55" t="str">
+        <x:v>Bälle</x:v>
+      </x:c>
+      <x:c r="G43" s="56" t="str">
+        <x:v>Aufn.</x:v>
+      </x:c>
+      <x:c r="H43" s="61"/>
+      <x:c r="I43" s="62"/>
+      <x:c r="J43" s="1"/>
+      <x:c r="K43" s="1"/>
+      <x:c r="L43" s="1"/>
+      <x:c r="M43" s="1"/>
+      <x:c r="N43" s="66" t="str">
+        <x:f>IF(COUNT(H44)=0,"",SUM(H44))</x:f>
+      </x:c>
+      <x:c r="O43" s="66" t="str">
+        <x:f>IF(COUNT(H43)=0,"",SUM(H43))</x:f>
+      </x:c>
+      <x:c r="P43" s="66" t="str">
+        <x:f>IF(COUNT(I43)=0,"",SUM(I43))</x:f>
+      </x:c>
+      <x:c r="Q43" s="69" t="str">
+        <x:f>IF(COUNT(H44)=0,"",MAX(IF(H44=2,H45,0)))</x:f>
+      </x:c>
+      <x:c r="R43" s="69" t="str">
+        <x:f>IF(P43&gt;0,TRUNC(O43/P43,3),"")</x:f>
+      </x:c>
+      <x:c r="S43" s="66" t="str">
+        <x:f>IF(COUNT(I45)=0,"",MAX(I45))</x:f>
+      </x:c>
+      <x:c r="T43" s="66" t="str">
+        <x:f>IF(ISNUMBER(N43),IF(N43=2,1,IF(N43=0,2,"")),"")</x:f>
+      </x:c>
     </x:row>
     <x:row r="44" ht="24" customHeight="1">
-      <x:c r="A44" s="2"/>
-      <x:c r="B44" s="2"/>
-      <x:c r="C44" s="2"/>
-      <x:c r="D44" s="2"/>
-      <x:c r="E44" s="2"/>
-      <x:c r="F44" s="2"/>
-      <x:c r="G44" s="2"/>
-      <x:c r="H44" s="2"/>
-      <x:c r="I44" s="2"/>
-      <x:c r="J44" s="2"/>
-      <x:c r="K44" s="2"/>
-      <x:c r="L44" s="2"/>
-      <x:c r="M44" s="2"/>
-      <x:c r="N44" s="2"/>
-      <x:c r="O44" s="2"/>
-      <x:c r="P44" s="2"/>
-      <x:c r="Q44" s="2"/>
-      <x:c r="R44" s="2"/>
-      <x:c r="S44" s="2"/>
-      <x:c r="T44" s="2"/>
+      <x:c r="A44" s="1"/>
+      <x:c r="B44" s="57"/>
+      <x:c r="C44" s="58"/>
+      <x:c r="D44" s="57"/>
+      <x:c r="E44" s="58"/>
+      <x:c r="F44" s="57" t="str">
+        <x:v>Partiepunkte</x:v>
+      </x:c>
+      <x:c r="G44" s="58"/>
+      <x:c r="H44" s="64" t="str">
+        <x:f>IF(AND(ISNUMBER(H43),ISNUMBER(F46),U38&lt;&gt;"",U39&lt;&gt;""),IF(IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U38,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(U39,Teilnehmer!$A$2:$A$10,0))&gt;0),H43/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U38,Teilnehmer!$A$2:$A$10,0)),H43)&gt;IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U38,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(U39,Teilnehmer!$A$2:$A$10,0))&gt;0),F46/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U39,Teilnehmer!$A$2:$A$10,0)),F46),2,IF(IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U38,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(U39,Teilnehmer!$A$2:$A$10,0))&gt;0),H43/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U38,Teilnehmer!$A$2:$A$10,0)),H43)=IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U38,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(U39,Teilnehmer!$A$2:$A$10,0))&gt;0),F46/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U39,Teilnehmer!$A$2:$A$10,0)),F46),1,0)),"")</x:f>
+      </x:c>
+      <x:c r="I44" s="52"/>
+      <x:c r="J44" s="1"/>
+      <x:c r="K44" s="1"/>
+      <x:c r="L44" s="1"/>
+      <x:c r="M44" s="1"/>
+      <x:c r="N44" s="67"/>
+      <x:c r="O44" s="67"/>
+      <x:c r="P44" s="67"/>
+      <x:c r="Q44" s="70"/>
+      <x:c r="R44" s="70"/>
+      <x:c r="S44" s="67"/>
+      <x:c r="T44" s="67"/>
     </x:row>
     <x:row r="45" ht="24" customHeight="1">
-      <x:c r="A45" s="2"/>
-      <x:c r="B45" s="2"/>
-      <x:c r="C45" s="2"/>
-      <x:c r="D45" s="2"/>
-      <x:c r="E45" s="2"/>
-      <x:c r="F45" s="2"/>
-      <x:c r="G45" s="2"/>
-      <x:c r="H45" s="2"/>
-      <x:c r="I45" s="2"/>
-      <x:c r="J45" s="2"/>
-      <x:c r="K45" s="2"/>
-      <x:c r="L45" s="2"/>
-      <x:c r="M45" s="2"/>
-      <x:c r="N45" s="2"/>
-      <x:c r="O45" s="2"/>
-      <x:c r="P45" s="2"/>
-      <x:c r="Q45" s="2"/>
-      <x:c r="R45" s="2"/>
-      <x:c r="S45" s="2"/>
-      <x:c r="T45" s="2"/>
+      <x:c r="A45" s="1"/>
+      <x:c r="B45" s="59"/>
+      <x:c r="C45" s="60"/>
+      <x:c r="D45" s="59"/>
+      <x:c r="E45" s="60"/>
+      <x:c r="F45" s="59" t="str">
+        <x:v>DS</x:v>
+      </x:c>
+      <x:c r="G45" s="60" t="str">
+        <x:v>HS</x:v>
+      </x:c>
+      <x:c r="H45" s="65" t="str">
+        <x:f>IF(AND(ISNUMBER(H43),I43&gt;0),TRUNC(H43/I43,3),"")</x:f>
+      </x:c>
+      <x:c r="I45" s="63"/>
+      <x:c r="J45" s="1"/>
+      <x:c r="K45" s="1"/>
+      <x:c r="L45" s="1"/>
+      <x:c r="M45" s="1"/>
+      <x:c r="N45" s="68"/>
+      <x:c r="O45" s="68"/>
+      <x:c r="P45" s="68"/>
+      <x:c r="Q45" s="71"/>
+      <x:c r="R45" s="71"/>
+      <x:c r="S45" s="68"/>
+      <x:c r="T45" s="68"/>
+    </x:row>
+    <x:row r="46" ht="24" customHeight="1">
+      <x:c r="A46" s="48" t="str">
+        <x:f>IF(H36="","",H36)</x:f>
+      </x:c>
+      <x:c r="B46" s="55"/>
+      <x:c r="C46" s="56"/>
+      <x:c r="D46" s="55"/>
+      <x:c r="E46" s="56"/>
+      <x:c r="F46" s="61"/>
+      <x:c r="G46" s="62" t="str">
+        <x:f>IF(ISNUMBER(I43),I43,"")</x:f>
+      </x:c>
+      <x:c r="H46" s="55" t="str">
+        <x:v>Bälle</x:v>
+      </x:c>
+      <x:c r="I46" s="56" t="str">
+        <x:v>Aufn.</x:v>
+      </x:c>
+      <x:c r="J46" s="1"/>
+      <x:c r="K46" s="1"/>
+      <x:c r="L46" s="1"/>
+      <x:c r="M46" s="1"/>
+      <x:c r="N46" s="66" t="str">
+        <x:f>IF(COUNT(F47)=0,"",SUM(F47))</x:f>
+      </x:c>
+      <x:c r="O46" s="66" t="str">
+        <x:f>IF(COUNT(F46)=0,"",SUM(F46))</x:f>
+      </x:c>
+      <x:c r="P46" s="66" t="str">
+        <x:f>IF(COUNT(G46)=0,"",SUM(G46))</x:f>
+      </x:c>
+      <x:c r="Q46" s="69" t="str">
+        <x:f>IF(COUNT(F47)=0,"",MAX(IF(F47=2,F48,0)))</x:f>
+      </x:c>
+      <x:c r="R46" s="69" t="str">
+        <x:f>IF(P46&gt;0,TRUNC(O46/P46,3),"")</x:f>
+      </x:c>
+      <x:c r="S46" s="66" t="str">
+        <x:f>IF(COUNT(G48)=0,"",MAX(G48))</x:f>
+      </x:c>
+      <x:c r="T46" s="66" t="str">
+        <x:f>IF(ISNUMBER(N46),IF(N46=2,1,IF(N46=0,2,"")),"")</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="24" customHeight="1">
+      <x:c r="A47" s="1"/>
+      <x:c r="B47" s="57"/>
+      <x:c r="C47" s="58"/>
+      <x:c r="D47" s="57"/>
+      <x:c r="E47" s="58"/>
+      <x:c r="F47" s="64" t="str">
+        <x:f>IF(AND(ISNUMBER(F46),ISNUMBER(H43),U39&lt;&gt;"",U38&lt;&gt;""),IF(IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U39,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(U38,Teilnehmer!$A$2:$A$10,0))&gt;0),F46/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U39,Teilnehmer!$A$2:$A$10,0)),F46)&gt;IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U39,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(U38,Teilnehmer!$A$2:$A$10,0))&gt;0),H43/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U38,Teilnehmer!$A$2:$A$10,0)),H43),2,IF(IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U39,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(U38,Teilnehmer!$A$2:$A$10,0))&gt;0),F46/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U39,Teilnehmer!$A$2:$A$10,0)),F46)=IF(AND(INDEX(Teilnehmer!$F$2:$F$10,MATCH(U39,Teilnehmer!$A$2:$A$10,0))&gt;0,INDEX(Teilnehmer!$F$2:$F$10,MATCH(U38,Teilnehmer!$A$2:$A$10,0))&gt;0),H43/INDEX(Teilnehmer!$F$2:$F$10,MATCH(U38,Teilnehmer!$A$2:$A$10,0)),H43),1,0)),"")</x:f>
+      </x:c>
+      <x:c r="G47" s="52"/>
+      <x:c r="H47" s="57" t="str">
+        <x:v>Partiepunkte</x:v>
+      </x:c>
+      <x:c r="I47" s="58"/>
+      <x:c r="J47" s="1"/>
+      <x:c r="K47" s="1"/>
+      <x:c r="L47" s="1"/>
+      <x:c r="M47" s="1"/>
+      <x:c r="N47" s="67"/>
+      <x:c r="O47" s="67"/>
+      <x:c r="P47" s="67"/>
+      <x:c r="Q47" s="70"/>
+      <x:c r="R47" s="70"/>
+      <x:c r="S47" s="67"/>
+      <x:c r="T47" s="67"/>
+    </x:row>
+    <x:row r="48" ht="24" customHeight="1">
+      <x:c r="A48" s="1"/>
+      <x:c r="B48" s="59"/>
+      <x:c r="C48" s="60"/>
+      <x:c r="D48" s="59"/>
+      <x:c r="E48" s="60"/>
+      <x:c r="F48" s="65" t="str">
+        <x:f>IF(AND(ISNUMBER(F46),G46&gt;0),TRUNC(F46/G46,3),"")</x:f>
+      </x:c>
+      <x:c r="G48" s="63"/>
+      <x:c r="H48" s="59" t="str">
+        <x:v>DS</x:v>
+      </x:c>
+      <x:c r="I48" s="60" t="str">
+        <x:v>HS</x:v>
+      </x:c>
+      <x:c r="J48" s="1"/>
+      <x:c r="K48" s="1"/>
+      <x:c r="L48" s="1"/>
+      <x:c r="M48" s="1"/>
+      <x:c r="N48" s="68"/>
+      <x:c r="O48" s="68"/>
+      <x:c r="P48" s="68"/>
+      <x:c r="Q48" s="71"/>
+      <x:c r="R48" s="71"/>
+      <x:c r="S48" s="68"/>
+      <x:c r="T48" s="68"/>
+    </x:row>
+    <x:row r="49" ht="24" customHeight="1">
+      <x:c r="A49" s="1"/>
+      <x:c r="B49" s="1"/>
+      <x:c r="C49" s="1"/>
+      <x:c r="D49" s="1"/>
+      <x:c r="E49" s="1"/>
+      <x:c r="F49" s="1"/>
+      <x:c r="G49" s="1"/>
+      <x:c r="H49" s="1"/>
+      <x:c r="I49" s="1"/>
+      <x:c r="J49" s="1"/>
+      <x:c r="K49" s="1"/>
+      <x:c r="L49" s="1"/>
+      <x:c r="M49" s="1"/>
+      <x:c r="N49" s="1"/>
+      <x:c r="O49" s="1"/>
+      <x:c r="P49" s="1"/>
+      <x:c r="Q49" s="1"/>
+      <x:c r="R49" s="1"/>
+      <x:c r="S49" s="1"/>
+      <x:c r="T49" s="1"/>
+    </x:row>
+    <x:row r="50" ht="24" customHeight="1">
+      <x:c r="A50" s="1"/>
+      <x:c r="B50" s="1"/>
+      <x:c r="C50" s="1"/>
+      <x:c r="D50" s="1"/>
+      <x:c r="E50" s="1"/>
+      <x:c r="F50" s="1"/>
+      <x:c r="G50" s="1"/>
+      <x:c r="H50" s="1"/>
+      <x:c r="I50" s="1"/>
+      <x:c r="J50" s="1"/>
+      <x:c r="K50" s="1"/>
+      <x:c r="L50" s="1"/>
+      <x:c r="M50" s="1"/>
+      <x:c r="N50" s="1"/>
+      <x:c r="O50" s="1"/>
+      <x:c r="P50" s="1"/>
+      <x:c r="Q50" s="1"/>
+      <x:c r="R50" s="1"/>
+      <x:c r="S50" s="1"/>
+      <x:c r="T50" s="1"/>
+    </x:row>
+    <x:row r="51" ht="24" customHeight="1">
+      <x:c r="A51" s="1" t="str">
+        <x:v>Grün: Ergebnisse. Bei K.O.-Verlängerung Partiepunkte im Tableau auf 2/0 setzen. Grau: keine Begegnung.</x:v>
+      </x:c>
+      <x:c r="B51" s="1"/>
+      <x:c r="C51" s="1"/>
+      <x:c r="D51" s="1"/>
+      <x:c r="E51" s="1"/>
+      <x:c r="F51" s="1"/>
+      <x:c r="G51" s="1"/>
+      <x:c r="H51" s="1"/>
+      <x:c r="I51" s="1"/>
+      <x:c r="J51" s="1"/>
+      <x:c r="K51" s="1"/>
+      <x:c r="L51" s="1"/>
+      <x:c r="M51" s="1"/>
+      <x:c r="N51" s="1"/>
+      <x:c r="O51" s="1"/>
+      <x:c r="P51" s="1"/>
+      <x:c r="Q51" s="1"/>
+      <x:c r="R51" s="1"/>
+      <x:c r="S51" s="1"/>
+      <x:c r="T51" s="1"/>
+    </x:row>
+    <x:row r="52" ht="24" customHeight="1">
+      <x:c r="A52" s="1"/>
+      <x:c r="B52" s="1"/>
+      <x:c r="C52" s="1"/>
+      <x:c r="D52" s="1"/>
+      <x:c r="E52" s="1"/>
+      <x:c r="F52" s="1"/>
+      <x:c r="G52" s="1"/>
+      <x:c r="H52" s="1"/>
+      <x:c r="I52" s="1"/>
+      <x:c r="J52" s="1"/>
+      <x:c r="K52" s="1"/>
+      <x:c r="L52" s="1"/>
+      <x:c r="M52" s="1"/>
+      <x:c r="N52" s="1"/>
+      <x:c r="O52" s="1"/>
+      <x:c r="P52" s="1"/>
+      <x:c r="Q52" s="1"/>
+      <x:c r="R52" s="1"/>
+      <x:c r="S52" s="1"/>
+      <x:c r="T52" s="1"/>
+    </x:row>
+    <x:row r="53" ht="24" customHeight="1">
+      <x:c r="A53" s="1"/>
+      <x:c r="B53" s="1"/>
+      <x:c r="C53" s="1"/>
+      <x:c r="D53" s="1"/>
+      <x:c r="E53" s="1"/>
+      <x:c r="F53" s="1"/>
+      <x:c r="G53" s="1"/>
+      <x:c r="H53" s="1"/>
+      <x:c r="I53" s="1"/>
+      <x:c r="J53" s="1"/>
+      <x:c r="K53" s="1"/>
+      <x:c r="L53" s="1"/>
+      <x:c r="M53" s="1"/>
+      <x:c r="N53" s="1"/>
+      <x:c r="O53" s="1"/>
+      <x:c r="P53" s="1"/>
+      <x:c r="Q53" s="1"/>
+      <x:c r="R53" s="1"/>
+      <x:c r="S53" s="1"/>
+      <x:c r="T53" s="1"/>
+    </x:row>
+    <x:row r="54" ht="24" customHeight="1">
+      <x:c r="A54" s="1"/>
+      <x:c r="B54" s="1"/>
+      <x:c r="C54" s="1"/>
+      <x:c r="D54" s="1"/>
+      <x:c r="E54" s="1"/>
+      <x:c r="F54" s="1"/>
+      <x:c r="G54" s="1"/>
+      <x:c r="H54" s="1"/>
+      <x:c r="I54" s="1"/>
+      <x:c r="J54" s="1"/>
+      <x:c r="K54" s="1"/>
+      <x:c r="L54" s="1"/>
+      <x:c r="M54" s="1"/>
+      <x:c r="N54" s="1"/>
+      <x:c r="O54" s="1"/>
+      <x:c r="P54" s="1"/>
+      <x:c r="Q54" s="1"/>
+      <x:c r="R54" s="1"/>
+      <x:c r="S54" s="1"/>
+      <x:c r="T54" s="1"/>
+    </x:row>
+    <x:row r="55" ht="24" customHeight="1">
+      <x:c r="A55" s="1"/>
+      <x:c r="B55" s="1"/>
+      <x:c r="C55" s="1"/>
+      <x:c r="D55" s="1"/>
+      <x:c r="E55" s="1"/>
+      <x:c r="F55" s="1"/>
+      <x:c r="G55" s="1"/>
+      <x:c r="H55" s="1"/>
+      <x:c r="I55" s="1"/>
+      <x:c r="J55" s="1"/>
+      <x:c r="K55" s="1"/>
+      <x:c r="L55" s="1"/>
+      <x:c r="M55" s="1"/>
+      <x:c r="N55" s="1"/>
+      <x:c r="O55" s="1"/>
+      <x:c r="P55" s="1"/>
+      <x:c r="Q55" s="1"/>
+      <x:c r="R55" s="1"/>
+      <x:c r="S55" s="1"/>
+      <x:c r="T55" s="1"/>
+    </x:row>
+    <x:row r="56" ht="24" customHeight="1">
+      <x:c r="A56" s="1"/>
+      <x:c r="B56" s="1"/>
+      <x:c r="C56" s="1"/>
+      <x:c r="D56" s="1"/>
+      <x:c r="E56" s="1"/>
+      <x:c r="F56" s="1"/>
+      <x:c r="G56" s="1"/>
+      <x:c r="H56" s="1"/>
+      <x:c r="I56" s="1"/>
+      <x:c r="J56" s="1"/>
+      <x:c r="K56" s="1"/>
+      <x:c r="L56" s="1"/>
+      <x:c r="M56" s="1"/>
+      <x:c r="N56" s="1"/>
+      <x:c r="O56" s="1"/>
+      <x:c r="P56" s="1"/>
+      <x:c r="Q56" s="1"/>
+      <x:c r="R56" s="1"/>
+      <x:c r="S56" s="1"/>
+      <x:c r="T56" s="1"/>
+    </x:row>
+    <x:row r="57" ht="24" customHeight="1">
+      <x:c r="A57" s="1"/>
+      <x:c r="B57" s="1"/>
+      <x:c r="C57" s="1"/>
+      <x:c r="D57" s="1"/>
+      <x:c r="E57" s="1"/>
+      <x:c r="F57" s="1"/>
+      <x:c r="G57" s="1"/>
+      <x:c r="H57" s="1"/>
+      <x:c r="I57" s="1"/>
+      <x:c r="J57" s="1"/>
+      <x:c r="K57" s="1"/>
+      <x:c r="L57" s="1"/>
+      <x:c r="M57" s="1"/>
+      <x:c r="N57" s="1"/>
+      <x:c r="O57" s="1"/>
+      <x:c r="P57" s="1"/>
+      <x:c r="Q57" s="1"/>
+      <x:c r="R57" s="1"/>
+      <x:c r="S57" s="1"/>
+      <x:c r="T57" s="1"/>
+    </x:row>
+    <x:row r="58" ht="24" customHeight="1">
+      <x:c r="A58" s="1"/>
+      <x:c r="B58" s="1"/>
+      <x:c r="C58" s="1"/>
+      <x:c r="D58" s="1"/>
+      <x:c r="E58" s="1"/>
+      <x:c r="F58" s="1"/>
+      <x:c r="G58" s="1"/>
+      <x:c r="H58" s="1"/>
+      <x:c r="I58" s="1"/>
+      <x:c r="J58" s="1"/>
+      <x:c r="K58" s="1"/>
+      <x:c r="L58" s="1"/>
+      <x:c r="M58" s="1"/>
+      <x:c r="N58" s="1"/>
+      <x:c r="O58" s="1"/>
+      <x:c r="P58" s="1"/>
+      <x:c r="Q58" s="1"/>
+      <x:c r="R58" s="1"/>
+      <x:c r="S58" s="1"/>
+      <x:c r="T58" s="1"/>
+    </x:row>
+    <x:row r="59" ht="24" customHeight="1">
+      <x:c r="A59" s="1"/>
+      <x:c r="B59" s="1"/>
+      <x:c r="C59" s="1"/>
+      <x:c r="D59" s="1"/>
+      <x:c r="E59" s="1"/>
+      <x:c r="F59" s="1"/>
+      <x:c r="G59" s="1"/>
+      <x:c r="H59" s="1"/>
+      <x:c r="I59" s="1"/>
+      <x:c r="J59" s="1"/>
+      <x:c r="K59" s="1"/>
+      <x:c r="L59" s="1"/>
+      <x:c r="M59" s="1"/>
+      <x:c r="N59" s="1"/>
+      <x:c r="O59" s="1"/>
+      <x:c r="P59" s="1"/>
+      <x:c r="Q59" s="1"/>
+      <x:c r="R59" s="1"/>
+      <x:c r="S59" s="1"/>
+      <x:c r="T59" s="1"/>
+    </x:row>
+    <x:row r="60" ht="24" customHeight="1">
+      <x:c r="A60" s="1"/>
+      <x:c r="B60" s="1"/>
+      <x:c r="C60" s="1"/>
+      <x:c r="D60" s="1"/>
+      <x:c r="E60" s="1"/>
+      <x:c r="F60" s="1"/>
+      <x:c r="G60" s="1"/>
+      <x:c r="H60" s="1"/>
+      <x:c r="I60" s="1"/>
+      <x:c r="J60" s="1"/>
+      <x:c r="K60" s="1"/>
+      <x:c r="L60" s="1"/>
+      <x:c r="M60" s="1"/>
+      <x:c r="N60" s="1"/>
+      <x:c r="O60" s="1"/>
+      <x:c r="P60" s="1"/>
+      <x:c r="Q60" s="1"/>
+      <x:c r="R60" s="1"/>
+      <x:c r="S60" s="1"/>
+      <x:c r="T60" s="1"/>
+    </x:row>
+    <x:row r="61" ht="24" customHeight="1">
+      <x:c r="A61" s="1"/>
+      <x:c r="B61" s="1"/>
+      <x:c r="C61" s="1"/>
+      <x:c r="D61" s="1"/>
+      <x:c r="E61" s="1"/>
+      <x:c r="F61" s="1"/>
+      <x:c r="G61" s="1"/>
+      <x:c r="H61" s="1"/>
+      <x:c r="I61" s="1"/>
+      <x:c r="J61" s="1"/>
+      <x:c r="K61" s="1"/>
+      <x:c r="L61" s="1"/>
+      <x:c r="M61" s="1"/>
+      <x:c r="N61" s="1"/>
+      <x:c r="O61" s="1"/>
+      <x:c r="P61" s="1"/>
+      <x:c r="Q61" s="1"/>
+      <x:c r="R61" s="1"/>
+      <x:c r="S61" s="1"/>
+      <x:c r="T61" s="1"/>
+    </x:row>
+    <x:row r="62" ht="24" customHeight="1">
+      <x:c r="A62" s="1"/>
+      <x:c r="B62" s="1"/>
+      <x:c r="C62" s="1"/>
+      <x:c r="D62" s="1"/>
+      <x:c r="E62" s="1"/>
+      <x:c r="F62" s="1"/>
+      <x:c r="G62" s="1"/>
+      <x:c r="H62" s="1"/>
+      <x:c r="I62" s="1"/>
+      <x:c r="J62" s="1"/>
+      <x:c r="K62" s="1"/>
+      <x:c r="L62" s="1"/>
+      <x:c r="M62" s="1"/>
+      <x:c r="N62" s="1"/>
+      <x:c r="O62" s="1"/>
+      <x:c r="P62" s="1"/>
+      <x:c r="Q62" s="1"/>
+      <x:c r="R62" s="1"/>
+      <x:c r="S62" s="1"/>
+      <x:c r="T62" s="1"/>
+    </x:row>
+    <x:row r="63" ht="24" customHeight="1">
+      <x:c r="A63" s="1"/>
+      <x:c r="B63" s="1"/>
+      <x:c r="C63" s="1"/>
+      <x:c r="D63" s="1"/>
+      <x:c r="E63" s="1"/>
+      <x:c r="F63" s="1"/>
+      <x:c r="G63" s="1"/>
+      <x:c r="H63" s="1"/>
+      <x:c r="I63" s="1"/>
+      <x:c r="J63" s="1"/>
+      <x:c r="K63" s="1"/>
+      <x:c r="L63" s="1"/>
+      <x:c r="M63" s="1"/>
+      <x:c r="N63" s="1"/>
+      <x:c r="O63" s="1"/>
+      <x:c r="P63" s="1"/>
+      <x:c r="Q63" s="1"/>
+      <x:c r="R63" s="1"/>
+      <x:c r="S63" s="1"/>
+      <x:c r="T63" s="1"/>
+    </x:row>
+    <x:row r="64" ht="24" customHeight="1">
+      <x:c r="A64" s="1"/>
+      <x:c r="B64" s="1"/>
+      <x:c r="C64" s="1"/>
+      <x:c r="D64" s="1"/>
+      <x:c r="E64" s="1"/>
+      <x:c r="F64" s="1"/>
+      <x:c r="G64" s="1"/>
+      <x:c r="H64" s="1"/>
+      <x:c r="I64" s="1"/>
+      <x:c r="J64" s="1"/>
+      <x:c r="K64" s="1"/>
+      <x:c r="L64" s="1"/>
+      <x:c r="M64" s="1"/>
+      <x:c r="N64" s="1"/>
+      <x:c r="O64" s="1"/>
+      <x:c r="P64" s="1"/>
+      <x:c r="Q64" s="1"/>
+      <x:c r="R64" s="1"/>
+      <x:c r="S64" s="1"/>
+      <x:c r="T64" s="1"/>
+    </x:row>
+    <x:row r="65" ht="24" customHeight="1">
+      <x:c r="A65" s="1"/>
+      <x:c r="B65" s="1"/>
+      <x:c r="C65" s="1"/>
+      <x:c r="D65" s="1"/>
+      <x:c r="E65" s="1"/>
+      <x:c r="F65" s="1"/>
+      <x:c r="G65" s="1"/>
+      <x:c r="H65" s="1"/>
+      <x:c r="I65" s="1"/>
+      <x:c r="J65" s="1"/>
+      <x:c r="K65" s="1"/>
+      <x:c r="L65" s="1"/>
+      <x:c r="M65" s="1"/>
+      <x:c r="N65" s="1"/>
+      <x:c r="O65" s="1"/>
+      <x:c r="P65" s="1"/>
+      <x:c r="Q65" s="1"/>
+      <x:c r="R65" s="1"/>
+      <x:c r="S65" s="1"/>
+      <x:c r="T65" s="1"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="D1:P1"/>
-    <x:mergeCell ref="S1:T1"/>
     <x:mergeCell ref="S2:T2"/>
+    <x:mergeCell ref="A3:T3"/>
+    <x:mergeCell ref="B4:C4"/>
+    <x:mergeCell ref="A5:A7"/>
+    <x:mergeCell ref="B6:C6"/>
+    <x:mergeCell ref="D6:E6"/>
+    <x:mergeCell ref="F6:G6"/>
+    <x:mergeCell ref="H6:I6"/>
+    <x:mergeCell ref="N5:N7"/>
+    <x:mergeCell ref="O5:O7"/>
+    <x:mergeCell ref="P5:P7"/>
+    <x:mergeCell ref="Q5:Q7"/>
+    <x:mergeCell ref="R5:R7"/>
+    <x:mergeCell ref="S5:S7"/>
+    <x:mergeCell ref="T5:T7"/>
+    <x:mergeCell ref="D4:E4"/>
+    <x:mergeCell ref="A8:A10"/>
+    <x:mergeCell ref="B9:C9"/>
+    <x:mergeCell ref="D9:E9"/>
+    <x:mergeCell ref="F9:G9"/>
+    <x:mergeCell ref="H9:I9"/>
+    <x:mergeCell ref="N8:N10"/>
+    <x:mergeCell ref="O8:O10"/>
+    <x:mergeCell ref="P8:P10"/>
+    <x:mergeCell ref="Q8:Q10"/>
+    <x:mergeCell ref="R8:R10"/>
+    <x:mergeCell ref="S8:S10"/>
+    <x:mergeCell ref="T8:T10"/>
+    <x:mergeCell ref="F4:G4"/>
+    <x:mergeCell ref="A11:A13"/>
+    <x:mergeCell ref="B12:C12"/>
+    <x:mergeCell ref="D12:E12"/>
+    <x:mergeCell ref="F12:G12"/>
+    <x:mergeCell ref="H12:I12"/>
+    <x:mergeCell ref="N11:N13"/>
+    <x:mergeCell ref="O11:O13"/>
+    <x:mergeCell ref="P11:P13"/>
+    <x:mergeCell ref="Q11:Q13"/>
+    <x:mergeCell ref="R11:R13"/>
+    <x:mergeCell ref="S11:S13"/>
+    <x:mergeCell ref="T11:T13"/>
+    <x:mergeCell ref="H4:I4"/>
+    <x:mergeCell ref="A14:A16"/>
+    <x:mergeCell ref="B15:C15"/>
+    <x:mergeCell ref="D15:E15"/>
+    <x:mergeCell ref="F15:G15"/>
+    <x:mergeCell ref="H15:I15"/>
+    <x:mergeCell ref="N14:N16"/>
+    <x:mergeCell ref="O14:O16"/>
+    <x:mergeCell ref="P14:P16"/>
+    <x:mergeCell ref="Q14:Q16"/>
+    <x:mergeCell ref="R14:R16"/>
+    <x:mergeCell ref="S14:S16"/>
+    <x:mergeCell ref="T14:T16"/>
+    <x:mergeCell ref="A19:T19"/>
+    <x:mergeCell ref="B20:C20"/>
+    <x:mergeCell ref="A21:A23"/>
+    <x:mergeCell ref="B22:C22"/>
+    <x:mergeCell ref="D22:E22"/>
+    <x:mergeCell ref="F22:G22"/>
+    <x:mergeCell ref="H22:I22"/>
+    <x:mergeCell ref="N21:N23"/>
+    <x:mergeCell ref="O21:O23"/>
+    <x:mergeCell ref="P21:P23"/>
+    <x:mergeCell ref="Q21:Q23"/>
+    <x:mergeCell ref="R21:R23"/>
+    <x:mergeCell ref="S21:S23"/>
+    <x:mergeCell ref="T21:T23"/>
+    <x:mergeCell ref="D20:E20"/>
+    <x:mergeCell ref="A24:A26"/>
+    <x:mergeCell ref="B25:C25"/>
+    <x:mergeCell ref="D25:E25"/>
+    <x:mergeCell ref="F25:G25"/>
+    <x:mergeCell ref="H25:I25"/>
+    <x:mergeCell ref="N24:N26"/>
+    <x:mergeCell ref="O24:O26"/>
+    <x:mergeCell ref="P24:P26"/>
+    <x:mergeCell ref="Q24:Q26"/>
+    <x:mergeCell ref="R24:R26"/>
+    <x:mergeCell ref="S24:S26"/>
+    <x:mergeCell ref="T24:T26"/>
+    <x:mergeCell ref="F20:G20"/>
+    <x:mergeCell ref="A27:A29"/>
+    <x:mergeCell ref="B28:C28"/>
+    <x:mergeCell ref="D28:E28"/>
+    <x:mergeCell ref="F28:G28"/>
+    <x:mergeCell ref="H28:I28"/>
+    <x:mergeCell ref="N27:N29"/>
+    <x:mergeCell ref="O27:O29"/>
+    <x:mergeCell ref="P27:P29"/>
+    <x:mergeCell ref="Q27:Q29"/>
+    <x:mergeCell ref="R27:R29"/>
+    <x:mergeCell ref="S27:S29"/>
+    <x:mergeCell ref="T27:T29"/>
+    <x:mergeCell ref="H20:I20"/>
+    <x:mergeCell ref="A30:A32"/>
+    <x:mergeCell ref="B31:C31"/>
+    <x:mergeCell ref="D31:E31"/>
+    <x:mergeCell ref="F31:G31"/>
+    <x:mergeCell ref="H31:I31"/>
+    <x:mergeCell ref="N30:N32"/>
+    <x:mergeCell ref="O30:O32"/>
+    <x:mergeCell ref="P30:P32"/>
+    <x:mergeCell ref="Q30:Q32"/>
+    <x:mergeCell ref="R30:R32"/>
+    <x:mergeCell ref="S30:S32"/>
+    <x:mergeCell ref="T30:T32"/>
+    <x:mergeCell ref="A35:T35"/>
+    <x:mergeCell ref="B36:C36"/>
+    <x:mergeCell ref="A37:A39"/>
+    <x:mergeCell ref="B38:C38"/>
+    <x:mergeCell ref="D38:E38"/>
+    <x:mergeCell ref="F38:G38"/>
+    <x:mergeCell ref="H38:I38"/>
+    <x:mergeCell ref="N37:N39"/>
+    <x:mergeCell ref="O37:O39"/>
+    <x:mergeCell ref="P37:P39"/>
+    <x:mergeCell ref="Q37:Q39"/>
+    <x:mergeCell ref="R37:R39"/>
+    <x:mergeCell ref="S37:S39"/>
+    <x:mergeCell ref="T37:T39"/>
+    <x:mergeCell ref="D36:E36"/>
+    <x:mergeCell ref="A40:A42"/>
+    <x:mergeCell ref="B41:C41"/>
+    <x:mergeCell ref="D41:E41"/>
+    <x:mergeCell ref="F41:G41"/>
+    <x:mergeCell ref="H41:I41"/>
+    <x:mergeCell ref="N40:N42"/>
+    <x:mergeCell ref="O40:O42"/>
+    <x:mergeCell ref="P40:P42"/>
+    <x:mergeCell ref="Q40:Q42"/>
+    <x:mergeCell ref="R40:R42"/>
+    <x:mergeCell ref="S40:S42"/>
+    <x:mergeCell ref="T40:T42"/>
+    <x:mergeCell ref="F36:G36"/>
+    <x:mergeCell ref="A43:A45"/>
+    <x:mergeCell ref="B44:C44"/>
+    <x:mergeCell ref="D44:E44"/>
+    <x:mergeCell ref="F44:G44"/>
+    <x:mergeCell ref="H44:I44"/>
+    <x:mergeCell ref="N43:N45"/>
+    <x:mergeCell ref="O43:O45"/>
+    <x:mergeCell ref="P43:P45"/>
+    <x:mergeCell ref="Q43:Q45"/>
+    <x:mergeCell ref="R43:R45"/>
+    <x:mergeCell ref="S43:S45"/>
+    <x:mergeCell ref="T43:T45"/>
+    <x:mergeCell ref="H36:I36"/>
+    <x:mergeCell ref="A46:A48"/>
+    <x:mergeCell ref="B47:C47"/>
+    <x:mergeCell ref="D47:E47"/>
+    <x:mergeCell ref="F47:G47"/>
+    <x:mergeCell ref="H47:I47"/>
+    <x:mergeCell ref="N46:N48"/>
+    <x:mergeCell ref="O46:O48"/>
+    <x:mergeCell ref="P46:P48"/>
+    <x:mergeCell ref="Q46:Q48"/>
+    <x:mergeCell ref="R46:R48"/>
+    <x:mergeCell ref="S46:S48"/>
+    <x:mergeCell ref="T46:T48"/>
+    <x:mergeCell ref="A51:T51"/>
   </x:mergeCells>
   <x:pageMargins left="0.2" right="0.2" top="0.3" bottom="0.3" header="0.1" footer="0.1"/>
-  <x:pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="1"/>
+  <x:pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <x:rowBreaks count="2" manualBreakCount="2">
+    <x:brk id="18" min="0" max="16383" man="1"/>
+    <x:brk id="34" min="0" max="16383" man="1"/>
+  </x:rowBreaks>
 </x:worksheet>
 </file>
 
@@ -6535,7 +7362,7 @@
     </x:row>
     <x:row r="18" ht="24" customHeight="1">
       <x:c r="A18" s="2" t="str">
-        <x:f>Finalrunde!C5</x:f>
+        <x:f>"HF1"</x:f>
         <x:v>HF1</x:v>
       </x:c>
       <x:c r="B18" s="2" t="n">
@@ -6545,28 +7372,28 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D18" s="2" t="str">
+        <x:f>IF(Finalrunde!U4="","",INDEX(Teilnehmer!$C$2:$C$10,MATCH(Finalrunde!U4,Teilnehmer!$A$2:$A$10,0)))</x:f>
+      </x:c>
+      <x:c r="E18" s="2" t="str">
         <x:f>IF(Finalrunde!U5="","",INDEX(Teilnehmer!$C$2:$C$10,MATCH(Finalrunde!U5,Teilnehmer!$A$2:$A$10,0)))</x:f>
       </x:c>
-      <x:c r="E18" s="2" t="str">
-        <x:f>IF(Finalrunde!V5="","",INDEX(Teilnehmer!$C$2:$C$10,MATCH(Finalrunde!V5,Teilnehmer!$A$2:$A$10,0)))</x:f>
-      </x:c>
       <x:c r="F18" s="2" t="str">
+        <x:f>IF(ISNUMBER(Finalrunde!D5),Finalrunde!D5,"")</x:f>
+      </x:c>
+      <x:c r="G18" s="2" t="str">
+        <x:f>IF(ISNUMBER(Finalrunde!B8),Finalrunde!B8,"")</x:f>
+      </x:c>
+      <x:c r="H18" s="2" t="str">
         <x:f>IF(ISNUMBER(Finalrunde!E5),Finalrunde!E5,"")</x:f>
       </x:c>
-      <x:c r="G18" s="2" t="str">
-        <x:f>IF(ISNUMBER(Finalrunde!J5),Finalrunde!J5,"")</x:f>
-      </x:c>
-      <x:c r="H18" s="2" t="str">
-        <x:f>IF(ISNUMBER(Finalrunde!F5),Finalrunde!F5,"")</x:f>
-      </x:c>
       <x:c r="I18" s="2" t="str">
-        <x:f>IF(ISNUMBER(Finalrunde!K5),Finalrunde!K5,"")</x:f>
+        <x:f>IF(ISNUMBER(Finalrunde!C8),Finalrunde!C8,"")</x:f>
       </x:c>
       <x:c r="J18" s="2" t="str">
-        <x:f>IF(ISNUMBER(Finalrunde!G5),Finalrunde!G5,"")</x:f>
+        <x:f>IF(ISNUMBER(Finalrunde!E7),Finalrunde!E7,"")</x:f>
       </x:c>
       <x:c r="K18" s="2" t="str">
-        <x:f>IF(ISNUMBER(Finalrunde!L5),Finalrunde!L5,"")</x:f>
+        <x:f>IF(ISNUMBER(Finalrunde!C10),Finalrunde!C10,"")</x:f>
       </x:c>
       <x:c r="L18" s="6" t="str">
         <x:f>IF(ISNUMBER('Gruppe A'!S2),'Gruppe A'!S2,"")</x:f>
@@ -6582,7 +7409,7 @@
     </x:row>
     <x:row r="19" ht="24" customHeight="1">
       <x:c r="A19" s="2" t="str">
-        <x:f>Finalrunde!C6</x:f>
+        <x:f>"HF2"</x:f>
         <x:v>HF2</x:v>
       </x:c>
       <x:c r="B19" s="2" t="n">
@@ -6595,25 +7422,25 @@
         <x:f>IF(Finalrunde!U6="","",INDEX(Teilnehmer!$C$2:$C$10,MATCH(Finalrunde!U6,Teilnehmer!$A$2:$A$10,0)))</x:f>
       </x:c>
       <x:c r="E19" s="2" t="str">
-        <x:f>IF(Finalrunde!V6="","",INDEX(Teilnehmer!$C$2:$C$10,MATCH(Finalrunde!V6,Teilnehmer!$A$2:$A$10,0)))</x:f>
+        <x:f>IF(Finalrunde!U7="","",INDEX(Teilnehmer!$C$2:$C$10,MATCH(Finalrunde!U7,Teilnehmer!$A$2:$A$10,0)))</x:f>
       </x:c>
       <x:c r="F19" s="2" t="str">
-        <x:f>IF(ISNUMBER(Finalrunde!E6),Finalrunde!E6,"")</x:f>
+        <x:f>IF(ISNUMBER(Finalrunde!H11),Finalrunde!H11,"")</x:f>
       </x:c>
       <x:c r="G19" s="2" t="str">
-        <x:f>IF(ISNUMBER(Finalrunde!J6),Finalrunde!J6,"")</x:f>
+        <x:f>IF(ISNUMBER(Finalrunde!F14),Finalrunde!F14,"")</x:f>
       </x:c>
       <x:c r="H19" s="2" t="str">
-        <x:f>IF(ISNUMBER(Finalrunde!F6),Finalrunde!F6,"")</x:f>
+        <x:f>IF(ISNUMBER(Finalrunde!I11),Finalrunde!I11,"")</x:f>
       </x:c>
       <x:c r="I19" s="2" t="str">
-        <x:f>IF(ISNUMBER(Finalrunde!K6),Finalrunde!K6,"")</x:f>
+        <x:f>IF(ISNUMBER(Finalrunde!G14),Finalrunde!G14,"")</x:f>
       </x:c>
       <x:c r="J19" s="2" t="str">
-        <x:f>IF(ISNUMBER(Finalrunde!G6),Finalrunde!G6,"")</x:f>
+        <x:f>IF(ISNUMBER(Finalrunde!I13),Finalrunde!I13,"")</x:f>
       </x:c>
       <x:c r="K19" s="2" t="str">
-        <x:f>IF(ISNUMBER(Finalrunde!L6),Finalrunde!L6,"")</x:f>
+        <x:f>IF(ISNUMBER(Finalrunde!G16),Finalrunde!G16,"")</x:f>
       </x:c>
       <x:c r="L19" s="6" t="str">
         <x:f>IF(ISNUMBER('Gruppe A'!S2),'Gruppe A'!S2,"")</x:f>
@@ -6629,7 +7456,7 @@
     </x:row>
     <x:row r="20" ht="24" customHeight="1">
       <x:c r="A20" s="2" t="str">
-        <x:f>Finalrunde!C7</x:f>
+        <x:f>"Platz 5–6"</x:f>
         <x:v>Platz 5–6</x:v>
       </x:c>
       <x:c r="B20" s="2" t="n">
@@ -6639,28 +7466,28 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D20" s="2" t="str">
-        <x:f>IF(Finalrunde!U7="","",INDEX(Teilnehmer!$C$2:$C$10,MATCH(Finalrunde!U7,Teilnehmer!$A$2:$A$10,0)))</x:f>
+        <x:f>IF(Finalrunde!U36="","",INDEX(Teilnehmer!$C$2:$C$10,MATCH(Finalrunde!U36,Teilnehmer!$A$2:$A$10,0)))</x:f>
       </x:c>
       <x:c r="E20" s="2" t="str">
-        <x:f>IF(Finalrunde!V7="","",INDEX(Teilnehmer!$C$2:$C$10,MATCH(Finalrunde!V7,Teilnehmer!$A$2:$A$10,0)))</x:f>
+        <x:f>IF(Finalrunde!U37="","",INDEX(Teilnehmer!$C$2:$C$10,MATCH(Finalrunde!U37,Teilnehmer!$A$2:$A$10,0)))</x:f>
       </x:c>
       <x:c r="F20" s="2" t="str">
-        <x:f>IF(ISNUMBER(Finalrunde!E7),Finalrunde!E7,"")</x:f>
+        <x:f>IF(ISNUMBER(Finalrunde!D37),Finalrunde!D37,"")</x:f>
       </x:c>
       <x:c r="G20" s="2" t="str">
-        <x:f>IF(ISNUMBER(Finalrunde!J7),Finalrunde!J7,"")</x:f>
+        <x:f>IF(ISNUMBER(Finalrunde!B40),Finalrunde!B40,"")</x:f>
       </x:c>
       <x:c r="H20" s="2" t="str">
-        <x:f>IF(ISNUMBER(Finalrunde!F7),Finalrunde!F7,"")</x:f>
+        <x:f>IF(ISNUMBER(Finalrunde!E37),Finalrunde!E37,"")</x:f>
       </x:c>
       <x:c r="I20" s="2" t="str">
-        <x:f>IF(ISNUMBER(Finalrunde!K7),Finalrunde!K7,"")</x:f>
+        <x:f>IF(ISNUMBER(Finalrunde!C40),Finalrunde!C40,"")</x:f>
       </x:c>
       <x:c r="J20" s="2" t="str">
-        <x:f>IF(ISNUMBER(Finalrunde!G7),Finalrunde!G7,"")</x:f>
+        <x:f>IF(ISNUMBER(Finalrunde!E39),Finalrunde!E39,"")</x:f>
       </x:c>
       <x:c r="K20" s="2" t="str">
-        <x:f>IF(ISNUMBER(Finalrunde!L7),Finalrunde!L7,"")</x:f>
+        <x:f>IF(ISNUMBER(Finalrunde!C42),Finalrunde!C42,"")</x:f>
       </x:c>
       <x:c r="L20" s="6" t="str">
         <x:f>IF(ISNUMBER('Gruppe A'!S2),'Gruppe A'!S2,"")</x:f>
@@ -6676,7 +7503,7 @@
     </x:row>
     <x:row r="21" ht="24" customHeight="1">
       <x:c r="A21" s="2" t="str">
-        <x:f>Finalrunde!C8</x:f>
+        <x:f>"Platz 7–8"</x:f>
         <x:v>Platz 7–8</x:v>
       </x:c>
       <x:c r="B21" s="2" t="n">
@@ -6686,28 +7513,28 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D21" s="2" t="str">
-        <x:f>IF(Finalrunde!U8="","",INDEX(Teilnehmer!$C$2:$C$10,MATCH(Finalrunde!U8,Teilnehmer!$A$2:$A$10,0)))</x:f>
+        <x:f>IF(Finalrunde!U38="","",INDEX(Teilnehmer!$C$2:$C$10,MATCH(Finalrunde!U38,Teilnehmer!$A$2:$A$10,0)))</x:f>
       </x:c>
       <x:c r="E21" s="2" t="str">
-        <x:f>IF(Finalrunde!V8="","",INDEX(Teilnehmer!$C$2:$C$10,MATCH(Finalrunde!V8,Teilnehmer!$A$2:$A$10,0)))</x:f>
+        <x:f>IF(Finalrunde!U39="","",INDEX(Teilnehmer!$C$2:$C$10,MATCH(Finalrunde!U39,Teilnehmer!$A$2:$A$10,0)))</x:f>
       </x:c>
       <x:c r="F21" s="2" t="str">
-        <x:f>IF(ISNUMBER(Finalrunde!E8),Finalrunde!E8,"")</x:f>
+        <x:f>IF(ISNUMBER(Finalrunde!H43),Finalrunde!H43,"")</x:f>
       </x:c>
       <x:c r="G21" s="2" t="str">
-        <x:f>IF(ISNUMBER(Finalrunde!J8),Finalrunde!J8,"")</x:f>
+        <x:f>IF(ISNUMBER(Finalrunde!F46),Finalrunde!F46,"")</x:f>
       </x:c>
       <x:c r="H21" s="2" t="str">
-        <x:f>IF(ISNUMBER(Finalrunde!F8),Finalrunde!F8,"")</x:f>
+        <x:f>IF(ISNUMBER(Finalrunde!I43),Finalrunde!I43,"")</x:f>
       </x:c>
       <x:c r="I21" s="2" t="str">
-        <x:f>IF(ISNUMBER(Finalrunde!K8),Finalrunde!K8,"")</x:f>
+        <x:f>IF(ISNUMBER(Finalrunde!G46),Finalrunde!G46,"")</x:f>
       </x:c>
       <x:c r="J21" s="2" t="str">
-        <x:f>IF(ISNUMBER(Finalrunde!G8),Finalrunde!G8,"")</x:f>
+        <x:f>IF(ISNUMBER(Finalrunde!I45),Finalrunde!I45,"")</x:f>
       </x:c>
       <x:c r="K21" s="2" t="str">
-        <x:f>IF(ISNUMBER(Finalrunde!L8),Finalrunde!L8,"")</x:f>
+        <x:f>IF(ISNUMBER(Finalrunde!G48),Finalrunde!G48,"")</x:f>
       </x:c>
       <x:c r="L21" s="6" t="str">
         <x:f>IF(ISNUMBER('Gruppe A'!S2),'Gruppe A'!S2,"")</x:f>
@@ -6723,7 +7550,7 @@
     </x:row>
     <x:row r="22" ht="24" customHeight="1">
       <x:c r="A22" s="2" t="str">
-        <x:f>Finalrunde!C9</x:f>
+        <x:f>"Finale"</x:f>
         <x:v>Finale</x:v>
       </x:c>
       <x:c r="B22" s="2" t="n">
@@ -6733,28 +7560,28 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D22" s="2" t="str">
-        <x:f>IF(Finalrunde!U9="","",INDEX(Teilnehmer!$C$2:$C$10,MATCH(Finalrunde!U9,Teilnehmer!$A$2:$A$10,0)))</x:f>
+        <x:f>IF(Finalrunde!U20="","",INDEX(Teilnehmer!$C$2:$C$10,MATCH(Finalrunde!U20,Teilnehmer!$A$2:$A$10,0)))</x:f>
       </x:c>
       <x:c r="E22" s="2" t="str">
-        <x:f>IF(Finalrunde!V9="","",INDEX(Teilnehmer!$C$2:$C$10,MATCH(Finalrunde!V9,Teilnehmer!$A$2:$A$10,0)))</x:f>
+        <x:f>IF(Finalrunde!U21="","",INDEX(Teilnehmer!$C$2:$C$10,MATCH(Finalrunde!U21,Teilnehmer!$A$2:$A$10,0)))</x:f>
       </x:c>
       <x:c r="F22" s="2" t="str">
-        <x:f>IF(ISNUMBER(Finalrunde!E9),Finalrunde!E9,"")</x:f>
+        <x:f>IF(ISNUMBER(Finalrunde!D21),Finalrunde!D21,"")</x:f>
       </x:c>
       <x:c r="G22" s="2" t="str">
-        <x:f>IF(ISNUMBER(Finalrunde!J9),Finalrunde!J9,"")</x:f>
+        <x:f>IF(ISNUMBER(Finalrunde!B24),Finalrunde!B24,"")</x:f>
       </x:c>
       <x:c r="H22" s="2" t="str">
-        <x:f>IF(ISNUMBER(Finalrunde!F9),Finalrunde!F9,"")</x:f>
+        <x:f>IF(ISNUMBER(Finalrunde!E21),Finalrunde!E21,"")</x:f>
       </x:c>
       <x:c r="I22" s="2" t="str">
-        <x:f>IF(ISNUMBER(Finalrunde!K9),Finalrunde!K9,"")</x:f>
+        <x:f>IF(ISNUMBER(Finalrunde!C24),Finalrunde!C24,"")</x:f>
       </x:c>
       <x:c r="J22" s="2" t="str">
-        <x:f>IF(ISNUMBER(Finalrunde!G9),Finalrunde!G9,"")</x:f>
+        <x:f>IF(ISNUMBER(Finalrunde!E23),Finalrunde!E23,"")</x:f>
       </x:c>
       <x:c r="K22" s="2" t="str">
-        <x:f>IF(ISNUMBER(Finalrunde!L9),Finalrunde!L9,"")</x:f>
+        <x:f>IF(ISNUMBER(Finalrunde!C26),Finalrunde!C26,"")</x:f>
       </x:c>
       <x:c r="L22" s="6" t="str">
         <x:f>IF(ISNUMBER('Gruppe A'!S2),'Gruppe A'!S2,"")</x:f>
@@ -6770,7 +7597,7 @@
     </x:row>
     <x:row r="23" ht="24" customHeight="1">
       <x:c r="A23" s="2" t="str">
-        <x:f>Finalrunde!C10</x:f>
+        <x:f>"Platz 3–4"</x:f>
         <x:v>Platz 3–4</x:v>
       </x:c>
       <x:c r="B23" s="2" t="n">
@@ -6780,28 +7607,28 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D23" s="2" t="str">
-        <x:f>IF(Finalrunde!U10="","",INDEX(Teilnehmer!$C$2:$C$10,MATCH(Finalrunde!U10,Teilnehmer!$A$2:$A$10,0)))</x:f>
+        <x:f>IF(Finalrunde!U22="","",INDEX(Teilnehmer!$C$2:$C$10,MATCH(Finalrunde!U22,Teilnehmer!$A$2:$A$10,0)))</x:f>
       </x:c>
       <x:c r="E23" s="2" t="str">
-        <x:f>IF(Finalrunde!V10="","",INDEX(Teilnehmer!$C$2:$C$10,MATCH(Finalrunde!V10,Teilnehmer!$A$2:$A$10,0)))</x:f>
+        <x:f>IF(Finalrunde!U23="","",INDEX(Teilnehmer!$C$2:$C$10,MATCH(Finalrunde!U23,Teilnehmer!$A$2:$A$10,0)))</x:f>
       </x:c>
       <x:c r="F23" s="2" t="str">
-        <x:f>IF(ISNUMBER(Finalrunde!E10),Finalrunde!E10,"")</x:f>
+        <x:f>IF(ISNUMBER(Finalrunde!H27),Finalrunde!H27,"")</x:f>
       </x:c>
       <x:c r="G23" s="2" t="str">
-        <x:f>IF(ISNUMBER(Finalrunde!J10),Finalrunde!J10,"")</x:f>
+        <x:f>IF(ISNUMBER(Finalrunde!F30),Finalrunde!F30,"")</x:f>
       </x:c>
       <x:c r="H23" s="2" t="str">
-        <x:f>IF(ISNUMBER(Finalrunde!F10),Finalrunde!F10,"")</x:f>
+        <x:f>IF(ISNUMBER(Finalrunde!I27),Finalrunde!I27,"")</x:f>
       </x:c>
       <x:c r="I23" s="2" t="str">
-        <x:f>IF(ISNUMBER(Finalrunde!K10),Finalrunde!K10,"")</x:f>
+        <x:f>IF(ISNUMBER(Finalrunde!G30),Finalrunde!G30,"")</x:f>
       </x:c>
       <x:c r="J23" s="2" t="str">
-        <x:f>IF(ISNUMBER(Finalrunde!G10),Finalrunde!G10,"")</x:f>
+        <x:f>IF(ISNUMBER(Finalrunde!I29),Finalrunde!I29,"")</x:f>
       </x:c>
       <x:c r="K23" s="2" t="str">
-        <x:f>IF(ISNUMBER(Finalrunde!L10),Finalrunde!L10,"")</x:f>
+        <x:f>IF(ISNUMBER(Finalrunde!G32),Finalrunde!G32,"")</x:f>
       </x:c>
       <x:c r="L23" s="6" t="str">
         <x:f>IF(ISNUMBER('Gruppe A'!S2),'Gruppe A'!S2,"")</x:f>
@@ -7303,4 +8130,1708 @@
   <x:pageMargins left="0.2" right="0.2" top="0.3" bottom="0.3" header="0.1" footer="0.1"/>
   <x:pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="1"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:pageSetUpPr fitToPage="1"/>
+  </x:sheetPr>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="8" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="15" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="15" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="15" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="15" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="15" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="15" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="3" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="3" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="3" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="12" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="12" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="12" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="12" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="12" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="12" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="12" hidden="0" customWidth="1"/>
+    <x:col min="21" max="22" hidden="1" width="10" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="36" customHeight="1">
+      <x:c r="A1" s="1"/>
+      <x:c r="B1" s="1"/>
+      <x:c r="C1" s="1"/>
+      <x:c r="D1" s="43" t="str">
+        <x:v>T16a – Rangliste</x:v>
+      </x:c>
+      <x:c r="E1" s="43"/>
+      <x:c r="F1" s="43"/>
+      <x:c r="G1" s="43"/>
+      <x:c r="H1" s="43"/>
+      <x:c r="I1" s="43"/>
+      <x:c r="J1" s="43"/>
+      <x:c r="K1" s="43"/>
+      <x:c r="L1" s="43"/>
+      <x:c r="M1" s="43"/>
+      <x:c r="N1" s="43"/>
+      <x:c r="O1" s="43"/>
+      <x:c r="P1" s="43"/>
+      <x:c r="Q1" s="1"/>
+      <x:c r="R1" s="1"/>
+      <x:c r="S1" s="1"/>
+      <x:c r="T1" s="1"/>
+    </x:row>
+    <x:row r="2" ht="24" customHeight="1">
+      <x:c r="A2" s="1"/>
+      <x:c r="B2" s="1"/>
+      <x:c r="C2" s="1"/>
+      <x:c r="D2" s="1"/>
+      <x:c r="E2" s="1"/>
+      <x:c r="F2" s="1"/>
+      <x:c r="G2" s="1"/>
+      <x:c r="H2" s="1"/>
+      <x:c r="I2" s="1"/>
+      <x:c r="J2" s="1"/>
+      <x:c r="K2" s="1"/>
+      <x:c r="L2" s="1"/>
+      <x:c r="M2" s="1"/>
+      <x:c r="N2" s="1"/>
+      <x:c r="O2" s="1"/>
+      <x:c r="P2" s="1"/>
+      <x:c r="Q2" s="1"/>
+      <x:c r="R2" s="1" t="str">
+        <x:v>Datum:</x:v>
+      </x:c>
+      <x:c r="S2" s="44"/>
+      <x:c r="T2" s="1"/>
+    </x:row>
+    <x:row r="3" ht="24" customHeight="1">
+      <x:c r="A3" s="1"/>
+      <x:c r="B3" s="1"/>
+      <x:c r="C3" s="1"/>
+      <x:c r="D3" s="1"/>
+      <x:c r="E3" s="1"/>
+      <x:c r="F3" s="1"/>
+      <x:c r="G3" s="1"/>
+      <x:c r="H3" s="1"/>
+      <x:c r="I3" s="1"/>
+      <x:c r="J3" s="1"/>
+      <x:c r="K3" s="1"/>
+      <x:c r="L3" s="1"/>
+      <x:c r="M3" s="1"/>
+      <x:c r="N3" s="1"/>
+      <x:c r="O3" s="1"/>
+      <x:c r="P3" s="1"/>
+      <x:c r="Q3" s="1"/>
+      <x:c r="R3" s="1"/>
+      <x:c r="S3" s="1"/>
+      <x:c r="T3" s="1"/>
+    </x:row>
+    <x:row r="4" ht="40" customHeight="1">
+      <x:c r="A4" s="47" t="str">
+        <x:v>Platz</x:v>
+      </x:c>
+      <x:c r="B4" s="47" t="str">
+        <x:v>Spieler</x:v>
+      </x:c>
+      <x:c r="C4" s="47" t="str">
+        <x:v>Verein</x:v>
+      </x:c>
+      <x:c r="D4" s="47" t="str">
+        <x:v>Passnummer</x:v>
+      </x:c>
+      <x:c r="E4" s="47" t="str">
+        <x:v>Partiepunkte</x:v>
+      </x:c>
+      <x:c r="F4" s="47" t="str">
+        <x:v>Bälle</x:v>
+      </x:c>
+      <x:c r="G4" s="47" t="str">
+        <x:v>Aufnahmen</x:v>
+      </x:c>
+      <x:c r="H4" s="47" t="str">
+        <x:v>BED</x:v>
+      </x:c>
+      <x:c r="I4" s="47" t="str">
+        <x:v>DS</x:v>
+      </x:c>
+      <x:c r="J4" s="47" t="str">
+        <x:v>HS</x:v>
+      </x:c>
+      <x:c r="K4" s="1"/>
+      <x:c r="L4" s="1"/>
+      <x:c r="M4" s="1"/>
+      <x:c r="N4" s="1"/>
+      <x:c r="O4" s="1"/>
+      <x:c r="P4" s="1"/>
+      <x:c r="Q4" s="1"/>
+      <x:c r="R4" s="1"/>
+      <x:c r="S4" s="1"/>
+      <x:c r="T4" s="1"/>
+    </x:row>
+    <x:row r="5" ht="24" customHeight="1">
+      <x:c r="A5" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B5" s="1" t="str">
+        <x:f>IF(U5="","",INDEX(Teilnehmer!$B$2:$B$10,MATCH(U5,Teilnehmer!$A$2:$A$10,0)))</x:f>
+      </x:c>
+      <x:c r="C5" s="1" t="str">
+        <x:f>IF(U5="","",INDEX(Teilnehmer!$D$2:$D$10,MATCH(U5,Teilnehmer!$A$2:$A$10,0)))</x:f>
+      </x:c>
+      <x:c r="D5" s="1" t="str">
+        <x:f>IF(U5="","",INDEX(Teilnehmer!$C$2:$C$10,MATCH(U5,Teilnehmer!$A$2:$A$10,0)))</x:f>
+      </x:c>
+      <x:c r="E5" s="1" t="str">
+        <x:f>IF(U5="","",INDEX(Teilnehmer!$I$2:$I$10,MATCH(U5,Teilnehmer!$A$2:$A$10,0))+SUM(IF(Finalrunde!U4=U5,IF(ISNUMBER(Finalrunde!D6),Finalrunde!D6,0),0),IF(Finalrunde!U5=U5,IF(ISNUMBER(Finalrunde!B9),Finalrunde!B9,0),0),IF(Finalrunde!U6=U5,IF(ISNUMBER(Finalrunde!H12),Finalrunde!H12,0),0),IF(Finalrunde!U7=U5,IF(ISNUMBER(Finalrunde!F15),Finalrunde!F15,0),0),IF(Finalrunde!U20=U5,IF(ISNUMBER(Finalrunde!D22),Finalrunde!D22,0),0),IF(Finalrunde!U21=U5,IF(ISNUMBER(Finalrunde!B25),Finalrunde!B25,0),0),IF(Finalrunde!U22=U5,IF(ISNUMBER(Finalrunde!H28),Finalrunde!H28,0),0),IF(Finalrunde!U23=U5,IF(ISNUMBER(Finalrunde!F31),Finalrunde!F31,0),0),IF(Finalrunde!U36=U5,IF(ISNUMBER(Finalrunde!D38),Finalrunde!D38,0),0),IF(Finalrunde!U37=U5,IF(ISNUMBER(Finalrunde!B41),Finalrunde!B41,0),0),IF(Finalrunde!U38=U5,IF(ISNUMBER(Finalrunde!H44),Finalrunde!H44,0),0),IF(Finalrunde!U39=U5,IF(ISNUMBER(Finalrunde!F47),Finalrunde!F47,0),0)))</x:f>
+      </x:c>
+      <x:c r="F5" s="1" t="str">
+        <x:f>IF(U5="","",INDEX(Teilnehmer!$J$2:$J$10,MATCH(U5,Teilnehmer!$A$2:$A$10,0))+SUM(IF(Finalrunde!U4=U5,IF(ISNUMBER(Finalrunde!D5),Finalrunde!D5,0),0),IF(Finalrunde!U5=U5,IF(ISNUMBER(Finalrunde!B8),Finalrunde!B8,0),0),IF(Finalrunde!U6=U5,IF(ISNUMBER(Finalrunde!H11),Finalrunde!H11,0),0),IF(Finalrunde!U7=U5,IF(ISNUMBER(Finalrunde!F14),Finalrunde!F14,0),0),IF(Finalrunde!U20=U5,IF(ISNUMBER(Finalrunde!D21),Finalrunde!D21,0),0),IF(Finalrunde!U21=U5,IF(ISNUMBER(Finalrunde!B24),Finalrunde!B24,0),0),IF(Finalrunde!U22=U5,IF(ISNUMBER(Finalrunde!H27),Finalrunde!H27,0),0),IF(Finalrunde!U23=U5,IF(ISNUMBER(Finalrunde!F30),Finalrunde!F30,0),0),IF(Finalrunde!U36=U5,IF(ISNUMBER(Finalrunde!D37),Finalrunde!D37,0),0),IF(Finalrunde!U37=U5,IF(ISNUMBER(Finalrunde!B40),Finalrunde!B40,0),0),IF(Finalrunde!U38=U5,IF(ISNUMBER(Finalrunde!H43),Finalrunde!H43,0),0),IF(Finalrunde!U39=U5,IF(ISNUMBER(Finalrunde!F46),Finalrunde!F46,0),0)))</x:f>
+      </x:c>
+      <x:c r="G5" s="1" t="str">
+        <x:f>IF(U5="","",INDEX(Teilnehmer!$K$2:$K$10,MATCH(U5,Teilnehmer!$A$2:$A$10,0))+SUM(IF(Finalrunde!U4=U5,IF(ISNUMBER(Finalrunde!E5),Finalrunde!E5,0),0),IF(Finalrunde!U5=U5,IF(ISNUMBER(Finalrunde!C8),Finalrunde!C8,0),0),IF(Finalrunde!U6=U5,IF(ISNUMBER(Finalrunde!I11),Finalrunde!I11,0),0),IF(Finalrunde!U7=U5,IF(ISNUMBER(Finalrunde!G14),Finalrunde!G14,0),0),IF(Finalrunde!U20=U5,IF(ISNUMBER(Finalrunde!E21),Finalrunde!E21,0),0),IF(Finalrunde!U21=U5,IF(ISNUMBER(Finalrunde!C24),Finalrunde!C24,0),0),IF(Finalrunde!U22=U5,IF(ISNUMBER(Finalrunde!I27),Finalrunde!I27,0),0),IF(Finalrunde!U23=U5,IF(ISNUMBER(Finalrunde!G30),Finalrunde!G30,0),0),IF(Finalrunde!U36=U5,IF(ISNUMBER(Finalrunde!E37),Finalrunde!E37,0),0),IF(Finalrunde!U37=U5,IF(ISNUMBER(Finalrunde!C40),Finalrunde!C40,0),0),IF(Finalrunde!U38=U5,IF(ISNUMBER(Finalrunde!I43),Finalrunde!I43,0),0),IF(Finalrunde!U39=U5,IF(ISNUMBER(Finalrunde!G46),Finalrunde!G46,0),0)))</x:f>
+      </x:c>
+      <x:c r="H5" s="73" t="str">
+        <x:f>IF(U5="","",MAX(IF(U5=1,'Gruppe A'!Q4,0),IF(U5=4,'Gruppe A'!Q7,0),IF(U5=5,'Gruppe A'!Q10,0),IF(U5=8,'Gruppe A'!Q13,0),IF(U5=2,'Gruppe B'!Q4,0),IF(U5=3,'Gruppe B'!Q7,0),IF(U5=6,'Gruppe B'!Q10,0),IF(U5=7,'Gruppe B'!Q13,0),IF(U5=9,'Gruppe B'!Q16,0),IF(AND(Finalrunde!U4=U5,Finalrunde!D6=2,Finalrunde!E5&gt;0),Finalrunde!D5/Finalrunde!E5,0),IF(AND(Finalrunde!U5=U5,Finalrunde!B9=2,Finalrunde!C8&gt;0),Finalrunde!B8/Finalrunde!C8,0),IF(AND(Finalrunde!U6=U5,Finalrunde!H12=2,Finalrunde!I11&gt;0),Finalrunde!H11/Finalrunde!I11,0),IF(AND(Finalrunde!U7=U5,Finalrunde!F15=2,Finalrunde!G14&gt;0),Finalrunde!F14/Finalrunde!G14,0),IF(AND(Finalrunde!U20=U5,Finalrunde!D22=2,Finalrunde!E21&gt;0),Finalrunde!D21/Finalrunde!E21,0),IF(AND(Finalrunde!U21=U5,Finalrunde!B25=2,Finalrunde!C24&gt;0),Finalrunde!B24/Finalrunde!C24,0),IF(AND(Finalrunde!U22=U5,Finalrunde!H28=2,Finalrunde!I27&gt;0),Finalrunde!H27/Finalrunde!I27,0),IF(AND(Finalrunde!U23=U5,Finalrunde!F31=2,Finalrunde!G30&gt;0),Finalrunde!F30/Finalrunde!G30,0),IF(AND(Finalrunde!U36=U5,Finalrunde!D38=2,Finalrunde!E37&gt;0),Finalrunde!D37/Finalrunde!E37,0),IF(AND(Finalrunde!U37=U5,Finalrunde!B41=2,Finalrunde!C40&gt;0),Finalrunde!B40/Finalrunde!C40,0),IF(AND(Finalrunde!U38=U5,Finalrunde!H44=2,Finalrunde!I43&gt;0),Finalrunde!H43/Finalrunde!I43,0),IF(AND(Finalrunde!U39=U5,Finalrunde!F47=2,Finalrunde!G46&gt;0),Finalrunde!F46/Finalrunde!G46,0)))</x:f>
+      </x:c>
+      <x:c r="I5" s="73" t="str">
+        <x:f>IF(G5&gt;0,TRUNC(F5/G5,3),"")</x:f>
+      </x:c>
+      <x:c r="J5" s="1" t="str">
+        <x:f>IF(U5="","",MAX(INDEX(Teilnehmer!$M$2:$M$10,MATCH(U5,Teilnehmer!$A$2:$A$10,0)),IF(Finalrunde!U4=U5,IF(ISNUMBER(Finalrunde!E7),Finalrunde!E7,0),0),IF(Finalrunde!U5=U5,IF(ISNUMBER(Finalrunde!C10),Finalrunde!C10,0),0),IF(Finalrunde!U6=U5,IF(ISNUMBER(Finalrunde!I13),Finalrunde!I13,0),0),IF(Finalrunde!U7=U5,IF(ISNUMBER(Finalrunde!G16),Finalrunde!G16,0),0),IF(Finalrunde!U20=U5,IF(ISNUMBER(Finalrunde!E23),Finalrunde!E23,0),0),IF(Finalrunde!U21=U5,IF(ISNUMBER(Finalrunde!C26),Finalrunde!C26,0),0),IF(Finalrunde!U22=U5,IF(ISNUMBER(Finalrunde!I29),Finalrunde!I29,0),0),IF(Finalrunde!U23=U5,IF(ISNUMBER(Finalrunde!G32),Finalrunde!G32,0),0),IF(Finalrunde!U36=U5,IF(ISNUMBER(Finalrunde!E39),Finalrunde!E39,0),0),IF(Finalrunde!U37=U5,IF(ISNUMBER(Finalrunde!C42),Finalrunde!C42,0),0),IF(Finalrunde!U38=U5,IF(ISNUMBER(Finalrunde!I45),Finalrunde!I45,0),0),IF(Finalrunde!U39=U5,IF(ISNUMBER(Finalrunde!G48),Finalrunde!G48,0),0)))</x:f>
+      </x:c>
+      <x:c r="K5" s="1"/>
+      <x:c r="L5" s="1"/>
+      <x:c r="M5" s="1"/>
+      <x:c r="N5" s="1"/>
+      <x:c r="O5" s="1"/>
+      <x:c r="P5" s="1"/>
+      <x:c r="Q5" s="1"/>
+      <x:c r="R5" s="1"/>
+      <x:c r="S5" s="1"/>
+      <x:c r="T5" s="1"/>
+      <x:c r="U5" t="str">
+        <x:f>IF(AND(ISNUMBER(Finalrunde!D22),ISNUMBER(Finalrunde!B25),Finalrunde!D22&lt;&gt;Finalrunde!B25),IF(Finalrunde!D22&gt;Finalrunde!B25,Finalrunde!U20,Finalrunde!U21),"")</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="24" customHeight="1">
+      <x:c r="A6" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B6" s="1" t="str">
+        <x:f>IF(U6="","",INDEX(Teilnehmer!$B$2:$B$10,MATCH(U6,Teilnehmer!$A$2:$A$10,0)))</x:f>
+      </x:c>
+      <x:c r="C6" s="1" t="str">
+        <x:f>IF(U6="","",INDEX(Teilnehmer!$D$2:$D$10,MATCH(U6,Teilnehmer!$A$2:$A$10,0)))</x:f>
+      </x:c>
+      <x:c r="D6" s="1" t="str">
+        <x:f>IF(U6="","",INDEX(Teilnehmer!$C$2:$C$10,MATCH(U6,Teilnehmer!$A$2:$A$10,0)))</x:f>
+      </x:c>
+      <x:c r="E6" s="1" t="str">
+        <x:f>IF(U6="","",INDEX(Teilnehmer!$I$2:$I$10,MATCH(U6,Teilnehmer!$A$2:$A$10,0))+SUM(IF(Finalrunde!U4=U6,IF(ISNUMBER(Finalrunde!D6),Finalrunde!D6,0),0),IF(Finalrunde!U5=U6,IF(ISNUMBER(Finalrunde!B9),Finalrunde!B9,0),0),IF(Finalrunde!U6=U6,IF(ISNUMBER(Finalrunde!H12),Finalrunde!H12,0),0),IF(Finalrunde!U7=U6,IF(ISNUMBER(Finalrunde!F15),Finalrunde!F15,0),0),IF(Finalrunde!U20=U6,IF(ISNUMBER(Finalrunde!D22),Finalrunde!D22,0),0),IF(Finalrunde!U21=U6,IF(ISNUMBER(Finalrunde!B25),Finalrunde!B25,0),0),IF(Finalrunde!U22=U6,IF(ISNUMBER(Finalrunde!H28),Finalrunde!H28,0),0),IF(Finalrunde!U23=U6,IF(ISNUMBER(Finalrunde!F31),Finalrunde!F31,0),0),IF(Finalrunde!U36=U6,IF(ISNUMBER(Finalrunde!D38),Finalrunde!D38,0),0),IF(Finalrunde!U37=U6,IF(ISNUMBER(Finalrunde!B41),Finalrunde!B41,0),0),IF(Finalrunde!U38=U6,IF(ISNUMBER(Finalrunde!H44),Finalrunde!H44,0),0),IF(Finalrunde!U39=U6,IF(ISNUMBER(Finalrunde!F47),Finalrunde!F47,0),0)))</x:f>
+      </x:c>
+      <x:c r="F6" s="1" t="str">
+        <x:f>IF(U6="","",INDEX(Teilnehmer!$J$2:$J$10,MATCH(U6,Teilnehmer!$A$2:$A$10,0))+SUM(IF(Finalrunde!U4=U6,IF(ISNUMBER(Finalrunde!D5),Finalrunde!D5,0),0),IF(Finalrunde!U5=U6,IF(ISNUMBER(Finalrunde!B8),Finalrunde!B8,0),0),IF(Finalrunde!U6=U6,IF(ISNUMBER(Finalrunde!H11),Finalrunde!H11,0),0),IF(Finalrunde!U7=U6,IF(ISNUMBER(Finalrunde!F14),Finalrunde!F14,0),0),IF(Finalrunde!U20=U6,IF(ISNUMBER(Finalrunde!D21),Finalrunde!D21,0),0),IF(Finalrunde!U21=U6,IF(ISNUMBER(Finalrunde!B24),Finalrunde!B24,0),0),IF(Finalrunde!U22=U6,IF(ISNUMBER(Finalrunde!H27),Finalrunde!H27,0),0),IF(Finalrunde!U23=U6,IF(ISNUMBER(Finalrunde!F30),Finalrunde!F30,0),0),IF(Finalrunde!U36=U6,IF(ISNUMBER(Finalrunde!D37),Finalrunde!D37,0),0),IF(Finalrunde!U37=U6,IF(ISNUMBER(Finalrunde!B40),Finalrunde!B40,0),0),IF(Finalrunde!U38=U6,IF(ISNUMBER(Finalrunde!H43),Finalrunde!H43,0),0),IF(Finalrunde!U39=U6,IF(ISNUMBER(Finalrunde!F46),Finalrunde!F46,0),0)))</x:f>
+      </x:c>
+      <x:c r="G6" s="1" t="str">
+        <x:f>IF(U6="","",INDEX(Teilnehmer!$K$2:$K$10,MATCH(U6,Teilnehmer!$A$2:$A$10,0))+SUM(IF(Finalrunde!U4=U6,IF(ISNUMBER(Finalrunde!E5),Finalrunde!E5,0),0),IF(Finalrunde!U5=U6,IF(ISNUMBER(Finalrunde!C8),Finalrunde!C8,0),0),IF(Finalrunde!U6=U6,IF(ISNUMBER(Finalrunde!I11),Finalrunde!I11,0),0),IF(Finalrunde!U7=U6,IF(ISNUMBER(Finalrunde!G14),Finalrunde!G14,0),0),IF(Finalrunde!U20=U6,IF(ISNUMBER(Finalrunde!E21),Finalrunde!E21,0),0),IF(Finalrunde!U21=U6,IF(ISNUMBER(Finalrunde!C24),Finalrunde!C24,0),0),IF(Finalrunde!U22=U6,IF(ISNUMBER(Finalrunde!I27),Finalrunde!I27,0),0),IF(Finalrunde!U23=U6,IF(ISNUMBER(Finalrunde!G30),Finalrunde!G30,0),0),IF(Finalrunde!U36=U6,IF(ISNUMBER(Finalrunde!E37),Finalrunde!E37,0),0),IF(Finalrunde!U37=U6,IF(ISNUMBER(Finalrunde!C40),Finalrunde!C40,0),0),IF(Finalrunde!U38=U6,IF(ISNUMBER(Finalrunde!I43),Finalrunde!I43,0),0),IF(Finalrunde!U39=U6,IF(ISNUMBER(Finalrunde!G46),Finalrunde!G46,0),0)))</x:f>
+      </x:c>
+      <x:c r="H6" s="73" t="str">
+        <x:f>IF(U6="","",MAX(IF(U6=1,'Gruppe A'!Q4,0),IF(U6=4,'Gruppe A'!Q7,0),IF(U6=5,'Gruppe A'!Q10,0),IF(U6=8,'Gruppe A'!Q13,0),IF(U6=2,'Gruppe B'!Q4,0),IF(U6=3,'Gruppe B'!Q7,0),IF(U6=6,'Gruppe B'!Q10,0),IF(U6=7,'Gruppe B'!Q13,0),IF(U6=9,'Gruppe B'!Q16,0),IF(AND(Finalrunde!U4=U6,Finalrunde!D6=2,Finalrunde!E5&gt;0),Finalrunde!D5/Finalrunde!E5,0),IF(AND(Finalrunde!U5=U6,Finalrunde!B9=2,Finalrunde!C8&gt;0),Finalrunde!B8/Finalrunde!C8,0),IF(AND(Finalrunde!U6=U6,Finalrunde!H12=2,Finalrunde!I11&gt;0),Finalrunde!H11/Finalrunde!I11,0),IF(AND(Finalrunde!U7=U6,Finalrunde!F15=2,Finalrunde!G14&gt;0),Finalrunde!F14/Finalrunde!G14,0),IF(AND(Finalrunde!U20=U6,Finalrunde!D22=2,Finalrunde!E21&gt;0),Finalrunde!D21/Finalrunde!E21,0),IF(AND(Finalrunde!U21=U6,Finalrunde!B25=2,Finalrunde!C24&gt;0),Finalrunde!B24/Finalrunde!C24,0),IF(AND(Finalrunde!U22=U6,Finalrunde!H28=2,Finalrunde!I27&gt;0),Finalrunde!H27/Finalrunde!I27,0),IF(AND(Finalrunde!U23=U6,Finalrunde!F31=2,Finalrunde!G30&gt;0),Finalrunde!F30/Finalrunde!G30,0),IF(AND(Finalrunde!U36=U6,Finalrunde!D38=2,Finalrunde!E37&gt;0),Finalrunde!D37/Finalrunde!E37,0),IF(AND(Finalrunde!U37=U6,Finalrunde!B41=2,Finalrunde!C40&gt;0),Finalrunde!B40/Finalrunde!C40,0),IF(AND(Finalrunde!U38=U6,Finalrunde!H44=2,Finalrunde!I43&gt;0),Finalrunde!H43/Finalrunde!I43,0),IF(AND(Finalrunde!U39=U6,Finalrunde!F47=2,Finalrunde!G46&gt;0),Finalrunde!F46/Finalrunde!G46,0)))</x:f>
+      </x:c>
+      <x:c r="I6" s="73" t="str">
+        <x:f>IF(G6&gt;0,TRUNC(F6/G6,3),"")</x:f>
+      </x:c>
+      <x:c r="J6" s="1" t="str">
+        <x:f>IF(U6="","",MAX(INDEX(Teilnehmer!$M$2:$M$10,MATCH(U6,Teilnehmer!$A$2:$A$10,0)),IF(Finalrunde!U4=U6,IF(ISNUMBER(Finalrunde!E7),Finalrunde!E7,0),0),IF(Finalrunde!U5=U6,IF(ISNUMBER(Finalrunde!C10),Finalrunde!C10,0),0),IF(Finalrunde!U6=U6,IF(ISNUMBER(Finalrunde!I13),Finalrunde!I13,0),0),IF(Finalrunde!U7=U6,IF(ISNUMBER(Finalrunde!G16),Finalrunde!G16,0),0),IF(Finalrunde!U20=U6,IF(ISNUMBER(Finalrunde!E23),Finalrunde!E23,0),0),IF(Finalrunde!U21=U6,IF(ISNUMBER(Finalrunde!C26),Finalrunde!C26,0),0),IF(Finalrunde!U22=U6,IF(ISNUMBER(Finalrunde!I29),Finalrunde!I29,0),0),IF(Finalrunde!U23=U6,IF(ISNUMBER(Finalrunde!G32),Finalrunde!G32,0),0),IF(Finalrunde!U36=U6,IF(ISNUMBER(Finalrunde!E39),Finalrunde!E39,0),0),IF(Finalrunde!U37=U6,IF(ISNUMBER(Finalrunde!C42),Finalrunde!C42,0),0),IF(Finalrunde!U38=U6,IF(ISNUMBER(Finalrunde!I45),Finalrunde!I45,0),0),IF(Finalrunde!U39=U6,IF(ISNUMBER(Finalrunde!G48),Finalrunde!G48,0),0)))</x:f>
+      </x:c>
+      <x:c r="K6" s="1"/>
+      <x:c r="L6" s="1"/>
+      <x:c r="M6" s="1"/>
+      <x:c r="N6" s="1"/>
+      <x:c r="O6" s="1"/>
+      <x:c r="P6" s="1"/>
+      <x:c r="Q6" s="1"/>
+      <x:c r="R6" s="1"/>
+      <x:c r="S6" s="1"/>
+      <x:c r="T6" s="1"/>
+      <x:c r="U6" t="str">
+        <x:f>IF(AND(ISNUMBER(Finalrunde!D22),ISNUMBER(Finalrunde!B25),Finalrunde!D22&lt;&gt;Finalrunde!B25),IF(Finalrunde!D22&lt;Finalrunde!B25,Finalrunde!U20,Finalrunde!U21),"")</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="24" customHeight="1">
+      <x:c r="A7" s="1" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B7" s="1" t="str">
+        <x:f>IF(U7="","",INDEX(Teilnehmer!$B$2:$B$10,MATCH(U7,Teilnehmer!$A$2:$A$10,0)))</x:f>
+      </x:c>
+      <x:c r="C7" s="1" t="str">
+        <x:f>IF(U7="","",INDEX(Teilnehmer!$D$2:$D$10,MATCH(U7,Teilnehmer!$A$2:$A$10,0)))</x:f>
+      </x:c>
+      <x:c r="D7" s="1" t="str">
+        <x:f>IF(U7="","",INDEX(Teilnehmer!$C$2:$C$10,MATCH(U7,Teilnehmer!$A$2:$A$10,0)))</x:f>
+      </x:c>
+      <x:c r="E7" s="1" t="str">
+        <x:f>IF(U7="","",INDEX(Teilnehmer!$I$2:$I$10,MATCH(U7,Teilnehmer!$A$2:$A$10,0))+SUM(IF(Finalrunde!U4=U7,IF(ISNUMBER(Finalrunde!D6),Finalrunde!D6,0),0),IF(Finalrunde!U5=U7,IF(ISNUMBER(Finalrunde!B9),Finalrunde!B9,0),0),IF(Finalrunde!U6=U7,IF(ISNUMBER(Finalrunde!H12),Finalrunde!H12,0),0),IF(Finalrunde!U7=U7,IF(ISNUMBER(Finalrunde!F15),Finalrunde!F15,0),0),IF(Finalrunde!U20=U7,IF(ISNUMBER(Finalrunde!D22),Finalrunde!D22,0),0),IF(Finalrunde!U21=U7,IF(ISNUMBER(Finalrunde!B25),Finalrunde!B25,0),0),IF(Finalrunde!U22=U7,IF(ISNUMBER(Finalrunde!H28),Finalrunde!H28,0),0),IF(Finalrunde!U23=U7,IF(ISNUMBER(Finalrunde!F31),Finalrunde!F31,0),0),IF(Finalrunde!U36=U7,IF(ISNUMBER(Finalrunde!D38),Finalrunde!D38,0),0),IF(Finalrunde!U37=U7,IF(ISNUMBER(Finalrunde!B41),Finalrunde!B41,0),0),IF(Finalrunde!U38=U7,IF(ISNUMBER(Finalrunde!H44),Finalrunde!H44,0),0),IF(Finalrunde!U39=U7,IF(ISNUMBER(Finalrunde!F47),Finalrunde!F47,0),0)))</x:f>
+      </x:c>
+      <x:c r="F7" s="1" t="str">
+        <x:f>IF(U7="","",INDEX(Teilnehmer!$J$2:$J$10,MATCH(U7,Teilnehmer!$A$2:$A$10,0))+SUM(IF(Finalrunde!U4=U7,IF(ISNUMBER(Finalrunde!D5),Finalrunde!D5,0),0),IF(Finalrunde!U5=U7,IF(ISNUMBER(Finalrunde!B8),Finalrunde!B8,0),0),IF(Finalrunde!U6=U7,IF(ISNUMBER(Finalrunde!H11),Finalrunde!H11,0),0),IF(Finalrunde!U7=U7,IF(ISNUMBER(Finalrunde!F14),Finalrunde!F14,0),0),IF(Finalrunde!U20=U7,IF(ISNUMBER(Finalrunde!D21),Finalrunde!D21,0),0),IF(Finalrunde!U21=U7,IF(ISNUMBER(Finalrunde!B24),Finalrunde!B24,0),0),IF(Finalrunde!U22=U7,IF(ISNUMBER(Finalrunde!H27),Finalrunde!H27,0),0),IF(Finalrunde!U23=U7,IF(ISNUMBER(Finalrunde!F30),Finalrunde!F30,0),0),IF(Finalrunde!U36=U7,IF(ISNUMBER(Finalrunde!D37),Finalrunde!D37,0),0),IF(Finalrunde!U37=U7,IF(ISNUMBER(Finalrunde!B40),Finalrunde!B40,0),0),IF(Finalrunde!U38=U7,IF(ISNUMBER(Finalrunde!H43),Finalrunde!H43,0),0),IF(Finalrunde!U39=U7,IF(ISNUMBER(Finalrunde!F46),Finalrunde!F46,0),0)))</x:f>
+      </x:c>
+      <x:c r="G7" s="1" t="str">
+        <x:f>IF(U7="","",INDEX(Teilnehmer!$K$2:$K$10,MATCH(U7,Teilnehmer!$A$2:$A$10,0))+SUM(IF(Finalrunde!U4=U7,IF(ISNUMBER(Finalrunde!E5),Finalrunde!E5,0),0),IF(Finalrunde!U5=U7,IF(ISNUMBER(Finalrunde!C8),Finalrunde!C8,0),0),IF(Finalrunde!U6=U7,IF(ISNUMBER(Finalrunde!I11),Finalrunde!I11,0),0),IF(Finalrunde!U7=U7,IF(ISNUMBER(Finalrunde!G14),Finalrunde!G14,0),0),IF(Finalrunde!U20=U7,IF(ISNUMBER(Finalrunde!E21),Finalrunde!E21,0),0),IF(Finalrunde!U21=U7,IF(ISNUMBER(Finalrunde!C24),Finalrunde!C24,0),0),IF(Finalrunde!U22=U7,IF(ISNUMBER(Finalrunde!I27),Finalrunde!I27,0),0),IF(Finalrunde!U23=U7,IF(ISNUMBER(Finalrunde!G30),Finalrunde!G30,0),0),IF(Finalrunde!U36=U7,IF(ISNUMBER(Finalrunde!E37),Finalrunde!E37,0),0),IF(Finalrunde!U37=U7,IF(ISNUMBER(Finalrunde!C40),Finalrunde!C40,0),0),IF(Finalrunde!U38=U7,IF(ISNUMBER(Finalrunde!I43),Finalrunde!I43,0),0),IF(Finalrunde!U39=U7,IF(ISNUMBER(Finalrunde!G46),Finalrunde!G46,0),0)))</x:f>
+      </x:c>
+      <x:c r="H7" s="73" t="str">
+        <x:f>IF(U7="","",MAX(IF(U7=1,'Gruppe A'!Q4,0),IF(U7=4,'Gruppe A'!Q7,0),IF(U7=5,'Gruppe A'!Q10,0),IF(U7=8,'Gruppe A'!Q13,0),IF(U7=2,'Gruppe B'!Q4,0),IF(U7=3,'Gruppe B'!Q7,0),IF(U7=6,'Gruppe B'!Q10,0),IF(U7=7,'Gruppe B'!Q13,0),IF(U7=9,'Gruppe B'!Q16,0),IF(AND(Finalrunde!U4=U7,Finalrunde!D6=2,Finalrunde!E5&gt;0),Finalrunde!D5/Finalrunde!E5,0),IF(AND(Finalrunde!U5=U7,Finalrunde!B9=2,Finalrunde!C8&gt;0),Finalrunde!B8/Finalrunde!C8,0),IF(AND(Finalrunde!U6=U7,Finalrunde!H12=2,Finalrunde!I11&gt;0),Finalrunde!H11/Finalrunde!I11,0),IF(AND(Finalrunde!U7=U7,Finalrunde!F15=2,Finalrunde!G14&gt;0),Finalrunde!F14/Finalrunde!G14,0),IF(AND(Finalrunde!U20=U7,Finalrunde!D22=2,Finalrunde!E21&gt;0),Finalrunde!D21/Finalrunde!E21,0),IF(AND(Finalrunde!U21=U7,Finalrunde!B25=2,Finalrunde!C24&gt;0),Finalrunde!B24/Finalrunde!C24,0),IF(AND(Finalrunde!U22=U7,Finalrunde!H28=2,Finalrunde!I27&gt;0),Finalrunde!H27/Finalrunde!I27,0),IF(AND(Finalrunde!U23=U7,Finalrunde!F31=2,Finalrunde!G30&gt;0),Finalrunde!F30/Finalrunde!G30,0),IF(AND(Finalrunde!U36=U7,Finalrunde!D38=2,Finalrunde!E37&gt;0),Finalrunde!D37/Finalrunde!E37,0),IF(AND(Finalrunde!U37=U7,Finalrunde!B41=2,Finalrunde!C40&gt;0),Finalrunde!B40/Finalrunde!C40,0),IF(AND(Finalrunde!U38=U7,Finalrunde!H44=2,Finalrunde!I43&gt;0),Finalrunde!H43/Finalrunde!I43,0),IF(AND(Finalrunde!U39=U7,Finalrunde!F47=2,Finalrunde!G46&gt;0),Finalrunde!F46/Finalrunde!G46,0)))</x:f>
+      </x:c>
+      <x:c r="I7" s="73" t="str">
+        <x:f>IF(G7&gt;0,TRUNC(F7/G7,3),"")</x:f>
+      </x:c>
+      <x:c r="J7" s="1" t="str">
+        <x:f>IF(U7="","",MAX(INDEX(Teilnehmer!$M$2:$M$10,MATCH(U7,Teilnehmer!$A$2:$A$10,0)),IF(Finalrunde!U4=U7,IF(ISNUMBER(Finalrunde!E7),Finalrunde!E7,0),0),IF(Finalrunde!U5=U7,IF(ISNUMBER(Finalrunde!C10),Finalrunde!C10,0),0),IF(Finalrunde!U6=U7,IF(ISNUMBER(Finalrunde!I13),Finalrunde!I13,0),0),IF(Finalrunde!U7=U7,IF(ISNUMBER(Finalrunde!G16),Finalrunde!G16,0),0),IF(Finalrunde!U20=U7,IF(ISNUMBER(Finalrunde!E23),Finalrunde!E23,0),0),IF(Finalrunde!U21=U7,IF(ISNUMBER(Finalrunde!C26),Finalrunde!C26,0),0),IF(Finalrunde!U22=U7,IF(ISNUMBER(Finalrunde!I29),Finalrunde!I29,0),0),IF(Finalrunde!U23=U7,IF(ISNUMBER(Finalrunde!G32),Finalrunde!G32,0),0),IF(Finalrunde!U36=U7,IF(ISNUMBER(Finalrunde!E39),Finalrunde!E39,0),0),IF(Finalrunde!U37=U7,IF(ISNUMBER(Finalrunde!C42),Finalrunde!C42,0),0),IF(Finalrunde!U38=U7,IF(ISNUMBER(Finalrunde!I45),Finalrunde!I45,0),0),IF(Finalrunde!U39=U7,IF(ISNUMBER(Finalrunde!G48),Finalrunde!G48,0),0)))</x:f>
+      </x:c>
+      <x:c r="K7" s="1"/>
+      <x:c r="L7" s="1"/>
+      <x:c r="M7" s="1"/>
+      <x:c r="N7" s="1"/>
+      <x:c r="O7" s="1"/>
+      <x:c r="P7" s="1"/>
+      <x:c r="Q7" s="1"/>
+      <x:c r="R7" s="1"/>
+      <x:c r="S7" s="1"/>
+      <x:c r="T7" s="1"/>
+      <x:c r="U7" t="str">
+        <x:f>IF(AND(ISNUMBER(Finalrunde!H28),ISNUMBER(Finalrunde!F31),Finalrunde!H28&lt;&gt;Finalrunde!F31),IF(Finalrunde!H28&gt;Finalrunde!F31,Finalrunde!U22,Finalrunde!U23),"")</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="24" customHeight="1">
+      <x:c r="A8" s="1" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B8" s="1" t="str">
+        <x:f>IF(U8="","",INDEX(Teilnehmer!$B$2:$B$10,MATCH(U8,Teilnehmer!$A$2:$A$10,0)))</x:f>
+      </x:c>
+      <x:c r="C8" s="1" t="str">
+        <x:f>IF(U8="","",INDEX(Teilnehmer!$D$2:$D$10,MATCH(U8,Teilnehmer!$A$2:$A$10,0)))</x:f>
+      </x:c>
+      <x:c r="D8" s="1" t="str">
+        <x:f>IF(U8="","",INDEX(Teilnehmer!$C$2:$C$10,MATCH(U8,Teilnehmer!$A$2:$A$10,0)))</x:f>
+      </x:c>
+      <x:c r="E8" s="1" t="str">
+        <x:f>IF(U8="","",INDEX(Teilnehmer!$I$2:$I$10,MATCH(U8,Teilnehmer!$A$2:$A$10,0))+SUM(IF(Finalrunde!U4=U8,IF(ISNUMBER(Finalrunde!D6),Finalrunde!D6,0),0),IF(Finalrunde!U5=U8,IF(ISNUMBER(Finalrunde!B9),Finalrunde!B9,0),0),IF(Finalrunde!U6=U8,IF(ISNUMBER(Finalrunde!H12),Finalrunde!H12,0),0),IF(Finalrunde!U7=U8,IF(ISNUMBER(Finalrunde!F15),Finalrunde!F15,0),0),IF(Finalrunde!U20=U8,IF(ISNUMBER(Finalrunde!D22),Finalrunde!D22,0),0),IF(Finalrunde!U21=U8,IF(ISNUMBER(Finalrunde!B25),Finalrunde!B25,0),0),IF(Finalrunde!U22=U8,IF(ISNUMBER(Finalrunde!H28),Finalrunde!H28,0),0),IF(Finalrunde!U23=U8,IF(ISNUMBER(Finalrunde!F31),Finalrunde!F31,0),0),IF(Finalrunde!U36=U8,IF(ISNUMBER(Finalrunde!D38),Finalrunde!D38,0),0),IF(Finalrunde!U37=U8,IF(ISNUMBER(Finalrunde!B41),Finalrunde!B41,0),0),IF(Finalrunde!U38=U8,IF(ISNUMBER(Finalrunde!H44),Finalrunde!H44,0),0),IF(Finalrunde!U39=U8,IF(ISNUMBER(Finalrunde!F47),Finalrunde!F47,0),0)))</x:f>
+      </x:c>
+      <x:c r="F8" s="1" t="str">
+        <x:f>IF(U8="","",INDEX(Teilnehmer!$J$2:$J$10,MATCH(U8,Teilnehmer!$A$2:$A$10,0))+SUM(IF(Finalrunde!U4=U8,IF(ISNUMBER(Finalrunde!D5),Finalrunde!D5,0),0),IF(Finalrunde!U5=U8,IF(ISNUMBER(Finalrunde!B8),Finalrunde!B8,0),0),IF(Finalrunde!U6=U8,IF(ISNUMBER(Finalrunde!H11),Finalrunde!H11,0),0),IF(Finalrunde!U7=U8,IF(ISNUMBER(Finalrunde!F14),Finalrunde!F14,0),0),IF(Finalrunde!U20=U8,IF(ISNUMBER(Finalrunde!D21),Finalrunde!D21,0),0),IF(Finalrunde!U21=U8,IF(ISNUMBER(Finalrunde!B24),Finalrunde!B24,0),0),IF(Finalrunde!U22=U8,IF(ISNUMBER(Finalrunde!H27),Finalrunde!H27,0),0),IF(Finalrunde!U23=U8,IF(ISNUMBER(Finalrunde!F30),Finalrunde!F30,0),0),IF(Finalrunde!U36=U8,IF(ISNUMBER(Finalrunde!D37),Finalrunde!D37,0),0),IF(Finalrunde!U37=U8,IF(ISNUMBER(Finalrunde!B40),Finalrunde!B40,0),0),IF(Finalrunde!U38=U8,IF(ISNUMBER(Finalrunde!H43),Finalrunde!H43,0),0),IF(Finalrunde!U39=U8,IF(ISNUMBER(Finalrunde!F46),Finalrunde!F46,0),0)))</x:f>
+      </x:c>
+      <x:c r="G8" s="1" t="str">
+        <x:f>IF(U8="","",INDEX(Teilnehmer!$K$2:$K$10,MATCH(U8,Teilnehmer!$A$2:$A$10,0))+SUM(IF(Finalrunde!U4=U8,IF(ISNUMBER(Finalrunde!E5),Finalrunde!E5,0),0),IF(Finalrunde!U5=U8,IF(ISNUMBER(Finalrunde!C8),Finalrunde!C8,0),0),IF(Finalrunde!U6=U8,IF(ISNUMBER(Finalrunde!I11),Finalrunde!I11,0),0),IF(Finalrunde!U7=U8,IF(ISNUMBER(Finalrunde!G14),Finalrunde!G14,0),0),IF(Finalrunde!U20=U8,IF(ISNUMBER(Finalrunde!E21),Finalrunde!E21,0),0),IF(Finalrunde!U21=U8,IF(ISNUMBER(Finalrunde!C24),Finalrunde!C24,0),0),IF(Finalrunde!U22=U8,IF(ISNUMBER(Finalrunde!I27),Finalrunde!I27,0),0),IF(Finalrunde!U23=U8,IF(ISNUMBER(Finalrunde!G30),Finalrunde!G30,0),0),IF(Finalrunde!U36=U8,IF(ISNUMBER(Finalrunde!E37),Finalrunde!E37,0),0),IF(Finalrunde!U37=U8,IF(ISNUMBER(Finalrunde!C40),Finalrunde!C40,0),0),IF(Finalrunde!U38=U8,IF(ISNUMBER(Finalrunde!I43),Finalrunde!I43,0),0),IF(Finalrunde!U39=U8,IF(ISNUMBER(Finalrunde!G46),Finalrunde!G46,0),0)))</x:f>
+      </x:c>
+      <x:c r="H8" s="73" t="str">
+        <x:f>IF(U8="","",MAX(IF(U8=1,'Gruppe A'!Q4,0),IF(U8=4,'Gruppe A'!Q7,0),IF(U8=5,'Gruppe A'!Q10,0),IF(U8=8,'Gruppe A'!Q13,0),IF(U8=2,'Gruppe B'!Q4,0),IF(U8=3,'Gruppe B'!Q7,0),IF(U8=6,'Gruppe B'!Q10,0),IF(U8=7,'Gruppe B'!Q13,0),IF(U8=9,'Gruppe B'!Q16,0),IF(AND(Finalrunde!U4=U8,Finalrunde!D6=2,Finalrunde!E5&gt;0),Finalrunde!D5/Finalrunde!E5,0),IF(AND(Finalrunde!U5=U8,Finalrunde!B9=2,Finalrunde!C8&gt;0),Finalrunde!B8/Finalrunde!C8,0),IF(AND(Finalrunde!U6=U8,Finalrunde!H12=2,Finalrunde!I11&gt;0),Finalrunde!H11/Finalrunde!I11,0),IF(AND(Finalrunde!U7=U8,Finalrunde!F15=2,Finalrunde!G14&gt;0),Finalrunde!F14/Finalrunde!G14,0),IF(AND(Finalrunde!U20=U8,Finalrunde!D22=2,Finalrunde!E21&gt;0),Finalrunde!D21/Finalrunde!E21,0),IF(AND(Finalrunde!U21=U8,Finalrunde!B25=2,Finalrunde!C24&gt;0),Finalrunde!B24/Finalrunde!C24,0),IF(AND(Finalrunde!U22=U8,Finalrunde!H28=2,Finalrunde!I27&gt;0),Finalrunde!H27/Finalrunde!I27,0),IF(AND(Finalrunde!U23=U8,Finalrunde!F31=2,Finalrunde!G30&gt;0),Finalrunde!F30/Finalrunde!G30,0),IF(AND(Finalrunde!U36=U8,Finalrunde!D38=2,Finalrunde!E37&gt;0),Finalrunde!D37/Finalrunde!E37,0),IF(AND(Finalrunde!U37=U8,Finalrunde!B41=2,Finalrunde!C40&gt;0),Finalrunde!B40/Finalrunde!C40,0),IF(AND(Finalrunde!U38=U8,Finalrunde!H44=2,Finalrunde!I43&gt;0),Finalrunde!H43/Finalrunde!I43,0),IF(AND(Finalrunde!U39=U8,Finalrunde!F47=2,Finalrunde!G46&gt;0),Finalrunde!F46/Finalrunde!G46,0)))</x:f>
+      </x:c>
+      <x:c r="I8" s="73" t="str">
+        <x:f>IF(G8&gt;0,TRUNC(F8/G8,3),"")</x:f>
+      </x:c>
+      <x:c r="J8" s="1" t="str">
+        <x:f>IF(U8="","",MAX(INDEX(Teilnehmer!$M$2:$M$10,MATCH(U8,Teilnehmer!$A$2:$A$10,0)),IF(Finalrunde!U4=U8,IF(ISNUMBER(Finalrunde!E7),Finalrunde!E7,0),0),IF(Finalrunde!U5=U8,IF(ISNUMBER(Finalrunde!C10),Finalrunde!C10,0),0),IF(Finalrunde!U6=U8,IF(ISNUMBER(Finalrunde!I13),Finalrunde!I13,0),0),IF(Finalrunde!U7=U8,IF(ISNUMBER(Finalrunde!G16),Finalrunde!G16,0),0),IF(Finalrunde!U20=U8,IF(ISNUMBER(Finalrunde!E23),Finalrunde!E23,0),0),IF(Finalrunde!U21=U8,IF(ISNUMBER(Finalrunde!C26),Finalrunde!C26,0),0),IF(Finalrunde!U22=U8,IF(ISNUMBER(Finalrunde!I29),Finalrunde!I29,0),0),IF(Finalrunde!U23=U8,IF(ISNUMBER(Finalrunde!G32),Finalrunde!G32,0),0),IF(Finalrunde!U36=U8,IF(ISNUMBER(Finalrunde!E39),Finalrunde!E39,0),0),IF(Finalrunde!U37=U8,IF(ISNUMBER(Finalrunde!C42),Finalrunde!C42,0),0),IF(Finalrunde!U38=U8,IF(ISNUMBER(Finalrunde!I45),Finalrunde!I45,0),0),IF(Finalrunde!U39=U8,IF(ISNUMBER(Finalrunde!G48),Finalrunde!G48,0),0)))</x:f>
+      </x:c>
+      <x:c r="K8" s="1"/>
+      <x:c r="L8" s="1"/>
+      <x:c r="M8" s="1"/>
+      <x:c r="N8" s="1"/>
+      <x:c r="O8" s="1"/>
+      <x:c r="P8" s="1"/>
+      <x:c r="Q8" s="1"/>
+      <x:c r="R8" s="1"/>
+      <x:c r="S8" s="1"/>
+      <x:c r="T8" s="1"/>
+      <x:c r="U8" t="str">
+        <x:f>IF(AND(ISNUMBER(Finalrunde!H28),ISNUMBER(Finalrunde!F31),Finalrunde!H28&lt;&gt;Finalrunde!F31),IF(Finalrunde!H28&lt;Finalrunde!F31,Finalrunde!U22,Finalrunde!U23),"")</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="24" customHeight="1">
+      <x:c r="A9" s="1" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B9" s="1" t="str">
+        <x:f>IF(U9="","",INDEX(Teilnehmer!$B$2:$B$10,MATCH(U9,Teilnehmer!$A$2:$A$10,0)))</x:f>
+      </x:c>
+      <x:c r="C9" s="1" t="str">
+        <x:f>IF(U9="","",INDEX(Teilnehmer!$D$2:$D$10,MATCH(U9,Teilnehmer!$A$2:$A$10,0)))</x:f>
+      </x:c>
+      <x:c r="D9" s="1" t="str">
+        <x:f>IF(U9="","",INDEX(Teilnehmer!$C$2:$C$10,MATCH(U9,Teilnehmer!$A$2:$A$10,0)))</x:f>
+      </x:c>
+      <x:c r="E9" s="1" t="str">
+        <x:f>IF(U9="","",INDEX(Teilnehmer!$I$2:$I$10,MATCH(U9,Teilnehmer!$A$2:$A$10,0))+SUM(IF(Finalrunde!U4=U9,IF(ISNUMBER(Finalrunde!D6),Finalrunde!D6,0),0),IF(Finalrunde!U5=U9,IF(ISNUMBER(Finalrunde!B9),Finalrunde!B9,0),0),IF(Finalrunde!U6=U9,IF(ISNUMBER(Finalrunde!H12),Finalrunde!H12,0),0),IF(Finalrunde!U7=U9,IF(ISNUMBER(Finalrunde!F15),Finalrunde!F15,0),0),IF(Finalrunde!U20=U9,IF(ISNUMBER(Finalrunde!D22),Finalrunde!D22,0),0),IF(Finalrunde!U21=U9,IF(ISNUMBER(Finalrunde!B25),Finalrunde!B25,0),0),IF(Finalrunde!U22=U9,IF(ISNUMBER(Finalrunde!H28),Finalrunde!H28,0),0),IF(Finalrunde!U23=U9,IF(ISNUMBER(Finalrunde!F31),Finalrunde!F31,0),0),IF(Finalrunde!U36=U9,IF(ISNUMBER(Finalrunde!D38),Finalrunde!D38,0),0),IF(Finalrunde!U37=U9,IF(ISNUMBER(Finalrunde!B41),Finalrunde!B41,0),0),IF(Finalrunde!U38=U9,IF(ISNUMBER(Finalrunde!H44),Finalrunde!H44,0),0),IF(Finalrunde!U39=U9,IF(ISNUMBER(Finalrunde!F47),Finalrunde!F47,0),0)))</x:f>
+      </x:c>
+      <x:c r="F9" s="1" t="str">
+        <x:f>IF(U9="","",INDEX(Teilnehmer!$J$2:$J$10,MATCH(U9,Teilnehmer!$A$2:$A$10,0))+SUM(IF(Finalrunde!U4=U9,IF(ISNUMBER(Finalrunde!D5),Finalrunde!D5,0),0),IF(Finalrunde!U5=U9,IF(ISNUMBER(Finalrunde!B8),Finalrunde!B8,0),0),IF(Finalrunde!U6=U9,IF(ISNUMBER(Finalrunde!H11),Finalrunde!H11,0),0),IF(Finalrunde!U7=U9,IF(ISNUMBER(Finalrunde!F14),Finalrunde!F14,0),0),IF(Finalrunde!U20=U9,IF(ISNUMBER(Finalrunde!D21),Finalrunde!D21,0),0),IF(Finalrunde!U21=U9,IF(ISNUMBER(Finalrunde!B24),Finalrunde!B24,0),0),IF(Finalrunde!U22=U9,IF(ISNUMBER(Finalrunde!H27),Finalrunde!H27,0),0),IF(Finalrunde!U23=U9,IF(ISNUMBER(Finalrunde!F30),Finalrunde!F30,0),0),IF(Finalrunde!U36=U9,IF(ISNUMBER(Finalrunde!D37),Finalrunde!D37,0),0),IF(Finalrunde!U37=U9,IF(ISNUMBER(Finalrunde!B40),Finalrunde!B40,0),0),IF(Finalrunde!U38=U9,IF(ISNUMBER(Finalrunde!H43),Finalrunde!H43,0),0),IF(Finalrunde!U39=U9,IF(ISNUMBER(Finalrunde!F46),Finalrunde!F46,0),0)))</x:f>
+      </x:c>
+      <x:c r="G9" s="1" t="str">
+        <x:f>IF(U9="","",INDEX(Teilnehmer!$K$2:$K$10,MATCH(U9,Teilnehmer!$A$2:$A$10,0))+SUM(IF(Finalrunde!U4=U9,IF(ISNUMBER(Finalrunde!E5),Finalrunde!E5,0),0),IF(Finalrunde!U5=U9,IF(ISNUMBER(Finalrunde!C8),Finalrunde!C8,0),0),IF(Finalrunde!U6=U9,IF(ISNUMBER(Finalrunde!I11),Finalrunde!I11,0),0),IF(Finalrunde!U7=U9,IF(ISNUMBER(Finalrunde!G14),Finalrunde!G14,0),0),IF(Finalrunde!U20=U9,IF(ISNUMBER(Finalrunde!E21),Finalrunde!E21,0),0),IF(Finalrunde!U21=U9,IF(ISNUMBER(Finalrunde!C24),Finalrunde!C24,0),0),IF(Finalrunde!U22=U9,IF(ISNUMBER(Finalrunde!I27),Finalrunde!I27,0),0),IF(Finalrunde!U23=U9,IF(ISNUMBER(Finalrunde!G30),Finalrunde!G30,0),0),IF(Finalrunde!U36=U9,IF(ISNUMBER(Finalrunde!E37),Finalrunde!E37,0),0),IF(Finalrunde!U37=U9,IF(ISNUMBER(Finalrunde!C40),Finalrunde!C40,0),0),IF(Finalrunde!U38=U9,IF(ISNUMBER(Finalrunde!I43),Finalrunde!I43,0),0),IF(Finalrunde!U39=U9,IF(ISNUMBER(Finalrunde!G46),Finalrunde!G46,0),0)))</x:f>
+      </x:c>
+      <x:c r="H9" s="73" t="str">
+        <x:f>IF(U9="","",MAX(IF(U9=1,'Gruppe A'!Q4,0),IF(U9=4,'Gruppe A'!Q7,0),IF(U9=5,'Gruppe A'!Q10,0),IF(U9=8,'Gruppe A'!Q13,0),IF(U9=2,'Gruppe B'!Q4,0),IF(U9=3,'Gruppe B'!Q7,0),IF(U9=6,'Gruppe B'!Q10,0),IF(U9=7,'Gruppe B'!Q13,0),IF(U9=9,'Gruppe B'!Q16,0),IF(AND(Finalrunde!U4=U9,Finalrunde!D6=2,Finalrunde!E5&gt;0),Finalrunde!D5/Finalrunde!E5,0),IF(AND(Finalrunde!U5=U9,Finalrunde!B9=2,Finalrunde!C8&gt;0),Finalrunde!B8/Finalrunde!C8,0),IF(AND(Finalrunde!U6=U9,Finalrunde!H12=2,Finalrunde!I11&gt;0),Finalrunde!H11/Finalrunde!I11,0),IF(AND(Finalrunde!U7=U9,Finalrunde!F15=2,Finalrunde!G14&gt;0),Finalrunde!F14/Finalrunde!G14,0),IF(AND(Finalrunde!U20=U9,Finalrunde!D22=2,Finalrunde!E21&gt;0),Finalrunde!D21/Finalrunde!E21,0),IF(AND(Finalrunde!U21=U9,Finalrunde!B25=2,Finalrunde!C24&gt;0),Finalrunde!B24/Finalrunde!C24,0),IF(AND(Finalrunde!U22=U9,Finalrunde!H28=2,Finalrunde!I27&gt;0),Finalrunde!H27/Finalrunde!I27,0),IF(AND(Finalrunde!U23=U9,Finalrunde!F31=2,Finalrunde!G30&gt;0),Finalrunde!F30/Finalrunde!G30,0),IF(AND(Finalrunde!U36=U9,Finalrunde!D38=2,Finalrunde!E37&gt;0),Finalrunde!D37/Finalrunde!E37,0),IF(AND(Finalrunde!U37=U9,Finalrunde!B41=2,Finalrunde!C40&gt;0),Finalrunde!B40/Finalrunde!C40,0),IF(AND(Finalrunde!U38=U9,Finalrunde!H44=2,Finalrunde!I43&gt;0),Finalrunde!H43/Finalrunde!I43,0),IF(AND(Finalrunde!U39=U9,Finalrunde!F47=2,Finalrunde!G46&gt;0),Finalrunde!F46/Finalrunde!G46,0)))</x:f>
+      </x:c>
+      <x:c r="I9" s="73" t="str">
+        <x:f>IF(G9&gt;0,TRUNC(F9/G9,3),"")</x:f>
+      </x:c>
+      <x:c r="J9" s="1" t="str">
+        <x:f>IF(U9="","",MAX(INDEX(Teilnehmer!$M$2:$M$10,MATCH(U9,Teilnehmer!$A$2:$A$10,0)),IF(Finalrunde!U4=U9,IF(ISNUMBER(Finalrunde!E7),Finalrunde!E7,0),0),IF(Finalrunde!U5=U9,IF(ISNUMBER(Finalrunde!C10),Finalrunde!C10,0),0),IF(Finalrunde!U6=U9,IF(ISNUMBER(Finalrunde!I13),Finalrunde!I13,0),0),IF(Finalrunde!U7=U9,IF(ISNUMBER(Finalrunde!G16),Finalrunde!G16,0),0),IF(Finalrunde!U20=U9,IF(ISNUMBER(Finalrunde!E23),Finalrunde!E23,0),0),IF(Finalrunde!U21=U9,IF(ISNUMBER(Finalrunde!C26),Finalrunde!C26,0),0),IF(Finalrunde!U22=U9,IF(ISNUMBER(Finalrunde!I29),Finalrunde!I29,0),0),IF(Finalrunde!U23=U9,IF(ISNUMBER(Finalrunde!G32),Finalrunde!G32,0),0),IF(Finalrunde!U36=U9,IF(ISNUMBER(Finalrunde!E39),Finalrunde!E39,0),0),IF(Finalrunde!U37=U9,IF(ISNUMBER(Finalrunde!C42),Finalrunde!C42,0),0),IF(Finalrunde!U38=U9,IF(ISNUMBER(Finalrunde!I45),Finalrunde!I45,0),0),IF(Finalrunde!U39=U9,IF(ISNUMBER(Finalrunde!G48),Finalrunde!G48,0),0)))</x:f>
+      </x:c>
+      <x:c r="K9" s="1"/>
+      <x:c r="L9" s="1"/>
+      <x:c r="M9" s="1"/>
+      <x:c r="N9" s="1"/>
+      <x:c r="O9" s="1"/>
+      <x:c r="P9" s="1"/>
+      <x:c r="Q9" s="1"/>
+      <x:c r="R9" s="1"/>
+      <x:c r="S9" s="1"/>
+      <x:c r="T9" s="1"/>
+      <x:c r="U9" t="str">
+        <x:f>IF(AND(ISNUMBER(Finalrunde!D38),ISNUMBER(Finalrunde!B41),Finalrunde!D38&lt;&gt;Finalrunde!B41),IF(Finalrunde!D38&gt;Finalrunde!B41,Finalrunde!U36,Finalrunde!U37),"")</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="24" customHeight="1">
+      <x:c r="A10" s="1" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B10" s="1" t="str">
+        <x:f>IF(U10="","",INDEX(Teilnehmer!$B$2:$B$10,MATCH(U10,Teilnehmer!$A$2:$A$10,0)))</x:f>
+      </x:c>
+      <x:c r="C10" s="1" t="str">
+        <x:f>IF(U10="","",INDEX(Teilnehmer!$D$2:$D$10,MATCH(U10,Teilnehmer!$A$2:$A$10,0)))</x:f>
+      </x:c>
+      <x:c r="D10" s="1" t="str">
+        <x:f>IF(U10="","",INDEX(Teilnehmer!$C$2:$C$10,MATCH(U10,Teilnehmer!$A$2:$A$10,0)))</x:f>
+      </x:c>
+      <x:c r="E10" s="1" t="str">
+        <x:f>IF(U10="","",INDEX(Teilnehmer!$I$2:$I$10,MATCH(U10,Teilnehmer!$A$2:$A$10,0))+SUM(IF(Finalrunde!U4=U10,IF(ISNUMBER(Finalrunde!D6),Finalrunde!D6,0),0),IF(Finalrunde!U5=U10,IF(ISNUMBER(Finalrunde!B9),Finalrunde!B9,0),0),IF(Finalrunde!U6=U10,IF(ISNUMBER(Finalrunde!H12),Finalrunde!H12,0),0),IF(Finalrunde!U7=U10,IF(ISNUMBER(Finalrunde!F15),Finalrunde!F15,0),0),IF(Finalrunde!U20=U10,IF(ISNUMBER(Finalrunde!D22),Finalrunde!D22,0),0),IF(Finalrunde!U21=U10,IF(ISNUMBER(Finalrunde!B25),Finalrunde!B25,0),0),IF(Finalrunde!U22=U10,IF(ISNUMBER(Finalrunde!H28),Finalrunde!H28,0),0),IF(Finalrunde!U23=U10,IF(ISNUMBER(Finalrunde!F31),Finalrunde!F31,0),0),IF(Finalrunde!U36=U10,IF(ISNUMBER(Finalrunde!D38),Finalrunde!D38,0),0),IF(Finalrunde!U37=U10,IF(ISNUMBER(Finalrunde!B41),Finalrunde!B41,0),0),IF(Finalrunde!U38=U10,IF(ISNUMBER(Finalrunde!H44),Finalrunde!H44,0),0),IF(Finalrunde!U39=U10,IF(ISNUMBER(Finalrunde!F47),Finalrunde!F47,0),0)))</x:f>
+      </x:c>
+      <x:c r="F10" s="1" t="str">
+        <x:f>IF(U10="","",INDEX(Teilnehmer!$J$2:$J$10,MATCH(U10,Teilnehmer!$A$2:$A$10,0))+SUM(IF(Finalrunde!U4=U10,IF(ISNUMBER(Finalrunde!D5),Finalrunde!D5,0),0),IF(Finalrunde!U5=U10,IF(ISNUMBER(Finalrunde!B8),Finalrunde!B8,0),0),IF(Finalrunde!U6=U10,IF(ISNUMBER(Finalrunde!H11),Finalrunde!H11,0),0),IF(Finalrunde!U7=U10,IF(ISNUMBER(Finalrunde!F14),Finalrunde!F14,0),0),IF(Finalrunde!U20=U10,IF(ISNUMBER(Finalrunde!D21),Finalrunde!D21,0),0),IF(Finalrunde!U21=U10,IF(ISNUMBER(Finalrunde!B24),Finalrunde!B24,0),0),IF(Finalrunde!U22=U10,IF(ISNUMBER(Finalrunde!H27),Finalrunde!H27,0),0),IF(Finalrunde!U23=U10,IF(ISNUMBER(Finalrunde!F30),Finalrunde!F30,0),0),IF(Finalrunde!U36=U10,IF(ISNUMBER(Finalrunde!D37),Finalrunde!D37,0),0),IF(Finalrunde!U37=U10,IF(ISNUMBER(Finalrunde!B40),Finalrunde!B40,0),0),IF(Finalrunde!U38=U10,IF(ISNUMBER(Finalrunde!H43),Finalrunde!H43,0),0),IF(Finalrunde!U39=U10,IF(ISNUMBER(Finalrunde!F46),Finalrunde!F46,0),0)))</x:f>
+      </x:c>
+      <x:c r="G10" s="1" t="str">
+        <x:f>IF(U10="","",INDEX(Teilnehmer!$K$2:$K$10,MATCH(U10,Teilnehmer!$A$2:$A$10,0))+SUM(IF(Finalrunde!U4=U10,IF(ISNUMBER(Finalrunde!E5),Finalrunde!E5,0),0),IF(Finalrunde!U5=U10,IF(ISNUMBER(Finalrunde!C8),Finalrunde!C8,0),0),IF(Finalrunde!U6=U10,IF(ISNUMBER(Finalrunde!I11),Finalrunde!I11,0),0),IF(Finalrunde!U7=U10,IF(ISNUMBER(Finalrunde!G14),Finalrunde!G14,0),0),IF(Finalrunde!U20=U10,IF(ISNUMBER(Finalrunde!E21),Finalrunde!E21,0),0),IF(Finalrunde!U21=U10,IF(ISNUMBER(Finalrunde!C24),Finalrunde!C24,0),0),IF(Finalrunde!U22=U10,IF(ISNUMBER(Finalrunde!I27),Finalrunde!I27,0),0),IF(Finalrunde!U23=U10,IF(ISNUMBER(Finalrunde!G30),Finalrunde!G30,0),0),IF(Finalrunde!U36=U10,IF(ISNUMBER(Finalrunde!E37),Finalrunde!E37,0),0),IF(Finalrunde!U37=U10,IF(ISNUMBER(Finalrunde!C40),Finalrunde!C40,0),0),IF(Finalrunde!U38=U10,IF(ISNUMBER(Finalrunde!I43),Finalrunde!I43,0),0),IF(Finalrunde!U39=U10,IF(ISNUMBER(Finalrunde!G46),Finalrunde!G46,0),0)))</x:f>
+      </x:c>
+      <x:c r="H10" s="73" t="str">
+        <x:f>IF(U10="","",MAX(IF(U10=1,'Gruppe A'!Q4,0),IF(U10=4,'Gruppe A'!Q7,0),IF(U10=5,'Gruppe A'!Q10,0),IF(U10=8,'Gruppe A'!Q13,0),IF(U10=2,'Gruppe B'!Q4,0),IF(U10=3,'Gruppe B'!Q7,0),IF(U10=6,'Gruppe B'!Q10,0),IF(U10=7,'Gruppe B'!Q13,0),IF(U10=9,'Gruppe B'!Q16,0),IF(AND(Finalrunde!U4=U10,Finalrunde!D6=2,Finalrunde!E5&gt;0),Finalrunde!D5/Finalrunde!E5,0),IF(AND(Finalrunde!U5=U10,Finalrunde!B9=2,Finalrunde!C8&gt;0),Finalrunde!B8/Finalrunde!C8,0),IF(AND(Finalrunde!U6=U10,Finalrunde!H12=2,Finalrunde!I11&gt;0),Finalrunde!H11/Finalrunde!I11,0),IF(AND(Finalrunde!U7=U10,Finalrunde!F15=2,Finalrunde!G14&gt;0),Finalrunde!F14/Finalrunde!G14,0),IF(AND(Finalrunde!U20=U10,Finalrunde!D22=2,Finalrunde!E21&gt;0),Finalrunde!D21/Finalrunde!E21,0),IF(AND(Finalrunde!U21=U10,Finalrunde!B25=2,Finalrunde!C24&gt;0),Finalrunde!B24/Finalrunde!C24,0),IF(AND(Finalrunde!U22=U10,Finalrunde!H28=2,Finalrunde!I27&gt;0),Finalrunde!H27/Finalrunde!I27,0),IF(AND(Finalrunde!U23=U10,Finalrunde!F31=2,Finalrunde!G30&gt;0),Finalrunde!F30/Finalrunde!G30,0),IF(AND(Finalrunde!U36=U10,Finalrunde!D38=2,Finalrunde!E37&gt;0),Finalrunde!D37/Finalrunde!E37,0),IF(AND(Finalrunde!U37=U10,Finalrunde!B41=2,Finalrunde!C40&gt;0),Finalrunde!B40/Finalrunde!C40,0),IF(AND(Finalrunde!U38=U10,Finalrunde!H44=2,Finalrunde!I43&gt;0),Finalrunde!H43/Finalrunde!I43,0),IF(AND(Finalrunde!U39=U10,Finalrunde!F47=2,Finalrunde!G46&gt;0),Finalrunde!F46/Finalrunde!G46,0)))</x:f>
+      </x:c>
+      <x:c r="I10" s="73" t="str">
+        <x:f>IF(G10&gt;0,TRUNC(F10/G10,3),"")</x:f>
+      </x:c>
+      <x:c r="J10" s="1" t="str">
+        <x:f>IF(U10="","",MAX(INDEX(Teilnehmer!$M$2:$M$10,MATCH(U10,Teilnehmer!$A$2:$A$10,0)),IF(Finalrunde!U4=U10,IF(ISNUMBER(Finalrunde!E7),Finalrunde!E7,0),0),IF(Finalrunde!U5=U10,IF(ISNUMBER(Finalrunde!C10),Finalrunde!C10,0),0),IF(Finalrunde!U6=U10,IF(ISNUMBER(Finalrunde!I13),Finalrunde!I13,0),0),IF(Finalrunde!U7=U10,IF(ISNUMBER(Finalrunde!G16),Finalrunde!G16,0),0),IF(Finalrunde!U20=U10,IF(ISNUMBER(Finalrunde!E23),Finalrunde!E23,0),0),IF(Finalrunde!U21=U10,IF(ISNUMBER(Finalrunde!C26),Finalrunde!C26,0),0),IF(Finalrunde!U22=U10,IF(ISNUMBER(Finalrunde!I29),Finalrunde!I29,0),0),IF(Finalrunde!U23=U10,IF(ISNUMBER(Finalrunde!G32),Finalrunde!G32,0),0),IF(Finalrunde!U36=U10,IF(ISNUMBER(Finalrunde!E39),Finalrunde!E39,0),0),IF(Finalrunde!U37=U10,IF(ISNUMBER(Finalrunde!C42),Finalrunde!C42,0),0),IF(Finalrunde!U38=U10,IF(ISNUMBER(Finalrunde!I45),Finalrunde!I45,0),0),IF(Finalrunde!U39=U10,IF(ISNUMBER(Finalrunde!G48),Finalrunde!G48,0),0)))</x:f>
+      </x:c>
+      <x:c r="K10" s="1"/>
+      <x:c r="L10" s="1"/>
+      <x:c r="M10" s="1"/>
+      <x:c r="N10" s="1"/>
+      <x:c r="O10" s="1"/>
+      <x:c r="P10" s="1"/>
+      <x:c r="Q10" s="1"/>
+      <x:c r="R10" s="1"/>
+      <x:c r="S10" s="1"/>
+      <x:c r="T10" s="1"/>
+      <x:c r="U10" t="str">
+        <x:f>IF(AND(ISNUMBER(Finalrunde!D38),ISNUMBER(Finalrunde!B41),Finalrunde!D38&lt;&gt;Finalrunde!B41),IF(Finalrunde!D38&lt;Finalrunde!B41,Finalrunde!U36,Finalrunde!U37),"")</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="24" customHeight="1">
+      <x:c r="A11" s="1" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B11" s="1" t="str">
+        <x:f>IF(U11="","",INDEX(Teilnehmer!$B$2:$B$10,MATCH(U11,Teilnehmer!$A$2:$A$10,0)))</x:f>
+      </x:c>
+      <x:c r="C11" s="1" t="str">
+        <x:f>IF(U11="","",INDEX(Teilnehmer!$D$2:$D$10,MATCH(U11,Teilnehmer!$A$2:$A$10,0)))</x:f>
+      </x:c>
+      <x:c r="D11" s="1" t="str">
+        <x:f>IF(U11="","",INDEX(Teilnehmer!$C$2:$C$10,MATCH(U11,Teilnehmer!$A$2:$A$10,0)))</x:f>
+      </x:c>
+      <x:c r="E11" s="1" t="str">
+        <x:f>IF(U11="","",INDEX(Teilnehmer!$I$2:$I$10,MATCH(U11,Teilnehmer!$A$2:$A$10,0))+SUM(IF(Finalrunde!U4=U11,IF(ISNUMBER(Finalrunde!D6),Finalrunde!D6,0),0),IF(Finalrunde!U5=U11,IF(ISNUMBER(Finalrunde!B9),Finalrunde!B9,0),0),IF(Finalrunde!U6=U11,IF(ISNUMBER(Finalrunde!H12),Finalrunde!H12,0),0),IF(Finalrunde!U7=U11,IF(ISNUMBER(Finalrunde!F15),Finalrunde!F15,0),0),IF(Finalrunde!U20=U11,IF(ISNUMBER(Finalrunde!D22),Finalrunde!D22,0),0),IF(Finalrunde!U21=U11,IF(ISNUMBER(Finalrunde!B25),Finalrunde!B25,0),0),IF(Finalrunde!U22=U11,IF(ISNUMBER(Finalrunde!H28),Finalrunde!H28,0),0),IF(Finalrunde!U23=U11,IF(ISNUMBER(Finalrunde!F31),Finalrunde!F31,0),0),IF(Finalrunde!U36=U11,IF(ISNUMBER(Finalrunde!D38),Finalrunde!D38,0),0),IF(Finalrunde!U37=U11,IF(ISNUMBER(Finalrunde!B41),Finalrunde!B41,0),0),IF(Finalrunde!U38=U11,IF(ISNUMBER(Finalrunde!H44),Finalrunde!H44,0),0),IF(Finalrunde!U39=U11,IF(ISNUMBER(Finalrunde!F47),Finalrunde!F47,0),0)))</x:f>
+      </x:c>
+      <x:c r="F11" s="1" t="str">
+        <x:f>IF(U11="","",INDEX(Teilnehmer!$J$2:$J$10,MATCH(U11,Teilnehmer!$A$2:$A$10,0))+SUM(IF(Finalrunde!U4=U11,IF(ISNUMBER(Finalrunde!D5),Finalrunde!D5,0),0),IF(Finalrunde!U5=U11,IF(ISNUMBER(Finalrunde!B8),Finalrunde!B8,0),0),IF(Finalrunde!U6=U11,IF(ISNUMBER(Finalrunde!H11),Finalrunde!H11,0),0),IF(Finalrunde!U7=U11,IF(ISNUMBER(Finalrunde!F14),Finalrunde!F14,0),0),IF(Finalrunde!U20=U11,IF(ISNUMBER(Finalrunde!D21),Finalrunde!D21,0),0),IF(Finalrunde!U21=U11,IF(ISNUMBER(Finalrunde!B24),Finalrunde!B24,0),0),IF(Finalrunde!U22=U11,IF(ISNUMBER(Finalrunde!H27),Finalrunde!H27,0),0),IF(Finalrunde!U23=U11,IF(ISNUMBER(Finalrunde!F30),Finalrunde!F30,0),0),IF(Finalrunde!U36=U11,IF(ISNUMBER(Finalrunde!D37),Finalrunde!D37,0),0),IF(Finalrunde!U37=U11,IF(ISNUMBER(Finalrunde!B40),Finalrunde!B40,0),0),IF(Finalrunde!U38=U11,IF(ISNUMBER(Finalrunde!H43),Finalrunde!H43,0),0),IF(Finalrunde!U39=U11,IF(ISNUMBER(Finalrunde!F46),Finalrunde!F46,0),0)))</x:f>
+      </x:c>
+      <x:c r="G11" s="1" t="str">
+        <x:f>IF(U11="","",INDEX(Teilnehmer!$K$2:$K$10,MATCH(U11,Teilnehmer!$A$2:$A$10,0))+SUM(IF(Finalrunde!U4=U11,IF(ISNUMBER(Finalrunde!E5),Finalrunde!E5,0),0),IF(Finalrunde!U5=U11,IF(ISNUMBER(Finalrunde!C8),Finalrunde!C8,0),0),IF(Finalrunde!U6=U11,IF(ISNUMBER(Finalrunde!I11),Finalrunde!I11,0),0),IF(Finalrunde!U7=U11,IF(ISNUMBER(Finalrunde!G14),Finalrunde!G14,0),0),IF(Finalrunde!U20=U11,IF(ISNUMBER(Finalrunde!E21),Finalrunde!E21,0),0),IF(Finalrunde!U21=U11,IF(ISNUMBER(Finalrunde!C24),Finalrunde!C24,0),0),IF(Finalrunde!U22=U11,IF(ISNUMBER(Finalrunde!I27),Finalrunde!I27,0),0),IF(Finalrunde!U23=U11,IF(ISNUMBER(Finalrunde!G30),Finalrunde!G30,0),0),IF(Finalrunde!U36=U11,IF(ISNUMBER(Finalrunde!E37),Finalrunde!E37,0),0),IF(Finalrunde!U37=U11,IF(ISNUMBER(Finalrunde!C40),Finalrunde!C40,0),0),IF(Finalrunde!U38=U11,IF(ISNUMBER(Finalrunde!I43),Finalrunde!I43,0),0),IF(Finalrunde!U39=U11,IF(ISNUMBER(Finalrunde!G46),Finalrunde!G46,0),0)))</x:f>
+      </x:c>
+      <x:c r="H11" s="73" t="str">
+        <x:f>IF(U11="","",MAX(IF(U11=1,'Gruppe A'!Q4,0),IF(U11=4,'Gruppe A'!Q7,0),IF(U11=5,'Gruppe A'!Q10,0),IF(U11=8,'Gruppe A'!Q13,0),IF(U11=2,'Gruppe B'!Q4,0),IF(U11=3,'Gruppe B'!Q7,0),IF(U11=6,'Gruppe B'!Q10,0),IF(U11=7,'Gruppe B'!Q13,0),IF(U11=9,'Gruppe B'!Q16,0),IF(AND(Finalrunde!U4=U11,Finalrunde!D6=2,Finalrunde!E5&gt;0),Finalrunde!D5/Finalrunde!E5,0),IF(AND(Finalrunde!U5=U11,Finalrunde!B9=2,Finalrunde!C8&gt;0),Finalrunde!B8/Finalrunde!C8,0),IF(AND(Finalrunde!U6=U11,Finalrunde!H12=2,Finalrunde!I11&gt;0),Finalrunde!H11/Finalrunde!I11,0),IF(AND(Finalrunde!U7=U11,Finalrunde!F15=2,Finalrunde!G14&gt;0),Finalrunde!F14/Finalrunde!G14,0),IF(AND(Finalrunde!U20=U11,Finalrunde!D22=2,Finalrunde!E21&gt;0),Finalrunde!D21/Finalrunde!E21,0),IF(AND(Finalrunde!U21=U11,Finalrunde!B25=2,Finalrunde!C24&gt;0),Finalrunde!B24/Finalrunde!C24,0),IF(AND(Finalrunde!U22=U11,Finalrunde!H28=2,Finalrunde!I27&gt;0),Finalrunde!H27/Finalrunde!I27,0),IF(AND(Finalrunde!U23=U11,Finalrunde!F31=2,Finalrunde!G30&gt;0),Finalrunde!F30/Finalrunde!G30,0),IF(AND(Finalrunde!U36=U11,Finalrunde!D38=2,Finalrunde!E37&gt;0),Finalrunde!D37/Finalrunde!E37,0),IF(AND(Finalrunde!U37=U11,Finalrunde!B41=2,Finalrunde!C40&gt;0),Finalrunde!B40/Finalrunde!C40,0),IF(AND(Finalrunde!U38=U11,Finalrunde!H44=2,Finalrunde!I43&gt;0),Finalrunde!H43/Finalrunde!I43,0),IF(AND(Finalrunde!U39=U11,Finalrunde!F47=2,Finalrunde!G46&gt;0),Finalrunde!F46/Finalrunde!G46,0)))</x:f>
+      </x:c>
+      <x:c r="I11" s="73" t="str">
+        <x:f>IF(G11&gt;0,TRUNC(F11/G11,3),"")</x:f>
+      </x:c>
+      <x:c r="J11" s="1" t="str">
+        <x:f>IF(U11="","",MAX(INDEX(Teilnehmer!$M$2:$M$10,MATCH(U11,Teilnehmer!$A$2:$A$10,0)),IF(Finalrunde!U4=U11,IF(ISNUMBER(Finalrunde!E7),Finalrunde!E7,0),0),IF(Finalrunde!U5=U11,IF(ISNUMBER(Finalrunde!C10),Finalrunde!C10,0),0),IF(Finalrunde!U6=U11,IF(ISNUMBER(Finalrunde!I13),Finalrunde!I13,0),0),IF(Finalrunde!U7=U11,IF(ISNUMBER(Finalrunde!G16),Finalrunde!G16,0),0),IF(Finalrunde!U20=U11,IF(ISNUMBER(Finalrunde!E23),Finalrunde!E23,0),0),IF(Finalrunde!U21=U11,IF(ISNUMBER(Finalrunde!C26),Finalrunde!C26,0),0),IF(Finalrunde!U22=U11,IF(ISNUMBER(Finalrunde!I29),Finalrunde!I29,0),0),IF(Finalrunde!U23=U11,IF(ISNUMBER(Finalrunde!G32),Finalrunde!G32,0),0),IF(Finalrunde!U36=U11,IF(ISNUMBER(Finalrunde!E39),Finalrunde!E39,0),0),IF(Finalrunde!U37=U11,IF(ISNUMBER(Finalrunde!C42),Finalrunde!C42,0),0),IF(Finalrunde!U38=U11,IF(ISNUMBER(Finalrunde!I45),Finalrunde!I45,0),0),IF(Finalrunde!U39=U11,IF(ISNUMBER(Finalrunde!G48),Finalrunde!G48,0),0)))</x:f>
+      </x:c>
+      <x:c r="K11" s="1"/>
+      <x:c r="L11" s="1"/>
+      <x:c r="M11" s="1"/>
+      <x:c r="N11" s="1"/>
+      <x:c r="O11" s="1"/>
+      <x:c r="P11" s="1"/>
+      <x:c r="Q11" s="1"/>
+      <x:c r="R11" s="1"/>
+      <x:c r="S11" s="1"/>
+      <x:c r="T11" s="1"/>
+      <x:c r="U11" t="str">
+        <x:f>IF(AND(ISNUMBER(Finalrunde!H44),ISNUMBER(Finalrunde!F47),Finalrunde!H44&lt;&gt;Finalrunde!F47),IF(Finalrunde!H44&gt;Finalrunde!F47,Finalrunde!U38,Finalrunde!U39),"")</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="24" customHeight="1">
+      <x:c r="A12" s="1" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B12" s="1" t="str">
+        <x:f>IF(U12="","",INDEX(Teilnehmer!$B$2:$B$10,MATCH(U12,Teilnehmer!$A$2:$A$10,0)))</x:f>
+      </x:c>
+      <x:c r="C12" s="1" t="str">
+        <x:f>IF(U12="","",INDEX(Teilnehmer!$D$2:$D$10,MATCH(U12,Teilnehmer!$A$2:$A$10,0)))</x:f>
+      </x:c>
+      <x:c r="D12" s="1" t="str">
+        <x:f>IF(U12="","",INDEX(Teilnehmer!$C$2:$C$10,MATCH(U12,Teilnehmer!$A$2:$A$10,0)))</x:f>
+      </x:c>
+      <x:c r="E12" s="1" t="str">
+        <x:f>IF(U12="","",INDEX(Teilnehmer!$I$2:$I$10,MATCH(U12,Teilnehmer!$A$2:$A$10,0))+SUM(IF(Finalrunde!U4=U12,IF(ISNUMBER(Finalrunde!D6),Finalrunde!D6,0),0),IF(Finalrunde!U5=U12,IF(ISNUMBER(Finalrunde!B9),Finalrunde!B9,0),0),IF(Finalrunde!U6=U12,IF(ISNUMBER(Finalrunde!H12),Finalrunde!H12,0),0),IF(Finalrunde!U7=U12,IF(ISNUMBER(Finalrunde!F15),Finalrunde!F15,0),0),IF(Finalrunde!U20=U12,IF(ISNUMBER(Finalrunde!D22),Finalrunde!D22,0),0),IF(Finalrunde!U21=U12,IF(ISNUMBER(Finalrunde!B25),Finalrunde!B25,0),0),IF(Finalrunde!U22=U12,IF(ISNUMBER(Finalrunde!H28),Finalrunde!H28,0),0),IF(Finalrunde!U23=U12,IF(ISNUMBER(Finalrunde!F31),Finalrunde!F31,0),0),IF(Finalrunde!U36=U12,IF(ISNUMBER(Finalrunde!D38),Finalrunde!D38,0),0),IF(Finalrunde!U37=U12,IF(ISNUMBER(Finalrunde!B41),Finalrunde!B41,0),0),IF(Finalrunde!U38=U12,IF(ISNUMBER(Finalrunde!H44),Finalrunde!H44,0),0),IF(Finalrunde!U39=U12,IF(ISNUMBER(Finalrunde!F47),Finalrunde!F47,0),0)))</x:f>
+      </x:c>
+      <x:c r="F12" s="1" t="str">
+        <x:f>IF(U12="","",INDEX(Teilnehmer!$J$2:$J$10,MATCH(U12,Teilnehmer!$A$2:$A$10,0))+SUM(IF(Finalrunde!U4=U12,IF(ISNUMBER(Finalrunde!D5),Finalrunde!D5,0),0),IF(Finalrunde!U5=U12,IF(ISNUMBER(Finalrunde!B8),Finalrunde!B8,0),0),IF(Finalrunde!U6=U12,IF(ISNUMBER(Finalrunde!H11),Finalrunde!H11,0),0),IF(Finalrunde!U7=U12,IF(ISNUMBER(Finalrunde!F14),Finalrunde!F14,0),0),IF(Finalrunde!U20=U12,IF(ISNUMBER(Finalrunde!D21),Finalrunde!D21,0),0),IF(Finalrunde!U21=U12,IF(ISNUMBER(Finalrunde!B24),Finalrunde!B24,0),0),IF(Finalrunde!U22=U12,IF(ISNUMBER(Finalrunde!H27),Finalrunde!H27,0),0),IF(Finalrunde!U23=U12,IF(ISNUMBER(Finalrunde!F30),Finalrunde!F30,0),0),IF(Finalrunde!U36=U12,IF(ISNUMBER(Finalrunde!D37),Finalrunde!D37,0),0),IF(Finalrunde!U37=U12,IF(ISNUMBER(Finalrunde!B40),Finalrunde!B40,0),0),IF(Finalrunde!U38=U12,IF(ISNUMBER(Finalrunde!H43),Finalrunde!H43,0),0),IF(Finalrunde!U39=U12,IF(ISNUMBER(Finalrunde!F46),Finalrunde!F46,0),0)))</x:f>
+      </x:c>
+      <x:c r="G12" s="1" t="str">
+        <x:f>IF(U12="","",INDEX(Teilnehmer!$K$2:$K$10,MATCH(U12,Teilnehmer!$A$2:$A$10,0))+SUM(IF(Finalrunde!U4=U12,IF(ISNUMBER(Finalrunde!E5),Finalrunde!E5,0),0),IF(Finalrunde!U5=U12,IF(ISNUMBER(Finalrunde!C8),Finalrunde!C8,0),0),IF(Finalrunde!U6=U12,IF(ISNUMBER(Finalrunde!I11),Finalrunde!I11,0),0),IF(Finalrunde!U7=U12,IF(ISNUMBER(Finalrunde!G14),Finalrunde!G14,0),0),IF(Finalrunde!U20=U12,IF(ISNUMBER(Finalrunde!E21),Finalrunde!E21,0),0),IF(Finalrunde!U21=U12,IF(ISNUMBER(Finalrunde!C24),Finalrunde!C24,0),0),IF(Finalrunde!U22=U12,IF(ISNUMBER(Finalrunde!I27),Finalrunde!I27,0),0),IF(Finalrunde!U23=U12,IF(ISNUMBER(Finalrunde!G30),Finalrunde!G30,0),0),IF(Finalrunde!U36=U12,IF(ISNUMBER(Finalrunde!E37),Finalrunde!E37,0),0),IF(Finalrunde!U37=U12,IF(ISNUMBER(Finalrunde!C40),Finalrunde!C40,0),0),IF(Finalrunde!U38=U12,IF(ISNUMBER(Finalrunde!I43),Finalrunde!I43,0),0),IF(Finalrunde!U39=U12,IF(ISNUMBER(Finalrunde!G46),Finalrunde!G46,0),0)))</x:f>
+      </x:c>
+      <x:c r="H12" s="73" t="str">
+        <x:f>IF(U12="","",MAX(IF(U12=1,'Gruppe A'!Q4,0),IF(U12=4,'Gruppe A'!Q7,0),IF(U12=5,'Gruppe A'!Q10,0),IF(U12=8,'Gruppe A'!Q13,0),IF(U12=2,'Gruppe B'!Q4,0),IF(U12=3,'Gruppe B'!Q7,0),IF(U12=6,'Gruppe B'!Q10,0),IF(U12=7,'Gruppe B'!Q13,0),IF(U12=9,'Gruppe B'!Q16,0),IF(AND(Finalrunde!U4=U12,Finalrunde!D6=2,Finalrunde!E5&gt;0),Finalrunde!D5/Finalrunde!E5,0),IF(AND(Finalrunde!U5=U12,Finalrunde!B9=2,Finalrunde!C8&gt;0),Finalrunde!B8/Finalrunde!C8,0),IF(AND(Finalrunde!U6=U12,Finalrunde!H12=2,Finalrunde!I11&gt;0),Finalrunde!H11/Finalrunde!I11,0),IF(AND(Finalrunde!U7=U12,Finalrunde!F15=2,Finalrunde!G14&gt;0),Finalrunde!F14/Finalrunde!G14,0),IF(AND(Finalrunde!U20=U12,Finalrunde!D22=2,Finalrunde!E21&gt;0),Finalrunde!D21/Finalrunde!E21,0),IF(AND(Finalrunde!U21=U12,Finalrunde!B25=2,Finalrunde!C24&gt;0),Finalrunde!B24/Finalrunde!C24,0),IF(AND(Finalrunde!U22=U12,Finalrunde!H28=2,Finalrunde!I27&gt;0),Finalrunde!H27/Finalrunde!I27,0),IF(AND(Finalrunde!U23=U12,Finalrunde!F31=2,Finalrunde!G30&gt;0),Finalrunde!F30/Finalrunde!G30,0),IF(AND(Finalrunde!U36=U12,Finalrunde!D38=2,Finalrunde!E37&gt;0),Finalrunde!D37/Finalrunde!E37,0),IF(AND(Finalrunde!U37=U12,Finalrunde!B41=2,Finalrunde!C40&gt;0),Finalrunde!B40/Finalrunde!C40,0),IF(AND(Finalrunde!U38=U12,Finalrunde!H44=2,Finalrunde!I43&gt;0),Finalrunde!H43/Finalrunde!I43,0),IF(AND(Finalrunde!U39=U12,Finalrunde!F47=2,Finalrunde!G46&gt;0),Finalrunde!F46/Finalrunde!G46,0)))</x:f>
+      </x:c>
+      <x:c r="I12" s="73" t="str">
+        <x:f>IF(G12&gt;0,TRUNC(F12/G12,3),"")</x:f>
+      </x:c>
+      <x:c r="J12" s="1" t="str">
+        <x:f>IF(U12="","",MAX(INDEX(Teilnehmer!$M$2:$M$10,MATCH(U12,Teilnehmer!$A$2:$A$10,0)),IF(Finalrunde!U4=U12,IF(ISNUMBER(Finalrunde!E7),Finalrunde!E7,0),0),IF(Finalrunde!U5=U12,IF(ISNUMBER(Finalrunde!C10),Finalrunde!C10,0),0),IF(Finalrunde!U6=U12,IF(ISNUMBER(Finalrunde!I13),Finalrunde!I13,0),0),IF(Finalrunde!U7=U12,IF(ISNUMBER(Finalrunde!G16),Finalrunde!G16,0),0),IF(Finalrunde!U20=U12,IF(ISNUMBER(Finalrunde!E23),Finalrunde!E23,0),0),IF(Finalrunde!U21=U12,IF(ISNUMBER(Finalrunde!C26),Finalrunde!C26,0),0),IF(Finalrunde!U22=U12,IF(ISNUMBER(Finalrunde!I29),Finalrunde!I29,0),0),IF(Finalrunde!U23=U12,IF(ISNUMBER(Finalrunde!G32),Finalrunde!G32,0),0),IF(Finalrunde!U36=U12,IF(ISNUMBER(Finalrunde!E39),Finalrunde!E39,0),0),IF(Finalrunde!U37=U12,IF(ISNUMBER(Finalrunde!C42),Finalrunde!C42,0),0),IF(Finalrunde!U38=U12,IF(ISNUMBER(Finalrunde!I45),Finalrunde!I45,0),0),IF(Finalrunde!U39=U12,IF(ISNUMBER(Finalrunde!G48),Finalrunde!G48,0),0)))</x:f>
+      </x:c>
+      <x:c r="K12" s="1"/>
+      <x:c r="L12" s="1"/>
+      <x:c r="M12" s="1"/>
+      <x:c r="N12" s="1"/>
+      <x:c r="O12" s="1"/>
+      <x:c r="P12" s="1"/>
+      <x:c r="Q12" s="1"/>
+      <x:c r="R12" s="1"/>
+      <x:c r="S12" s="1"/>
+      <x:c r="T12" s="1"/>
+      <x:c r="U12" t="str">
+        <x:f>IF(AND(ISNUMBER(Finalrunde!H44),ISNUMBER(Finalrunde!F47),Finalrunde!H44&lt;&gt;Finalrunde!F47),IF(Finalrunde!H44&lt;Finalrunde!F47,Finalrunde!U38,Finalrunde!U39),"")</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="24" customHeight="1">
+      <x:c r="A13" s="1" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B13" s="1" t="str">
+        <x:f>IF(U13="","",INDEX(Teilnehmer!$B$2:$B$10,MATCH(U13,Teilnehmer!$A$2:$A$10,0)))</x:f>
+      </x:c>
+      <x:c r="C13" s="1" t="str">
+        <x:f>IF(U13="","",INDEX(Teilnehmer!$D$2:$D$10,MATCH(U13,Teilnehmer!$A$2:$A$10,0)))</x:f>
+      </x:c>
+      <x:c r="D13" s="1" t="str">
+        <x:f>IF(U13="","",INDEX(Teilnehmer!$C$2:$C$10,MATCH(U13,Teilnehmer!$A$2:$A$10,0)))</x:f>
+      </x:c>
+      <x:c r="E13" s="1" t="str">
+        <x:f>IF(U13="","",INDEX(Teilnehmer!$I$2:$I$10,MATCH(U13,Teilnehmer!$A$2:$A$10,0))+SUM(IF(Finalrunde!U4=U13,IF(ISNUMBER(Finalrunde!D6),Finalrunde!D6,0),0),IF(Finalrunde!U5=U13,IF(ISNUMBER(Finalrunde!B9),Finalrunde!B9,0),0),IF(Finalrunde!U6=U13,IF(ISNUMBER(Finalrunde!H12),Finalrunde!H12,0),0),IF(Finalrunde!U7=U13,IF(ISNUMBER(Finalrunde!F15),Finalrunde!F15,0),0),IF(Finalrunde!U20=U13,IF(ISNUMBER(Finalrunde!D22),Finalrunde!D22,0),0),IF(Finalrunde!U21=U13,IF(ISNUMBER(Finalrunde!B25),Finalrunde!B25,0),0),IF(Finalrunde!U22=U13,IF(ISNUMBER(Finalrunde!H28),Finalrunde!H28,0),0),IF(Finalrunde!U23=U13,IF(ISNUMBER(Finalrunde!F31),Finalrunde!F31,0),0),IF(Finalrunde!U36=U13,IF(ISNUMBER(Finalrunde!D38),Finalrunde!D38,0),0),IF(Finalrunde!U37=U13,IF(ISNUMBER(Finalrunde!B41),Finalrunde!B41,0),0),IF(Finalrunde!U38=U13,IF(ISNUMBER(Finalrunde!H44),Finalrunde!H44,0),0),IF(Finalrunde!U39=U13,IF(ISNUMBER(Finalrunde!F47),Finalrunde!F47,0),0)))</x:f>
+      </x:c>
+      <x:c r="F13" s="1" t="str">
+        <x:f>IF(U13="","",INDEX(Teilnehmer!$J$2:$J$10,MATCH(U13,Teilnehmer!$A$2:$A$10,0))+SUM(IF(Finalrunde!U4=U13,IF(ISNUMBER(Finalrunde!D5),Finalrunde!D5,0),0),IF(Finalrunde!U5=U13,IF(ISNUMBER(Finalrunde!B8),Finalrunde!B8,0),0),IF(Finalrunde!U6=U13,IF(ISNUMBER(Finalrunde!H11),Finalrunde!H11,0),0),IF(Finalrunde!U7=U13,IF(ISNUMBER(Finalrunde!F14),Finalrunde!F14,0),0),IF(Finalrunde!U20=U13,IF(ISNUMBER(Finalrunde!D21),Finalrunde!D21,0),0),IF(Finalrunde!U21=U13,IF(ISNUMBER(Finalrunde!B24),Finalrunde!B24,0),0),IF(Finalrunde!U22=U13,IF(ISNUMBER(Finalrunde!H27),Finalrunde!H27,0),0),IF(Finalrunde!U23=U13,IF(ISNUMBER(Finalrunde!F30),Finalrunde!F30,0),0),IF(Finalrunde!U36=U13,IF(ISNUMBER(Finalrunde!D37),Finalrunde!D37,0),0),IF(Finalrunde!U37=U13,IF(ISNUMBER(Finalrunde!B40),Finalrunde!B40,0),0),IF(Finalrunde!U38=U13,IF(ISNUMBER(Finalrunde!H43),Finalrunde!H43,0),0),IF(Finalrunde!U39=U13,IF(ISNUMBER(Finalrunde!F46),Finalrunde!F46,0),0)))</x:f>
+      </x:c>
+      <x:c r="G13" s="1" t="str">
+        <x:f>IF(U13="","",INDEX(Teilnehmer!$K$2:$K$10,MATCH(U13,Teilnehmer!$A$2:$A$10,0))+SUM(IF(Finalrunde!U4=U13,IF(ISNUMBER(Finalrunde!E5),Finalrunde!E5,0),0),IF(Finalrunde!U5=U13,IF(ISNUMBER(Finalrunde!C8),Finalrunde!C8,0),0),IF(Finalrunde!U6=U13,IF(ISNUMBER(Finalrunde!I11),Finalrunde!I11,0),0),IF(Finalrunde!U7=U13,IF(ISNUMBER(Finalrunde!G14),Finalrunde!G14,0),0),IF(Finalrunde!U20=U13,IF(ISNUMBER(Finalrunde!E21),Finalrunde!E21,0),0),IF(Finalrunde!U21=U13,IF(ISNUMBER(Finalrunde!C24),Finalrunde!C24,0),0),IF(Finalrunde!U22=U13,IF(ISNUMBER(Finalrunde!I27),Finalrunde!I27,0),0),IF(Finalrunde!U23=U13,IF(ISNUMBER(Finalrunde!G30),Finalrunde!G30,0),0),IF(Finalrunde!U36=U13,IF(ISNUMBER(Finalrunde!E37),Finalrunde!E37,0),0),IF(Finalrunde!U37=U13,IF(ISNUMBER(Finalrunde!C40),Finalrunde!C40,0),0),IF(Finalrunde!U38=U13,IF(ISNUMBER(Finalrunde!I43),Finalrunde!I43,0),0),IF(Finalrunde!U39=U13,IF(ISNUMBER(Finalrunde!G46),Finalrunde!G46,0),0)))</x:f>
+      </x:c>
+      <x:c r="H13" s="73" t="str">
+        <x:f>IF(U13="","",MAX(IF(U13=1,'Gruppe A'!Q4,0),IF(U13=4,'Gruppe A'!Q7,0),IF(U13=5,'Gruppe A'!Q10,0),IF(U13=8,'Gruppe A'!Q13,0),IF(U13=2,'Gruppe B'!Q4,0),IF(U13=3,'Gruppe B'!Q7,0),IF(U13=6,'Gruppe B'!Q10,0),IF(U13=7,'Gruppe B'!Q13,0),IF(U13=9,'Gruppe B'!Q16,0),IF(AND(Finalrunde!U4=U13,Finalrunde!D6=2,Finalrunde!E5&gt;0),Finalrunde!D5/Finalrunde!E5,0),IF(AND(Finalrunde!U5=U13,Finalrunde!B9=2,Finalrunde!C8&gt;0),Finalrunde!B8/Finalrunde!C8,0),IF(AND(Finalrunde!U6=U13,Finalrunde!H12=2,Finalrunde!I11&gt;0),Finalrunde!H11/Finalrunde!I11,0),IF(AND(Finalrunde!U7=U13,Finalrunde!F15=2,Finalrunde!G14&gt;0),Finalrunde!F14/Finalrunde!G14,0),IF(AND(Finalrunde!U20=U13,Finalrunde!D22=2,Finalrunde!E21&gt;0),Finalrunde!D21/Finalrunde!E21,0),IF(AND(Finalrunde!U21=U13,Finalrunde!B25=2,Finalrunde!C24&gt;0),Finalrunde!B24/Finalrunde!C24,0),IF(AND(Finalrunde!U22=U13,Finalrunde!H28=2,Finalrunde!I27&gt;0),Finalrunde!H27/Finalrunde!I27,0),IF(AND(Finalrunde!U23=U13,Finalrunde!F31=2,Finalrunde!G30&gt;0),Finalrunde!F30/Finalrunde!G30,0),IF(AND(Finalrunde!U36=U13,Finalrunde!D38=2,Finalrunde!E37&gt;0),Finalrunde!D37/Finalrunde!E37,0),IF(AND(Finalrunde!U37=U13,Finalrunde!B41=2,Finalrunde!C40&gt;0),Finalrunde!B40/Finalrunde!C40,0),IF(AND(Finalrunde!U38=U13,Finalrunde!H44=2,Finalrunde!I43&gt;0),Finalrunde!H43/Finalrunde!I43,0),IF(AND(Finalrunde!U39=U13,Finalrunde!F47=2,Finalrunde!G46&gt;0),Finalrunde!F46/Finalrunde!G46,0)))</x:f>
+      </x:c>
+      <x:c r="I13" s="73" t="str">
+        <x:f>IF(G13&gt;0,TRUNC(F13/G13,3),"")</x:f>
+      </x:c>
+      <x:c r="J13" s="1" t="str">
+        <x:f>IF(U13="","",MAX(INDEX(Teilnehmer!$M$2:$M$10,MATCH(U13,Teilnehmer!$A$2:$A$10,0)),IF(Finalrunde!U4=U13,IF(ISNUMBER(Finalrunde!E7),Finalrunde!E7,0),0),IF(Finalrunde!U5=U13,IF(ISNUMBER(Finalrunde!C10),Finalrunde!C10,0),0),IF(Finalrunde!U6=U13,IF(ISNUMBER(Finalrunde!I13),Finalrunde!I13,0),0),IF(Finalrunde!U7=U13,IF(ISNUMBER(Finalrunde!G16),Finalrunde!G16,0),0),IF(Finalrunde!U20=U13,IF(ISNUMBER(Finalrunde!E23),Finalrunde!E23,0),0),IF(Finalrunde!U21=U13,IF(ISNUMBER(Finalrunde!C26),Finalrunde!C26,0),0),IF(Finalrunde!U22=U13,IF(ISNUMBER(Finalrunde!I29),Finalrunde!I29,0),0),IF(Finalrunde!U23=U13,IF(ISNUMBER(Finalrunde!G32),Finalrunde!G32,0),0),IF(Finalrunde!U36=U13,IF(ISNUMBER(Finalrunde!E39),Finalrunde!E39,0),0),IF(Finalrunde!U37=U13,IF(ISNUMBER(Finalrunde!C42),Finalrunde!C42,0),0),IF(Finalrunde!U38=U13,IF(ISNUMBER(Finalrunde!I45),Finalrunde!I45,0),0),IF(Finalrunde!U39=U13,IF(ISNUMBER(Finalrunde!G48),Finalrunde!G48,0),0)))</x:f>
+      </x:c>
+      <x:c r="K13" s="1"/>
+      <x:c r="L13" s="1"/>
+      <x:c r="M13" s="1"/>
+      <x:c r="N13" s="1"/>
+      <x:c r="O13" s="1"/>
+      <x:c r="P13" s="1"/>
+      <x:c r="Q13" s="1"/>
+      <x:c r="R13" s="1"/>
+      <x:c r="S13" s="1"/>
+      <x:c r="T13" s="1"/>
+      <x:c r="U13" t="str">
+        <x:f>IF(COUNTIF(Teilnehmer!$P$2:$P$10,"B5")=1,INDEX(Teilnehmer!$A$2:$A$10,MATCH("B5",Teilnehmer!$P$2:$P$10,0)),"")</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="24" customHeight="1">
+      <x:c r="A14" s="1"/>
+      <x:c r="B14" s="1"/>
+      <x:c r="C14" s="1"/>
+      <x:c r="D14" s="1"/>
+      <x:c r="E14" s="1"/>
+      <x:c r="F14" s="1"/>
+      <x:c r="G14" s="1"/>
+      <x:c r="H14" s="1"/>
+      <x:c r="I14" s="1"/>
+      <x:c r="J14" s="1"/>
+      <x:c r="K14" s="1"/>
+      <x:c r="L14" s="1"/>
+      <x:c r="M14" s="1"/>
+      <x:c r="N14" s="1"/>
+      <x:c r="O14" s="1"/>
+      <x:c r="P14" s="1"/>
+      <x:c r="Q14" s="1"/>
+      <x:c r="R14" s="1"/>
+      <x:c r="S14" s="1"/>
+      <x:c r="T14" s="1"/>
+    </x:row>
+    <x:row r="15" ht="24" customHeight="1">
+      <x:c r="A15" s="1" t="str">
+        <x:v>Rangliste aus Finalspielen. Gesamtstatistik umfasst Gruppen- und Finalrunde. Gruppenplatz 5 aus B = Gesamtplatz 9.</x:v>
+      </x:c>
+      <x:c r="B15" s="1"/>
+      <x:c r="C15" s="1"/>
+      <x:c r="D15" s="1"/>
+      <x:c r="E15" s="1"/>
+      <x:c r="F15" s="1"/>
+      <x:c r="G15" s="1"/>
+      <x:c r="H15" s="1"/>
+      <x:c r="I15" s="1"/>
+      <x:c r="J15" s="1"/>
+      <x:c r="K15" s="1"/>
+      <x:c r="L15" s="1"/>
+      <x:c r="M15" s="1"/>
+      <x:c r="N15" s="1"/>
+      <x:c r="O15" s="1"/>
+      <x:c r="P15" s="1"/>
+      <x:c r="Q15" s="1"/>
+      <x:c r="R15" s="1"/>
+      <x:c r="S15" s="1"/>
+      <x:c r="T15" s="1"/>
+    </x:row>
+    <x:row r="16" ht="24" customHeight="1">
+      <x:c r="A16" s="1"/>
+      <x:c r="B16" s="1"/>
+      <x:c r="C16" s="1"/>
+      <x:c r="D16" s="1"/>
+      <x:c r="E16" s="1"/>
+      <x:c r="F16" s="1"/>
+      <x:c r="G16" s="1"/>
+      <x:c r="H16" s="1"/>
+      <x:c r="I16" s="1"/>
+      <x:c r="J16" s="1"/>
+      <x:c r="K16" s="1"/>
+      <x:c r="L16" s="1"/>
+      <x:c r="M16" s="1"/>
+      <x:c r="N16" s="1"/>
+      <x:c r="O16" s="1"/>
+      <x:c r="P16" s="1"/>
+      <x:c r="Q16" s="1"/>
+      <x:c r="R16" s="1"/>
+      <x:c r="S16" s="1"/>
+      <x:c r="T16" s="1"/>
+    </x:row>
+    <x:row r="17" ht="24" customHeight="1">
+      <x:c r="A17" s="1"/>
+      <x:c r="B17" s="1"/>
+      <x:c r="C17" s="1"/>
+      <x:c r="D17" s="1"/>
+      <x:c r="E17" s="1"/>
+      <x:c r="F17" s="1"/>
+      <x:c r="G17" s="1"/>
+      <x:c r="H17" s="1"/>
+      <x:c r="I17" s="1"/>
+      <x:c r="J17" s="1"/>
+      <x:c r="K17" s="1"/>
+      <x:c r="L17" s="1"/>
+      <x:c r="M17" s="1"/>
+      <x:c r="N17" s="1"/>
+      <x:c r="O17" s="1"/>
+      <x:c r="P17" s="1"/>
+      <x:c r="Q17" s="1"/>
+      <x:c r="R17" s="1"/>
+      <x:c r="S17" s="1"/>
+      <x:c r="T17" s="1"/>
+    </x:row>
+    <x:row r="18" ht="24" customHeight="1">
+      <x:c r="A18" s="1"/>
+      <x:c r="B18" s="1"/>
+      <x:c r="C18" s="1"/>
+      <x:c r="D18" s="1"/>
+      <x:c r="E18" s="1"/>
+      <x:c r="F18" s="1"/>
+      <x:c r="G18" s="1"/>
+      <x:c r="H18" s="1"/>
+      <x:c r="I18" s="1"/>
+      <x:c r="J18" s="1"/>
+      <x:c r="K18" s="1"/>
+      <x:c r="L18" s="1"/>
+      <x:c r="M18" s="1"/>
+      <x:c r="N18" s="1"/>
+      <x:c r="O18" s="1"/>
+      <x:c r="P18" s="1"/>
+      <x:c r="Q18" s="1"/>
+      <x:c r="R18" s="1"/>
+      <x:c r="S18" s="1"/>
+      <x:c r="T18" s="1"/>
+    </x:row>
+    <x:row r="19" ht="24" customHeight="1">
+      <x:c r="A19" s="1"/>
+      <x:c r="B19" s="1"/>
+      <x:c r="C19" s="1"/>
+      <x:c r="D19" s="1"/>
+      <x:c r="E19" s="1"/>
+      <x:c r="F19" s="1"/>
+      <x:c r="G19" s="1"/>
+      <x:c r="H19" s="1"/>
+      <x:c r="I19" s="1"/>
+      <x:c r="J19" s="1"/>
+      <x:c r="K19" s="1"/>
+      <x:c r="L19" s="1"/>
+      <x:c r="M19" s="1"/>
+      <x:c r="N19" s="1"/>
+      <x:c r="O19" s="1"/>
+      <x:c r="P19" s="1"/>
+      <x:c r="Q19" s="1"/>
+      <x:c r="R19" s="1"/>
+      <x:c r="S19" s="1"/>
+      <x:c r="T19" s="1"/>
+    </x:row>
+    <x:row r="20" ht="24" customHeight="1">
+      <x:c r="A20" s="1"/>
+      <x:c r="B20" s="1"/>
+      <x:c r="C20" s="1"/>
+      <x:c r="D20" s="1"/>
+      <x:c r="E20" s="1"/>
+      <x:c r="F20" s="1"/>
+      <x:c r="G20" s="1"/>
+      <x:c r="H20" s="1"/>
+      <x:c r="I20" s="1"/>
+      <x:c r="J20" s="1"/>
+      <x:c r="K20" s="1"/>
+      <x:c r="L20" s="1"/>
+      <x:c r="M20" s="1"/>
+      <x:c r="N20" s="1"/>
+      <x:c r="O20" s="1"/>
+      <x:c r="P20" s="1"/>
+      <x:c r="Q20" s="1"/>
+      <x:c r="R20" s="1"/>
+      <x:c r="S20" s="1"/>
+      <x:c r="T20" s="1"/>
+    </x:row>
+    <x:row r="21" ht="24" customHeight="1">
+      <x:c r="A21" s="1"/>
+      <x:c r="B21" s="1"/>
+      <x:c r="C21" s="1"/>
+      <x:c r="D21" s="1"/>
+      <x:c r="E21" s="1"/>
+      <x:c r="F21" s="1"/>
+      <x:c r="G21" s="1"/>
+      <x:c r="H21" s="1"/>
+      <x:c r="I21" s="1"/>
+      <x:c r="J21" s="1"/>
+      <x:c r="K21" s="1"/>
+      <x:c r="L21" s="1"/>
+      <x:c r="M21" s="1"/>
+      <x:c r="N21" s="1"/>
+      <x:c r="O21" s="1"/>
+      <x:c r="P21" s="1"/>
+      <x:c r="Q21" s="1"/>
+      <x:c r="R21" s="1"/>
+      <x:c r="S21" s="1"/>
+      <x:c r="T21" s="1"/>
+    </x:row>
+    <x:row r="22" ht="24" customHeight="1">
+      <x:c r="A22" s="1"/>
+      <x:c r="B22" s="1"/>
+      <x:c r="C22" s="1"/>
+      <x:c r="D22" s="1"/>
+      <x:c r="E22" s="1"/>
+      <x:c r="F22" s="1"/>
+      <x:c r="G22" s="1"/>
+      <x:c r="H22" s="1"/>
+      <x:c r="I22" s="1"/>
+      <x:c r="J22" s="1"/>
+      <x:c r="K22" s="1"/>
+      <x:c r="L22" s="1"/>
+      <x:c r="M22" s="1"/>
+      <x:c r="N22" s="1"/>
+      <x:c r="O22" s="1"/>
+      <x:c r="P22" s="1"/>
+      <x:c r="Q22" s="1"/>
+      <x:c r="R22" s="1"/>
+      <x:c r="S22" s="1"/>
+      <x:c r="T22" s="1"/>
+    </x:row>
+    <x:row r="23" ht="24" customHeight="1">
+      <x:c r="A23" s="1"/>
+      <x:c r="B23" s="1"/>
+      <x:c r="C23" s="1"/>
+      <x:c r="D23" s="1"/>
+      <x:c r="E23" s="1"/>
+      <x:c r="F23" s="1"/>
+      <x:c r="G23" s="1"/>
+      <x:c r="H23" s="1"/>
+      <x:c r="I23" s="1"/>
+      <x:c r="J23" s="1"/>
+      <x:c r="K23" s="1"/>
+      <x:c r="L23" s="1"/>
+      <x:c r="M23" s="1"/>
+      <x:c r="N23" s="1"/>
+      <x:c r="O23" s="1"/>
+      <x:c r="P23" s="1"/>
+      <x:c r="Q23" s="1"/>
+      <x:c r="R23" s="1"/>
+      <x:c r="S23" s="1"/>
+      <x:c r="T23" s="1"/>
+    </x:row>
+    <x:row r="24" ht="24" customHeight="1">
+      <x:c r="A24" s="1"/>
+      <x:c r="B24" s="1"/>
+      <x:c r="C24" s="1"/>
+      <x:c r="D24" s="1"/>
+      <x:c r="E24" s="1"/>
+      <x:c r="F24" s="1"/>
+      <x:c r="G24" s="1"/>
+      <x:c r="H24" s="1"/>
+      <x:c r="I24" s="1"/>
+      <x:c r="J24" s="1"/>
+      <x:c r="K24" s="1"/>
+      <x:c r="L24" s="1"/>
+      <x:c r="M24" s="1"/>
+      <x:c r="N24" s="1"/>
+      <x:c r="O24" s="1"/>
+      <x:c r="P24" s="1"/>
+      <x:c r="Q24" s="1"/>
+      <x:c r="R24" s="1"/>
+      <x:c r="S24" s="1"/>
+      <x:c r="T24" s="1"/>
+    </x:row>
+    <x:row r="25" ht="24" customHeight="1">
+      <x:c r="A25" s="1"/>
+      <x:c r="B25" s="1"/>
+      <x:c r="C25" s="1"/>
+      <x:c r="D25" s="1"/>
+      <x:c r="E25" s="1"/>
+      <x:c r="F25" s="1"/>
+      <x:c r="G25" s="1"/>
+      <x:c r="H25" s="1"/>
+      <x:c r="I25" s="1"/>
+      <x:c r="J25" s="1"/>
+      <x:c r="K25" s="1"/>
+      <x:c r="L25" s="1"/>
+      <x:c r="M25" s="1"/>
+      <x:c r="N25" s="1"/>
+      <x:c r="O25" s="1"/>
+      <x:c r="P25" s="1"/>
+      <x:c r="Q25" s="1"/>
+      <x:c r="R25" s="1"/>
+      <x:c r="S25" s="1"/>
+      <x:c r="T25" s="1"/>
+    </x:row>
+    <x:row r="26" ht="24" customHeight="1">
+      <x:c r="A26" s="1"/>
+      <x:c r="B26" s="1"/>
+      <x:c r="C26" s="1"/>
+      <x:c r="D26" s="1"/>
+      <x:c r="E26" s="1"/>
+      <x:c r="F26" s="1"/>
+      <x:c r="G26" s="1"/>
+      <x:c r="H26" s="1"/>
+      <x:c r="I26" s="1"/>
+      <x:c r="J26" s="1"/>
+      <x:c r="K26" s="1"/>
+      <x:c r="L26" s="1"/>
+      <x:c r="M26" s="1"/>
+      <x:c r="N26" s="1"/>
+      <x:c r="O26" s="1"/>
+      <x:c r="P26" s="1"/>
+      <x:c r="Q26" s="1"/>
+      <x:c r="R26" s="1"/>
+      <x:c r="S26" s="1"/>
+      <x:c r="T26" s="1"/>
+    </x:row>
+    <x:row r="27" ht="24" customHeight="1">
+      <x:c r="A27" s="1"/>
+      <x:c r="B27" s="1"/>
+      <x:c r="C27" s="1"/>
+      <x:c r="D27" s="1"/>
+      <x:c r="E27" s="1"/>
+      <x:c r="F27" s="1"/>
+      <x:c r="G27" s="1"/>
+      <x:c r="H27" s="1"/>
+      <x:c r="I27" s="1"/>
+      <x:c r="J27" s="1"/>
+      <x:c r="K27" s="1"/>
+      <x:c r="L27" s="1"/>
+      <x:c r="M27" s="1"/>
+      <x:c r="N27" s="1"/>
+      <x:c r="O27" s="1"/>
+      <x:c r="P27" s="1"/>
+      <x:c r="Q27" s="1"/>
+      <x:c r="R27" s="1"/>
+      <x:c r="S27" s="1"/>
+      <x:c r="T27" s="1"/>
+    </x:row>
+    <x:row r="28" ht="24" customHeight="1">
+      <x:c r="A28" s="1"/>
+      <x:c r="B28" s="1"/>
+      <x:c r="C28" s="1"/>
+      <x:c r="D28" s="1"/>
+      <x:c r="E28" s="1"/>
+      <x:c r="F28" s="1"/>
+      <x:c r="G28" s="1"/>
+      <x:c r="H28" s="1"/>
+      <x:c r="I28" s="1"/>
+      <x:c r="J28" s="1"/>
+      <x:c r="K28" s="1"/>
+      <x:c r="L28" s="1"/>
+      <x:c r="M28" s="1"/>
+      <x:c r="N28" s="1"/>
+      <x:c r="O28" s="1"/>
+      <x:c r="P28" s="1"/>
+      <x:c r="Q28" s="1"/>
+      <x:c r="R28" s="1"/>
+      <x:c r="S28" s="1"/>
+      <x:c r="T28" s="1"/>
+    </x:row>
+    <x:row r="29" ht="24" customHeight="1">
+      <x:c r="A29" s="1"/>
+      <x:c r="B29" s="1"/>
+      <x:c r="C29" s="1"/>
+      <x:c r="D29" s="1"/>
+      <x:c r="E29" s="1"/>
+      <x:c r="F29" s="1"/>
+      <x:c r="G29" s="1"/>
+      <x:c r="H29" s="1"/>
+      <x:c r="I29" s="1"/>
+      <x:c r="J29" s="1"/>
+      <x:c r="K29" s="1"/>
+      <x:c r="L29" s="1"/>
+      <x:c r="M29" s="1"/>
+      <x:c r="N29" s="1"/>
+      <x:c r="O29" s="1"/>
+      <x:c r="P29" s="1"/>
+      <x:c r="Q29" s="1"/>
+      <x:c r="R29" s="1"/>
+      <x:c r="S29" s="1"/>
+      <x:c r="T29" s="1"/>
+    </x:row>
+    <x:row r="30" ht="24" customHeight="1">
+      <x:c r="A30" s="1"/>
+      <x:c r="B30" s="1"/>
+      <x:c r="C30" s="1"/>
+      <x:c r="D30" s="1"/>
+      <x:c r="E30" s="1"/>
+      <x:c r="F30" s="1"/>
+      <x:c r="G30" s="1"/>
+      <x:c r="H30" s="1"/>
+      <x:c r="I30" s="1"/>
+      <x:c r="J30" s="1"/>
+      <x:c r="K30" s="1"/>
+      <x:c r="L30" s="1"/>
+      <x:c r="M30" s="1"/>
+      <x:c r="N30" s="1"/>
+      <x:c r="O30" s="1"/>
+      <x:c r="P30" s="1"/>
+      <x:c r="Q30" s="1"/>
+      <x:c r="R30" s="1"/>
+      <x:c r="S30" s="1"/>
+      <x:c r="T30" s="1"/>
+    </x:row>
+    <x:row r="31" ht="24" customHeight="1">
+      <x:c r="A31" s="1"/>
+      <x:c r="B31" s="1"/>
+      <x:c r="C31" s="1"/>
+      <x:c r="D31" s="1"/>
+      <x:c r="E31" s="1"/>
+      <x:c r="F31" s="1"/>
+      <x:c r="G31" s="1"/>
+      <x:c r="H31" s="1"/>
+      <x:c r="I31" s="1"/>
+      <x:c r="J31" s="1"/>
+      <x:c r="K31" s="1"/>
+      <x:c r="L31" s="1"/>
+      <x:c r="M31" s="1"/>
+      <x:c r="N31" s="1"/>
+      <x:c r="O31" s="1"/>
+      <x:c r="P31" s="1"/>
+      <x:c r="Q31" s="1"/>
+      <x:c r="R31" s="1"/>
+      <x:c r="S31" s="1"/>
+      <x:c r="T31" s="1"/>
+    </x:row>
+    <x:row r="32" ht="24" customHeight="1">
+      <x:c r="A32" s="1"/>
+      <x:c r="B32" s="1"/>
+      <x:c r="C32" s="1"/>
+      <x:c r="D32" s="1"/>
+      <x:c r="E32" s="1"/>
+      <x:c r="F32" s="1"/>
+      <x:c r="G32" s="1"/>
+      <x:c r="H32" s="1"/>
+      <x:c r="I32" s="1"/>
+      <x:c r="J32" s="1"/>
+      <x:c r="K32" s="1"/>
+      <x:c r="L32" s="1"/>
+      <x:c r="M32" s="1"/>
+      <x:c r="N32" s="1"/>
+      <x:c r="O32" s="1"/>
+      <x:c r="P32" s="1"/>
+      <x:c r="Q32" s="1"/>
+      <x:c r="R32" s="1"/>
+      <x:c r="S32" s="1"/>
+      <x:c r="T32" s="1"/>
+    </x:row>
+    <x:row r="33" ht="24" customHeight="1">
+      <x:c r="A33" s="1"/>
+      <x:c r="B33" s="1"/>
+      <x:c r="C33" s="1"/>
+      <x:c r="D33" s="1"/>
+      <x:c r="E33" s="1"/>
+      <x:c r="F33" s="1"/>
+      <x:c r="G33" s="1"/>
+      <x:c r="H33" s="1"/>
+      <x:c r="I33" s="1"/>
+      <x:c r="J33" s="1"/>
+      <x:c r="K33" s="1"/>
+      <x:c r="L33" s="1"/>
+      <x:c r="M33" s="1"/>
+      <x:c r="N33" s="1"/>
+      <x:c r="O33" s="1"/>
+      <x:c r="P33" s="1"/>
+      <x:c r="Q33" s="1"/>
+      <x:c r="R33" s="1"/>
+      <x:c r="S33" s="1"/>
+      <x:c r="T33" s="1"/>
+    </x:row>
+    <x:row r="34" ht="24" customHeight="1">
+      <x:c r="A34" s="1"/>
+      <x:c r="B34" s="1"/>
+      <x:c r="C34" s="1"/>
+      <x:c r="D34" s="1"/>
+      <x:c r="E34" s="1"/>
+      <x:c r="F34" s="1"/>
+      <x:c r="G34" s="1"/>
+      <x:c r="H34" s="1"/>
+      <x:c r="I34" s="1"/>
+      <x:c r="J34" s="1"/>
+      <x:c r="K34" s="1"/>
+      <x:c r="L34" s="1"/>
+      <x:c r="M34" s="1"/>
+      <x:c r="N34" s="1"/>
+      <x:c r="O34" s="1"/>
+      <x:c r="P34" s="1"/>
+      <x:c r="Q34" s="1"/>
+      <x:c r="R34" s="1"/>
+      <x:c r="S34" s="1"/>
+      <x:c r="T34" s="1"/>
+    </x:row>
+    <x:row r="35" ht="24" customHeight="1">
+      <x:c r="A35" s="1"/>
+      <x:c r="B35" s="1"/>
+      <x:c r="C35" s="1"/>
+      <x:c r="D35" s="1"/>
+      <x:c r="E35" s="1"/>
+      <x:c r="F35" s="1"/>
+      <x:c r="G35" s="1"/>
+      <x:c r="H35" s="1"/>
+      <x:c r="I35" s="1"/>
+      <x:c r="J35" s="1"/>
+      <x:c r="K35" s="1"/>
+      <x:c r="L35" s="1"/>
+      <x:c r="M35" s="1"/>
+      <x:c r="N35" s="1"/>
+      <x:c r="O35" s="1"/>
+      <x:c r="P35" s="1"/>
+      <x:c r="Q35" s="1"/>
+      <x:c r="R35" s="1"/>
+      <x:c r="S35" s="1"/>
+      <x:c r="T35" s="1"/>
+    </x:row>
+    <x:row r="36" ht="24" customHeight="1">
+      <x:c r="A36" s="1"/>
+      <x:c r="B36" s="1"/>
+      <x:c r="C36" s="1"/>
+      <x:c r="D36" s="1"/>
+      <x:c r="E36" s="1"/>
+      <x:c r="F36" s="1"/>
+      <x:c r="G36" s="1"/>
+      <x:c r="H36" s="1"/>
+      <x:c r="I36" s="1"/>
+      <x:c r="J36" s="1"/>
+      <x:c r="K36" s="1"/>
+      <x:c r="L36" s="1"/>
+      <x:c r="M36" s="1"/>
+      <x:c r="N36" s="1"/>
+      <x:c r="O36" s="1"/>
+      <x:c r="P36" s="1"/>
+      <x:c r="Q36" s="1"/>
+      <x:c r="R36" s="1"/>
+      <x:c r="S36" s="1"/>
+      <x:c r="T36" s="1"/>
+    </x:row>
+    <x:row r="37" ht="24" customHeight="1">
+      <x:c r="A37" s="1"/>
+      <x:c r="B37" s="1"/>
+      <x:c r="C37" s="1"/>
+      <x:c r="D37" s="1"/>
+      <x:c r="E37" s="1"/>
+      <x:c r="F37" s="1"/>
+      <x:c r="G37" s="1"/>
+      <x:c r="H37" s="1"/>
+      <x:c r="I37" s="1"/>
+      <x:c r="J37" s="1"/>
+      <x:c r="K37" s="1"/>
+      <x:c r="L37" s="1"/>
+      <x:c r="M37" s="1"/>
+      <x:c r="N37" s="1"/>
+      <x:c r="O37" s="1"/>
+      <x:c r="P37" s="1"/>
+      <x:c r="Q37" s="1"/>
+      <x:c r="R37" s="1"/>
+      <x:c r="S37" s="1"/>
+      <x:c r="T37" s="1"/>
+    </x:row>
+    <x:row r="38" ht="24" customHeight="1">
+      <x:c r="A38" s="1"/>
+      <x:c r="B38" s="1"/>
+      <x:c r="C38" s="1"/>
+      <x:c r="D38" s="1"/>
+      <x:c r="E38" s="1"/>
+      <x:c r="F38" s="1"/>
+      <x:c r="G38" s="1"/>
+      <x:c r="H38" s="1"/>
+      <x:c r="I38" s="1"/>
+      <x:c r="J38" s="1"/>
+      <x:c r="K38" s="1"/>
+      <x:c r="L38" s="1"/>
+      <x:c r="M38" s="1"/>
+      <x:c r="N38" s="1"/>
+      <x:c r="O38" s="1"/>
+      <x:c r="P38" s="1"/>
+      <x:c r="Q38" s="1"/>
+      <x:c r="R38" s="1"/>
+      <x:c r="S38" s="1"/>
+      <x:c r="T38" s="1"/>
+    </x:row>
+    <x:row r="39" ht="24" customHeight="1">
+      <x:c r="A39" s="1"/>
+      <x:c r="B39" s="1"/>
+      <x:c r="C39" s="1"/>
+      <x:c r="D39" s="1"/>
+      <x:c r="E39" s="1"/>
+      <x:c r="F39" s="1"/>
+      <x:c r="G39" s="1"/>
+      <x:c r="H39" s="1"/>
+      <x:c r="I39" s="1"/>
+      <x:c r="J39" s="1"/>
+      <x:c r="K39" s="1"/>
+      <x:c r="L39" s="1"/>
+      <x:c r="M39" s="1"/>
+      <x:c r="N39" s="1"/>
+      <x:c r="O39" s="1"/>
+      <x:c r="P39" s="1"/>
+      <x:c r="Q39" s="1"/>
+      <x:c r="R39" s="1"/>
+      <x:c r="S39" s="1"/>
+      <x:c r="T39" s="1"/>
+    </x:row>
+    <x:row r="40" ht="24" customHeight="1">
+      <x:c r="A40" s="1"/>
+      <x:c r="B40" s="1"/>
+      <x:c r="C40" s="1"/>
+      <x:c r="D40" s="1"/>
+      <x:c r="E40" s="1"/>
+      <x:c r="F40" s="1"/>
+      <x:c r="G40" s="1"/>
+      <x:c r="H40" s="1"/>
+      <x:c r="I40" s="1"/>
+      <x:c r="J40" s="1"/>
+      <x:c r="K40" s="1"/>
+      <x:c r="L40" s="1"/>
+      <x:c r="M40" s="1"/>
+      <x:c r="N40" s="1"/>
+      <x:c r="O40" s="1"/>
+      <x:c r="P40" s="1"/>
+      <x:c r="Q40" s="1"/>
+      <x:c r="R40" s="1"/>
+      <x:c r="S40" s="1"/>
+      <x:c r="T40" s="1"/>
+    </x:row>
+    <x:row r="41" ht="24" customHeight="1">
+      <x:c r="A41" s="1"/>
+      <x:c r="B41" s="1"/>
+      <x:c r="C41" s="1"/>
+      <x:c r="D41" s="1"/>
+      <x:c r="E41" s="1"/>
+      <x:c r="F41" s="1"/>
+      <x:c r="G41" s="1"/>
+      <x:c r="H41" s="1"/>
+      <x:c r="I41" s="1"/>
+      <x:c r="J41" s="1"/>
+      <x:c r="K41" s="1"/>
+      <x:c r="L41" s="1"/>
+      <x:c r="M41" s="1"/>
+      <x:c r="N41" s="1"/>
+      <x:c r="O41" s="1"/>
+      <x:c r="P41" s="1"/>
+      <x:c r="Q41" s="1"/>
+      <x:c r="R41" s="1"/>
+      <x:c r="S41" s="1"/>
+      <x:c r="T41" s="1"/>
+    </x:row>
+    <x:row r="42" ht="24" customHeight="1">
+      <x:c r="A42" s="1"/>
+      <x:c r="B42" s="1"/>
+      <x:c r="C42" s="1"/>
+      <x:c r="D42" s="1"/>
+      <x:c r="E42" s="1"/>
+      <x:c r="F42" s="1"/>
+      <x:c r="G42" s="1"/>
+      <x:c r="H42" s="1"/>
+      <x:c r="I42" s="1"/>
+      <x:c r="J42" s="1"/>
+      <x:c r="K42" s="1"/>
+      <x:c r="L42" s="1"/>
+      <x:c r="M42" s="1"/>
+      <x:c r="N42" s="1"/>
+      <x:c r="O42" s="1"/>
+      <x:c r="P42" s="1"/>
+      <x:c r="Q42" s="1"/>
+      <x:c r="R42" s="1"/>
+      <x:c r="S42" s="1"/>
+      <x:c r="T42" s="1"/>
+    </x:row>
+    <x:row r="43" ht="24" customHeight="1">
+      <x:c r="A43" s="1"/>
+      <x:c r="B43" s="1"/>
+      <x:c r="C43" s="1"/>
+      <x:c r="D43" s="1"/>
+      <x:c r="E43" s="1"/>
+      <x:c r="F43" s="1"/>
+      <x:c r="G43" s="1"/>
+      <x:c r="H43" s="1"/>
+      <x:c r="I43" s="1"/>
+      <x:c r="J43" s="1"/>
+      <x:c r="K43" s="1"/>
+      <x:c r="L43" s="1"/>
+      <x:c r="M43" s="1"/>
+      <x:c r="N43" s="1"/>
+      <x:c r="O43" s="1"/>
+      <x:c r="P43" s="1"/>
+      <x:c r="Q43" s="1"/>
+      <x:c r="R43" s="1"/>
+      <x:c r="S43" s="1"/>
+      <x:c r="T43" s="1"/>
+    </x:row>
+    <x:row r="44" ht="24" customHeight="1">
+      <x:c r="A44" s="1"/>
+      <x:c r="B44" s="1"/>
+      <x:c r="C44" s="1"/>
+      <x:c r="D44" s="1"/>
+      <x:c r="E44" s="1"/>
+      <x:c r="F44" s="1"/>
+      <x:c r="G44" s="1"/>
+      <x:c r="H44" s="1"/>
+      <x:c r="I44" s="1"/>
+      <x:c r="J44" s="1"/>
+      <x:c r="K44" s="1"/>
+      <x:c r="L44" s="1"/>
+      <x:c r="M44" s="1"/>
+      <x:c r="N44" s="1"/>
+      <x:c r="O44" s="1"/>
+      <x:c r="P44" s="1"/>
+      <x:c r="Q44" s="1"/>
+      <x:c r="R44" s="1"/>
+      <x:c r="S44" s="1"/>
+      <x:c r="T44" s="1"/>
+    </x:row>
+    <x:row r="45" ht="24" customHeight="1">
+      <x:c r="A45" s="1"/>
+      <x:c r="B45" s="1"/>
+      <x:c r="C45" s="1"/>
+      <x:c r="D45" s="1"/>
+      <x:c r="E45" s="1"/>
+      <x:c r="F45" s="1"/>
+      <x:c r="G45" s="1"/>
+      <x:c r="H45" s="1"/>
+      <x:c r="I45" s="1"/>
+      <x:c r="J45" s="1"/>
+      <x:c r="K45" s="1"/>
+      <x:c r="L45" s="1"/>
+      <x:c r="M45" s="1"/>
+      <x:c r="N45" s="1"/>
+      <x:c r="O45" s="1"/>
+      <x:c r="P45" s="1"/>
+      <x:c r="Q45" s="1"/>
+      <x:c r="R45" s="1"/>
+      <x:c r="S45" s="1"/>
+      <x:c r="T45" s="1"/>
+    </x:row>
+    <x:row r="46" ht="24" customHeight="1">
+      <x:c r="A46" s="1"/>
+      <x:c r="B46" s="1"/>
+      <x:c r="C46" s="1"/>
+      <x:c r="D46" s="1"/>
+      <x:c r="E46" s="1"/>
+      <x:c r="F46" s="1"/>
+      <x:c r="G46" s="1"/>
+      <x:c r="H46" s="1"/>
+      <x:c r="I46" s="1"/>
+      <x:c r="J46" s="1"/>
+      <x:c r="K46" s="1"/>
+      <x:c r="L46" s="1"/>
+      <x:c r="M46" s="1"/>
+      <x:c r="N46" s="1"/>
+      <x:c r="O46" s="1"/>
+      <x:c r="P46" s="1"/>
+      <x:c r="Q46" s="1"/>
+      <x:c r="R46" s="1"/>
+      <x:c r="S46" s="1"/>
+      <x:c r="T46" s="1"/>
+    </x:row>
+    <x:row r="47" ht="24" customHeight="1">
+      <x:c r="A47" s="1"/>
+      <x:c r="B47" s="1"/>
+      <x:c r="C47" s="1"/>
+      <x:c r="D47" s="1"/>
+      <x:c r="E47" s="1"/>
+      <x:c r="F47" s="1"/>
+      <x:c r="G47" s="1"/>
+      <x:c r="H47" s="1"/>
+      <x:c r="I47" s="1"/>
+      <x:c r="J47" s="1"/>
+      <x:c r="K47" s="1"/>
+      <x:c r="L47" s="1"/>
+      <x:c r="M47" s="1"/>
+      <x:c r="N47" s="1"/>
+      <x:c r="O47" s="1"/>
+      <x:c r="P47" s="1"/>
+      <x:c r="Q47" s="1"/>
+      <x:c r="R47" s="1"/>
+      <x:c r="S47" s="1"/>
+      <x:c r="T47" s="1"/>
+    </x:row>
+    <x:row r="48" ht="24" customHeight="1">
+      <x:c r="A48" s="1"/>
+      <x:c r="B48" s="1"/>
+      <x:c r="C48" s="1"/>
+      <x:c r="D48" s="1"/>
+      <x:c r="E48" s="1"/>
+      <x:c r="F48" s="1"/>
+      <x:c r="G48" s="1"/>
+      <x:c r="H48" s="1"/>
+      <x:c r="I48" s="1"/>
+      <x:c r="J48" s="1"/>
+      <x:c r="K48" s="1"/>
+      <x:c r="L48" s="1"/>
+      <x:c r="M48" s="1"/>
+      <x:c r="N48" s="1"/>
+      <x:c r="O48" s="1"/>
+      <x:c r="P48" s="1"/>
+      <x:c r="Q48" s="1"/>
+      <x:c r="R48" s="1"/>
+      <x:c r="S48" s="1"/>
+      <x:c r="T48" s="1"/>
+    </x:row>
+    <x:row r="49" ht="24" customHeight="1">
+      <x:c r="A49" s="1"/>
+      <x:c r="B49" s="1"/>
+      <x:c r="C49" s="1"/>
+      <x:c r="D49" s="1"/>
+      <x:c r="E49" s="1"/>
+      <x:c r="F49" s="1"/>
+      <x:c r="G49" s="1"/>
+      <x:c r="H49" s="1"/>
+      <x:c r="I49" s="1"/>
+      <x:c r="J49" s="1"/>
+      <x:c r="K49" s="1"/>
+      <x:c r="L49" s="1"/>
+      <x:c r="M49" s="1"/>
+      <x:c r="N49" s="1"/>
+      <x:c r="O49" s="1"/>
+      <x:c r="P49" s="1"/>
+      <x:c r="Q49" s="1"/>
+      <x:c r="R49" s="1"/>
+      <x:c r="S49" s="1"/>
+      <x:c r="T49" s="1"/>
+    </x:row>
+    <x:row r="50" ht="24" customHeight="1">
+      <x:c r="A50" s="1"/>
+      <x:c r="B50" s="1"/>
+      <x:c r="C50" s="1"/>
+      <x:c r="D50" s="1"/>
+      <x:c r="E50" s="1"/>
+      <x:c r="F50" s="1"/>
+      <x:c r="G50" s="1"/>
+      <x:c r="H50" s="1"/>
+      <x:c r="I50" s="1"/>
+      <x:c r="J50" s="1"/>
+      <x:c r="K50" s="1"/>
+      <x:c r="L50" s="1"/>
+      <x:c r="M50" s="1"/>
+      <x:c r="N50" s="1"/>
+      <x:c r="O50" s="1"/>
+      <x:c r="P50" s="1"/>
+      <x:c r="Q50" s="1"/>
+      <x:c r="R50" s="1"/>
+      <x:c r="S50" s="1"/>
+      <x:c r="T50" s="1"/>
+    </x:row>
+    <x:row r="51" ht="24" customHeight="1">
+      <x:c r="A51" s="1"/>
+      <x:c r="B51" s="1"/>
+      <x:c r="C51" s="1"/>
+      <x:c r="D51" s="1"/>
+      <x:c r="E51" s="1"/>
+      <x:c r="F51" s="1"/>
+      <x:c r="G51" s="1"/>
+      <x:c r="H51" s="1"/>
+      <x:c r="I51" s="1"/>
+      <x:c r="J51" s="1"/>
+      <x:c r="K51" s="1"/>
+      <x:c r="L51" s="1"/>
+      <x:c r="M51" s="1"/>
+      <x:c r="N51" s="1"/>
+      <x:c r="O51" s="1"/>
+      <x:c r="P51" s="1"/>
+      <x:c r="Q51" s="1"/>
+      <x:c r="R51" s="1"/>
+      <x:c r="S51" s="1"/>
+      <x:c r="T51" s="1"/>
+    </x:row>
+    <x:row r="52" ht="24" customHeight="1">
+      <x:c r="A52" s="1"/>
+      <x:c r="B52" s="1"/>
+      <x:c r="C52" s="1"/>
+      <x:c r="D52" s="1"/>
+      <x:c r="E52" s="1"/>
+      <x:c r="F52" s="1"/>
+      <x:c r="G52" s="1"/>
+      <x:c r="H52" s="1"/>
+      <x:c r="I52" s="1"/>
+      <x:c r="J52" s="1"/>
+      <x:c r="K52" s="1"/>
+      <x:c r="L52" s="1"/>
+      <x:c r="M52" s="1"/>
+      <x:c r="N52" s="1"/>
+      <x:c r="O52" s="1"/>
+      <x:c r="P52" s="1"/>
+      <x:c r="Q52" s="1"/>
+      <x:c r="R52" s="1"/>
+      <x:c r="S52" s="1"/>
+      <x:c r="T52" s="1"/>
+    </x:row>
+    <x:row r="53" ht="24" customHeight="1">
+      <x:c r="A53" s="1"/>
+      <x:c r="B53" s="1"/>
+      <x:c r="C53" s="1"/>
+      <x:c r="D53" s="1"/>
+      <x:c r="E53" s="1"/>
+      <x:c r="F53" s="1"/>
+      <x:c r="G53" s="1"/>
+      <x:c r="H53" s="1"/>
+      <x:c r="I53" s="1"/>
+      <x:c r="J53" s="1"/>
+      <x:c r="K53" s="1"/>
+      <x:c r="L53" s="1"/>
+      <x:c r="M53" s="1"/>
+      <x:c r="N53" s="1"/>
+      <x:c r="O53" s="1"/>
+      <x:c r="P53" s="1"/>
+      <x:c r="Q53" s="1"/>
+      <x:c r="R53" s="1"/>
+      <x:c r="S53" s="1"/>
+      <x:c r="T53" s="1"/>
+    </x:row>
+    <x:row r="54" ht="24" customHeight="1">
+      <x:c r="A54" s="1"/>
+      <x:c r="B54" s="1"/>
+      <x:c r="C54" s="1"/>
+      <x:c r="D54" s="1"/>
+      <x:c r="E54" s="1"/>
+      <x:c r="F54" s="1"/>
+      <x:c r="G54" s="1"/>
+      <x:c r="H54" s="1"/>
+      <x:c r="I54" s="1"/>
+      <x:c r="J54" s="1"/>
+      <x:c r="K54" s="1"/>
+      <x:c r="L54" s="1"/>
+      <x:c r="M54" s="1"/>
+      <x:c r="N54" s="1"/>
+      <x:c r="O54" s="1"/>
+      <x:c r="P54" s="1"/>
+      <x:c r="Q54" s="1"/>
+      <x:c r="R54" s="1"/>
+      <x:c r="S54" s="1"/>
+      <x:c r="T54" s="1"/>
+    </x:row>
+    <x:row r="55" ht="24" customHeight="1">
+      <x:c r="A55" s="1"/>
+      <x:c r="B55" s="1"/>
+      <x:c r="C55" s="1"/>
+      <x:c r="D55" s="1"/>
+      <x:c r="E55" s="1"/>
+      <x:c r="F55" s="1"/>
+      <x:c r="G55" s="1"/>
+      <x:c r="H55" s="1"/>
+      <x:c r="I55" s="1"/>
+      <x:c r="J55" s="1"/>
+      <x:c r="K55" s="1"/>
+      <x:c r="L55" s="1"/>
+      <x:c r="M55" s="1"/>
+      <x:c r="N55" s="1"/>
+      <x:c r="O55" s="1"/>
+      <x:c r="P55" s="1"/>
+      <x:c r="Q55" s="1"/>
+      <x:c r="R55" s="1"/>
+      <x:c r="S55" s="1"/>
+      <x:c r="T55" s="1"/>
+    </x:row>
+    <x:row r="56" ht="24" customHeight="1">
+      <x:c r="A56" s="1"/>
+      <x:c r="B56" s="1"/>
+      <x:c r="C56" s="1"/>
+      <x:c r="D56" s="1"/>
+      <x:c r="E56" s="1"/>
+      <x:c r="F56" s="1"/>
+      <x:c r="G56" s="1"/>
+      <x:c r="H56" s="1"/>
+      <x:c r="I56" s="1"/>
+      <x:c r="J56" s="1"/>
+      <x:c r="K56" s="1"/>
+      <x:c r="L56" s="1"/>
+      <x:c r="M56" s="1"/>
+      <x:c r="N56" s="1"/>
+      <x:c r="O56" s="1"/>
+      <x:c r="P56" s="1"/>
+      <x:c r="Q56" s="1"/>
+      <x:c r="R56" s="1"/>
+      <x:c r="S56" s="1"/>
+      <x:c r="T56" s="1"/>
+    </x:row>
+    <x:row r="57" ht="24" customHeight="1">
+      <x:c r="A57" s="1"/>
+      <x:c r="B57" s="1"/>
+      <x:c r="C57" s="1"/>
+      <x:c r="D57" s="1"/>
+      <x:c r="E57" s="1"/>
+      <x:c r="F57" s="1"/>
+      <x:c r="G57" s="1"/>
+      <x:c r="H57" s="1"/>
+      <x:c r="I57" s="1"/>
+      <x:c r="J57" s="1"/>
+      <x:c r="K57" s="1"/>
+      <x:c r="L57" s="1"/>
+      <x:c r="M57" s="1"/>
+      <x:c r="N57" s="1"/>
+      <x:c r="O57" s="1"/>
+      <x:c r="P57" s="1"/>
+      <x:c r="Q57" s="1"/>
+      <x:c r="R57" s="1"/>
+      <x:c r="S57" s="1"/>
+      <x:c r="T57" s="1"/>
+    </x:row>
+    <x:row r="58" ht="24" customHeight="1">
+      <x:c r="A58" s="1"/>
+      <x:c r="B58" s="1"/>
+      <x:c r="C58" s="1"/>
+      <x:c r="D58" s="1"/>
+      <x:c r="E58" s="1"/>
+      <x:c r="F58" s="1"/>
+      <x:c r="G58" s="1"/>
+      <x:c r="H58" s="1"/>
+      <x:c r="I58" s="1"/>
+      <x:c r="J58" s="1"/>
+      <x:c r="K58" s="1"/>
+      <x:c r="L58" s="1"/>
+      <x:c r="M58" s="1"/>
+      <x:c r="N58" s="1"/>
+      <x:c r="O58" s="1"/>
+      <x:c r="P58" s="1"/>
+      <x:c r="Q58" s="1"/>
+      <x:c r="R58" s="1"/>
+      <x:c r="S58" s="1"/>
+      <x:c r="T58" s="1"/>
+    </x:row>
+    <x:row r="59" ht="24" customHeight="1">
+      <x:c r="A59" s="1"/>
+      <x:c r="B59" s="1"/>
+      <x:c r="C59" s="1"/>
+      <x:c r="D59" s="1"/>
+      <x:c r="E59" s="1"/>
+      <x:c r="F59" s="1"/>
+      <x:c r="G59" s="1"/>
+      <x:c r="H59" s="1"/>
+      <x:c r="I59" s="1"/>
+      <x:c r="J59" s="1"/>
+      <x:c r="K59" s="1"/>
+      <x:c r="L59" s="1"/>
+      <x:c r="M59" s="1"/>
+      <x:c r="N59" s="1"/>
+      <x:c r="O59" s="1"/>
+      <x:c r="P59" s="1"/>
+      <x:c r="Q59" s="1"/>
+      <x:c r="R59" s="1"/>
+      <x:c r="S59" s="1"/>
+      <x:c r="T59" s="1"/>
+    </x:row>
+    <x:row r="60" ht="24" customHeight="1">
+      <x:c r="A60" s="1"/>
+      <x:c r="B60" s="1"/>
+      <x:c r="C60" s="1"/>
+      <x:c r="D60" s="1"/>
+      <x:c r="E60" s="1"/>
+      <x:c r="F60" s="1"/>
+      <x:c r="G60" s="1"/>
+      <x:c r="H60" s="1"/>
+      <x:c r="I60" s="1"/>
+      <x:c r="J60" s="1"/>
+      <x:c r="K60" s="1"/>
+      <x:c r="L60" s="1"/>
+      <x:c r="M60" s="1"/>
+      <x:c r="N60" s="1"/>
+      <x:c r="O60" s="1"/>
+      <x:c r="P60" s="1"/>
+      <x:c r="Q60" s="1"/>
+      <x:c r="R60" s="1"/>
+      <x:c r="S60" s="1"/>
+      <x:c r="T60" s="1"/>
+    </x:row>
+    <x:row r="61" ht="24" customHeight="1">
+      <x:c r="A61" s="1"/>
+      <x:c r="B61" s="1"/>
+      <x:c r="C61" s="1"/>
+      <x:c r="D61" s="1"/>
+      <x:c r="E61" s="1"/>
+      <x:c r="F61" s="1"/>
+      <x:c r="G61" s="1"/>
+      <x:c r="H61" s="1"/>
+      <x:c r="I61" s="1"/>
+      <x:c r="J61" s="1"/>
+      <x:c r="K61" s="1"/>
+      <x:c r="L61" s="1"/>
+      <x:c r="M61" s="1"/>
+      <x:c r="N61" s="1"/>
+      <x:c r="O61" s="1"/>
+      <x:c r="P61" s="1"/>
+      <x:c r="Q61" s="1"/>
+      <x:c r="R61" s="1"/>
+      <x:c r="S61" s="1"/>
+      <x:c r="T61" s="1"/>
+    </x:row>
+    <x:row r="62" ht="24" customHeight="1">
+      <x:c r="A62" s="1"/>
+      <x:c r="B62" s="1"/>
+      <x:c r="C62" s="1"/>
+      <x:c r="D62" s="1"/>
+      <x:c r="E62" s="1"/>
+      <x:c r="F62" s="1"/>
+      <x:c r="G62" s="1"/>
+      <x:c r="H62" s="1"/>
+      <x:c r="I62" s="1"/>
+      <x:c r="J62" s="1"/>
+      <x:c r="K62" s="1"/>
+      <x:c r="L62" s="1"/>
+      <x:c r="M62" s="1"/>
+      <x:c r="N62" s="1"/>
+      <x:c r="O62" s="1"/>
+      <x:c r="P62" s="1"/>
+      <x:c r="Q62" s="1"/>
+      <x:c r="R62" s="1"/>
+      <x:c r="S62" s="1"/>
+      <x:c r="T62" s="1"/>
+    </x:row>
+    <x:row r="63" ht="24" customHeight="1">
+      <x:c r="A63" s="1"/>
+      <x:c r="B63" s="1"/>
+      <x:c r="C63" s="1"/>
+      <x:c r="D63" s="1"/>
+      <x:c r="E63" s="1"/>
+      <x:c r="F63" s="1"/>
+      <x:c r="G63" s="1"/>
+      <x:c r="H63" s="1"/>
+      <x:c r="I63" s="1"/>
+      <x:c r="J63" s="1"/>
+      <x:c r="K63" s="1"/>
+      <x:c r="L63" s="1"/>
+      <x:c r="M63" s="1"/>
+      <x:c r="N63" s="1"/>
+      <x:c r="O63" s="1"/>
+      <x:c r="P63" s="1"/>
+      <x:c r="Q63" s="1"/>
+      <x:c r="R63" s="1"/>
+      <x:c r="S63" s="1"/>
+      <x:c r="T63" s="1"/>
+    </x:row>
+    <x:row r="64" ht="24" customHeight="1">
+      <x:c r="A64" s="1"/>
+      <x:c r="B64" s="1"/>
+      <x:c r="C64" s="1"/>
+      <x:c r="D64" s="1"/>
+      <x:c r="E64" s="1"/>
+      <x:c r="F64" s="1"/>
+      <x:c r="G64" s="1"/>
+      <x:c r="H64" s="1"/>
+      <x:c r="I64" s="1"/>
+      <x:c r="J64" s="1"/>
+      <x:c r="K64" s="1"/>
+      <x:c r="L64" s="1"/>
+      <x:c r="M64" s="1"/>
+      <x:c r="N64" s="1"/>
+      <x:c r="O64" s="1"/>
+      <x:c r="P64" s="1"/>
+      <x:c r="Q64" s="1"/>
+      <x:c r="R64" s="1"/>
+      <x:c r="S64" s="1"/>
+      <x:c r="T64" s="1"/>
+    </x:row>
+    <x:row r="65" ht="24" customHeight="1">
+      <x:c r="A65" s="1"/>
+      <x:c r="B65" s="1"/>
+      <x:c r="C65" s="1"/>
+      <x:c r="D65" s="1"/>
+      <x:c r="E65" s="1"/>
+      <x:c r="F65" s="1"/>
+      <x:c r="G65" s="1"/>
+      <x:c r="H65" s="1"/>
+      <x:c r="I65" s="1"/>
+      <x:c r="J65" s="1"/>
+      <x:c r="K65" s="1"/>
+      <x:c r="L65" s="1"/>
+      <x:c r="M65" s="1"/>
+      <x:c r="N65" s="1"/>
+      <x:c r="O65" s="1"/>
+      <x:c r="P65" s="1"/>
+      <x:c r="Q65" s="1"/>
+      <x:c r="R65" s="1"/>
+      <x:c r="S65" s="1"/>
+      <x:c r="T65" s="1"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="D1:P1"/>
+    <x:mergeCell ref="S2:T2"/>
+    <x:mergeCell ref="A15:T15"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.2" right="0.2" top="0.3" bottom="0.3" header="0.1" footer="0.1"/>
+  <x:pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="1"/>
+</x:worksheet>
 </file>